--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="191">
   <si>
     <t>clues</t>
   </si>
@@ -22,15 +22,12 @@
     <t>entidad</t>
   </si>
   <si>
-    <t>nombre_de_la_unidad_x</t>
+    <t>nombre_de_la_unidad</t>
   </si>
   <si>
     <t>consultorios</t>
   </si>
   <si>
-    <t>nombre_de_la_unidad_y</t>
-  </si>
-  <si>
     <t>respondidas</t>
   </si>
   <si>
@@ -40,18 +37,21 @@
     <t>porcentaje</t>
   </si>
   <si>
+    <t>CCIMB000102</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MCIMB000926</t>
+  </si>
+  <si>
     <t>MCIMB000214</t>
   </si>
   <si>
-    <t>CCIMB000102</t>
-  </si>
-  <si>
     <t>MCIMB003941</t>
   </si>
   <si>
-    <t>MCIMB000926</t>
-  </si>
-  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
@@ -76,231 +76,234 @@
     <t>NTIMB000131</t>
   </si>
   <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
     <t>SPIMB002195</t>
   </si>
   <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
     <t>QRIMB001664</t>
   </si>
   <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
     <t>SPIMB000445</t>
   </si>
   <si>
-    <t>NTIMB001280</t>
+    <t>ZSIMB001641</t>
   </si>
   <si>
     <t>QRIMB001652</t>
   </si>
   <si>
-    <t>ZSIMB001641</t>
+    <t>SPIMB002562</t>
   </si>
   <si>
     <t>SPIMB003146</t>
   </si>
   <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
     <t>VZIMB002395</t>
   </si>
   <si>
     <t>NTIMB001292</t>
   </si>
   <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
     <t>NTIMB001316</t>
   </si>
   <si>
     <t>NTIMB001415</t>
   </si>
   <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
   </si>
   <si>
     <t>SPIMB002533</t>
   </si>
   <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
+    <t>TSIMB000876</t>
   </si>
   <si>
     <t>TSIMB000910</t>
   </si>
   <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
     <t>TSIMB000905</t>
   </si>
   <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
     <t>VZIMB005632</t>
   </si>
   <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
     <t>VZIMB007505</t>
   </si>
   <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
     <t>MCIMB008800</t>
   </si>
   <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>MEXICO</t>
   </si>
   <si>
-    <t>CAMPECHE</t>
-  </si>
-  <si>
     <t>QUINTANA ROO</t>
   </si>
   <si>
@@ -310,18 +313,15 @@
     <t>NAYARIT</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
     <t>CHIAPAS</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
@@ -331,18 +331,21 @@
     <t>ZACATECAS</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD CASTAMAY</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. MÉXICO NUEVO</t>
+  </si>
+  <si>
     <t>SAN PEDRO TEPETITLÁN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD CASTAMAY</t>
-  </si>
-  <si>
     <t>CIUDAD LAGO</t>
   </si>
   <si>
-    <t>COL. MÉXICO NUEVO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
@@ -367,217 +370,217 @@
     <t>EL CARRIZAL</t>
   </si>
   <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD 6 DE JUNIO</t>
   </si>
   <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
   </si>
   <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
     <t>AURELIO MANRIQUE</t>
   </si>
   <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+    <t>CENTRO DE SALUD ZACATECAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL UCUM</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
+    <t>CENTRO DE SALUD TERCERAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD VILLA CACTUS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
   </si>
   <si>
     <t>TEPIC, COL. CUAUHTÉMOC</t>
   </si>
   <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
     <t>TEPIC, COL. PARAÍSO</t>
   </si>
   <si>
     <t>COLORADO DE LA MORA</t>
   </si>
   <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
   </si>
   <si>
     <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
   </si>
   <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD LAS BLANCAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -941,10 +944,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -966,13 +969,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>93</v>
@@ -983,22 +983,19 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>105</v>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>44</v>
-      </c>
-      <c r="H2">
         <v>2.3</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>94</v>
@@ -1009,25 +1006,22 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>106</v>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>44</v>
-      </c>
-      <c r="H3">
         <v>2.3</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
@@ -1035,25 +1029,22 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>107</v>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>44</v>
-      </c>
-      <c r="H4">
         <v>2.3</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
         <v>108</v>
@@ -1061,22 +1052,19 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>108</v>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>44</v>
-      </c>
-      <c r="H5">
         <v>2.3</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>95</v>
@@ -1087,22 +1075,19 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>109</v>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>44</v>
-      </c>
-      <c r="H6">
         <v>2.3</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>96</v>
@@ -1113,25 +1098,22 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>110</v>
+      <c r="E7">
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G7">
-        <v>44</v>
-      </c>
-      <c r="H7">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
         <v>111</v>
@@ -1139,25 +1121,22 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
-        <v>111</v>
+      <c r="E8">
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G8">
-        <v>44</v>
-      </c>
-      <c r="H8">
         <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
         <v>112</v>
@@ -1165,25 +1144,22 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>112</v>
+      <c r="E9">
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="G9">
-        <v>44</v>
-      </c>
-      <c r="H9">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
@@ -1191,25 +1167,22 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>113</v>
+      <c r="E10">
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G10">
-        <v>44</v>
-      </c>
-      <c r="H10">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
@@ -1217,25 +1190,22 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" t="s">
-        <v>114</v>
+      <c r="E11">
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G11">
-        <v>44</v>
-      </c>
-      <c r="H11">
         <v>9.1</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
         <v>115</v>
@@ -1243,25 +1213,22 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
-        <v>115</v>
+      <c r="E12">
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G12">
-        <v>44</v>
-      </c>
-      <c r="H12">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
         <v>116</v>
@@ -1269,25 +1236,22 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
-        <v>116</v>
+      <c r="E13">
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G13">
-        <v>44</v>
-      </c>
-      <c r="H13">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
         <v>117</v>
@@ -1295,25 +1259,22 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" t="s">
-        <v>117</v>
+      <c r="E14">
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G14">
-        <v>44</v>
-      </c>
-      <c r="H14">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
         <v>118</v>
@@ -1321,25 +1282,22 @@
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15" t="s">
-        <v>118</v>
+      <c r="E15">
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G15">
-        <v>44</v>
-      </c>
-      <c r="H15">
         <v>31.8</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
         <v>119</v>
@@ -1347,22 +1305,19 @@
       <c r="D16">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>119</v>
+      <c r="E16">
+        <v>71</v>
       </c>
       <c r="F16">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="G16">
-        <v>132</v>
-      </c>
-      <c r="H16">
         <v>53.8</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>102</v>
@@ -1373,25 +1328,22 @@
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" t="s">
-        <v>120</v>
+      <c r="E17">
+        <v>60</v>
       </c>
       <c r="F17">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="G17">
-        <v>88</v>
-      </c>
-      <c r="H17">
         <v>68.2</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
         <v>121</v>
@@ -1399,25 +1351,22 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
-        <v>121</v>
+      <c r="E18">
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>44</v>
-      </c>
-      <c r="H18">
         <v>70.5</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
         <v>122</v>
@@ -1425,22 +1374,19 @@
       <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19" t="s">
-        <v>122</v>
+      <c r="E19">
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>44</v>
-      </c>
-      <c r="H19">
         <v>79.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>103</v>
@@ -1451,25 +1397,22 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" t="s">
-        <v>123</v>
+      <c r="E20">
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G20">
-        <v>44</v>
-      </c>
-      <c r="H20">
         <v>81.8</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
         <v>124</v>
@@ -1477,51 +1420,45 @@
       <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21" t="s">
-        <v>124</v>
+      <c r="E21">
+        <v>192</v>
       </c>
       <c r="F21">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="G21">
-        <v>220</v>
-      </c>
-      <c r="H21">
         <v>87.3</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
         <v>125</v>
       </c>
       <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>125</v>
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>83</v>
       </c>
       <c r="F22">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G22">
-        <v>44</v>
-      </c>
-      <c r="H22">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
         <v>126</v>
@@ -1529,25 +1466,22 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" t="s">
-        <v>126</v>
+      <c r="E23">
+        <v>42</v>
       </c>
       <c r="F23">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G23">
-        <v>44</v>
-      </c>
-      <c r="H23">
-        <v>97.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
         <v>127</v>
@@ -1555,48 +1489,42 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" t="s">
-        <v>127</v>
+      <c r="E24">
+        <v>43</v>
       </c>
       <c r="F24">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>44</v>
-      </c>
-      <c r="H24">
         <v>97.7</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
         <v>128</v>
       </c>
       <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>128</v>
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>43</v>
       </c>
       <c r="F25">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>88</v>
-      </c>
-      <c r="H25">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
         <v>104</v>
@@ -1607,51 +1535,45 @@
       <c r="D26">
         <v>6</v>
       </c>
-      <c r="E26" t="s">
-        <v>129</v>
+      <c r="E26">
+        <v>261</v>
       </c>
       <c r="F26">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G26">
-        <v>264</v>
-      </c>
-      <c r="H26">
         <v>98.90000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
         <v>130</v>
       </c>
       <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="E27" t="s">
-        <v>130</v>
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>87</v>
       </c>
       <c r="F27">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>176</v>
-      </c>
-      <c r="H27">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
         <v>131</v>
@@ -1659,22 +1581,19 @@
       <c r="D28">
         <v>4</v>
       </c>
-      <c r="E28" t="s">
-        <v>131</v>
+      <c r="E28">
+        <v>175</v>
       </c>
       <c r="F28">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G28">
-        <v>176</v>
-      </c>
-      <c r="H28">
         <v>99.40000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>101</v>
@@ -1683,79 +1602,70 @@
         <v>132</v>
       </c>
       <c r="D29">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>132</v>
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>175</v>
       </c>
       <c r="F29">
-        <v>615</v>
+        <v>176</v>
       </c>
       <c r="G29">
-        <v>616</v>
-      </c>
-      <c r="H29">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
         <v>133</v>
       </c>
       <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>133</v>
+        <v>14</v>
+      </c>
+      <c r="E30">
+        <v>615</v>
       </c>
       <c r="F30">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G30">
-        <v>44</v>
-      </c>
-      <c r="H30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
         <v>134</v>
       </c>
       <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31" t="s">
-        <v>134</v>
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>44</v>
       </c>
       <c r="F31">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G31">
-        <v>88</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
         <v>135</v>
@@ -1763,25 +1673,22 @@
       <c r="D32">
         <v>1</v>
       </c>
-      <c r="E32" t="s">
-        <v>135</v>
+      <c r="E32">
+        <v>44</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>44</v>
-      </c>
-      <c r="H32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
         <v>136</v>
@@ -1789,103 +1696,91 @@
       <c r="D33">
         <v>1</v>
       </c>
-      <c r="E33" t="s">
-        <v>136</v>
+      <c r="E33">
+        <v>44</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>44</v>
-      </c>
-      <c r="H33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
         <v>137</v>
       </c>
       <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34" t="s">
-        <v>137</v>
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>44</v>
       </c>
       <c r="F34">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G34">
-        <v>88</v>
-      </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
         <v>138</v>
       </c>
       <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>138</v>
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>88</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G35">
-        <v>44</v>
-      </c>
-      <c r="H35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
         <v>139</v>
       </c>
       <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>139</v>
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>44</v>
       </c>
       <c r="F36">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G36">
-        <v>88</v>
-      </c>
-      <c r="H36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
         <v>140</v>
@@ -1893,25 +1788,22 @@
       <c r="D37">
         <v>1</v>
       </c>
-      <c r="E37" t="s">
-        <v>140</v>
+      <c r="E37">
+        <v>44</v>
       </c>
       <c r="F37">
         <v>44</v>
       </c>
       <c r="G37">
-        <v>44</v>
-      </c>
-      <c r="H37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
         <v>141</v>
@@ -1919,25 +1811,22 @@
       <c r="D38">
         <v>1</v>
       </c>
-      <c r="E38" t="s">
-        <v>141</v>
+      <c r="E38">
+        <v>44</v>
       </c>
       <c r="F38">
         <v>44</v>
       </c>
       <c r="G38">
-        <v>44</v>
-      </c>
-      <c r="H38">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
         <v>142</v>
@@ -1945,25 +1834,22 @@
       <c r="D39">
         <v>1</v>
       </c>
-      <c r="E39" t="s">
-        <v>142</v>
+      <c r="E39">
+        <v>44</v>
       </c>
       <c r="F39">
         <v>44</v>
       </c>
       <c r="G39">
-        <v>44</v>
-      </c>
-      <c r="H39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
         <v>143</v>
@@ -1971,25 +1857,22 @@
       <c r="D40">
         <v>1</v>
       </c>
-      <c r="E40" t="s">
-        <v>143</v>
+      <c r="E40">
+        <v>44</v>
       </c>
       <c r="F40">
         <v>44</v>
       </c>
       <c r="G40">
-        <v>44</v>
-      </c>
-      <c r="H40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
         <v>144</v>
@@ -1997,25 +1880,22 @@
       <c r="D41">
         <v>1</v>
       </c>
-      <c r="E41" t="s">
-        <v>144</v>
+      <c r="E41">
+        <v>44</v>
       </c>
       <c r="F41">
         <v>44</v>
       </c>
       <c r="G41">
-        <v>44</v>
-      </c>
-      <c r="H41">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
         <v>145</v>
@@ -2023,25 +1903,22 @@
       <c r="D42">
         <v>1</v>
       </c>
-      <c r="E42" t="s">
-        <v>145</v>
+      <c r="E42">
+        <v>44</v>
       </c>
       <c r="F42">
         <v>44</v>
       </c>
       <c r="G42">
-        <v>44</v>
-      </c>
-      <c r="H42">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
         <v>146</v>
@@ -2049,51 +1926,45 @@
       <c r="D43">
         <v>1</v>
       </c>
-      <c r="E43" t="s">
-        <v>146</v>
+      <c r="E43">
+        <v>44</v>
       </c>
       <c r="F43">
         <v>44</v>
       </c>
       <c r="G43">
-        <v>44</v>
-      </c>
-      <c r="H43">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
         <v>147</v>
       </c>
       <c r="D44">
-        <v>3</v>
-      </c>
-      <c r="E44" t="s">
-        <v>147</v>
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>88</v>
       </c>
       <c r="F44">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G44">
-        <v>132</v>
-      </c>
-      <c r="H44">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
         <v>148</v>
@@ -2101,51 +1972,45 @@
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45" t="s">
-        <v>148</v>
+      <c r="E45">
+        <v>44</v>
       </c>
       <c r="F45">
         <v>44</v>
       </c>
       <c r="G45">
-        <v>44</v>
-      </c>
-      <c r="H45">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
         <v>149</v>
       </c>
       <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>149</v>
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>132</v>
       </c>
       <c r="F46">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G46">
-        <v>44</v>
-      </c>
-      <c r="H46">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
         <v>150</v>
@@ -2153,25 +2018,22 @@
       <c r="D47">
         <v>2</v>
       </c>
-      <c r="E47" t="s">
-        <v>150</v>
+      <c r="E47">
+        <v>88</v>
       </c>
       <c r="F47">
         <v>88</v>
       </c>
       <c r="G47">
-        <v>88</v>
-      </c>
-      <c r="H47">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
         <v>151</v>
@@ -2179,25 +2041,22 @@
       <c r="D48">
         <v>2</v>
       </c>
-      <c r="E48" t="s">
-        <v>151</v>
+      <c r="E48">
+        <v>88</v>
       </c>
       <c r="F48">
         <v>88</v>
       </c>
       <c r="G48">
-        <v>88</v>
-      </c>
-      <c r="H48">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
         <v>152</v>
@@ -2205,77 +2064,68 @@
       <c r="D49">
         <v>2</v>
       </c>
-      <c r="E49" t="s">
-        <v>152</v>
+      <c r="E49">
+        <v>88</v>
       </c>
       <c r="F49">
         <v>88</v>
       </c>
       <c r="G49">
-        <v>88</v>
-      </c>
-      <c r="H49">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
         <v>153</v>
       </c>
       <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>153</v>
+        <v>2</v>
+      </c>
+      <c r="E50">
+        <v>88</v>
       </c>
       <c r="F50">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G50">
-        <v>44</v>
-      </c>
-      <c r="H50">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
         <v>154</v>
       </c>
       <c r="D51">
-        <v>2</v>
-      </c>
-      <c r="E51" t="s">
-        <v>154</v>
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G51">
-        <v>88</v>
-      </c>
-      <c r="H51">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
         <v>155</v>
@@ -2283,25 +2133,22 @@
       <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52" t="s">
-        <v>155</v>
+      <c r="E52">
+        <v>44</v>
       </c>
       <c r="F52">
         <v>44</v>
       </c>
       <c r="G52">
-        <v>44</v>
-      </c>
-      <c r="H52">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
         <v>156</v>
@@ -2309,25 +2156,22 @@
       <c r="D53">
         <v>1</v>
       </c>
-      <c r="E53" t="s">
-        <v>156</v>
+      <c r="E53">
+        <v>44</v>
       </c>
       <c r="F53">
         <v>44</v>
       </c>
       <c r="G53">
-        <v>44</v>
-      </c>
-      <c r="H53">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
         <v>157</v>
@@ -2335,77 +2179,68 @@
       <c r="D54">
         <v>1</v>
       </c>
-      <c r="E54" t="s">
-        <v>157</v>
+      <c r="E54">
+        <v>44</v>
       </c>
       <c r="F54">
         <v>44</v>
       </c>
       <c r="G54">
-        <v>44</v>
-      </c>
-      <c r="H54">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
         <v>158</v>
       </c>
       <c r="D55">
-        <v>2</v>
-      </c>
-      <c r="E55" t="s">
-        <v>158</v>
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>44</v>
       </c>
       <c r="F55">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G55">
-        <v>88</v>
-      </c>
-      <c r="H55">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
         <v>159</v>
       </c>
       <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>159</v>
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>88</v>
       </c>
       <c r="F56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G56">
-        <v>44</v>
-      </c>
-      <c r="H56">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
         <v>160</v>
@@ -2413,77 +2248,68 @@
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="E57" t="s">
-        <v>160</v>
+      <c r="E57">
+        <v>44</v>
       </c>
       <c r="F57">
         <v>44</v>
       </c>
       <c r="G57">
-        <v>44</v>
-      </c>
-      <c r="H57">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
         <v>161</v>
       </c>
       <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>161</v>
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>88</v>
       </c>
       <c r="F58">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G58">
-        <v>44</v>
-      </c>
-      <c r="H58">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C59" t="s">
         <v>162</v>
       </c>
       <c r="D59">
-        <v>2</v>
-      </c>
-      <c r="E59" t="s">
-        <v>162</v>
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>44</v>
       </c>
       <c r="F59">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G59">
-        <v>88</v>
-      </c>
-      <c r="H59">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
         <v>163</v>
@@ -2491,25 +2317,22 @@
       <c r="D60">
         <v>2</v>
       </c>
-      <c r="E60" t="s">
-        <v>163</v>
+      <c r="E60">
+        <v>88</v>
       </c>
       <c r="F60">
         <v>88</v>
       </c>
       <c r="G60">
-        <v>88</v>
-      </c>
-      <c r="H60">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
         <v>164</v>
@@ -2517,74 +2340,65 @@
       <c r="D61">
         <v>1</v>
       </c>
-      <c r="E61" t="s">
-        <v>164</v>
+      <c r="E61">
+        <v>44</v>
       </c>
       <c r="F61">
         <v>44</v>
       </c>
       <c r="G61">
-        <v>44</v>
-      </c>
-      <c r="H61">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
         <v>165</v>
       </c>
       <c r="D62">
-        <v>2</v>
-      </c>
-      <c r="E62" t="s">
-        <v>165</v>
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G62">
-        <v>88</v>
-      </c>
-      <c r="H62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
         <v>166</v>
       </c>
       <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>166</v>
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>88</v>
       </c>
       <c r="F63">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G63">
-        <v>44</v>
-      </c>
-      <c r="H63">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" t="s">
         <v>102</v>
@@ -2595,22 +2409,19 @@
       <c r="D64">
         <v>1</v>
       </c>
-      <c r="E64" t="s">
-        <v>167</v>
+      <c r="E64">
+        <v>44</v>
       </c>
       <c r="F64">
         <v>44</v>
       </c>
       <c r="G64">
-        <v>44</v>
-      </c>
-      <c r="H64">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
         <v>102</v>
@@ -2621,25 +2432,22 @@
       <c r="D65">
         <v>1</v>
       </c>
-      <c r="E65" t="s">
-        <v>168</v>
+      <c r="E65">
+        <v>44</v>
       </c>
       <c r="F65">
         <v>44</v>
       </c>
       <c r="G65">
-        <v>44</v>
-      </c>
-      <c r="H65">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C66" t="s">
         <v>169</v>
@@ -2647,25 +2455,22 @@
       <c r="D66">
         <v>1</v>
       </c>
-      <c r="E66" t="s">
-        <v>169</v>
+      <c r="E66">
+        <v>44</v>
       </c>
       <c r="F66">
         <v>44</v>
       </c>
       <c r="G66">
-        <v>44</v>
-      </c>
-      <c r="H66">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C67" t="s">
         <v>170</v>
@@ -2673,25 +2478,22 @@
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="E67" t="s">
-        <v>170</v>
+      <c r="E67">
+        <v>44</v>
       </c>
       <c r="F67">
         <v>44</v>
       </c>
       <c r="G67">
-        <v>44</v>
-      </c>
-      <c r="H67">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C68" t="s">
         <v>171</v>
@@ -2699,25 +2501,22 @@
       <c r="D68">
         <v>2</v>
       </c>
-      <c r="E68" t="s">
-        <v>171</v>
+      <c r="E68">
+        <v>88</v>
       </c>
       <c r="F68">
         <v>88</v>
       </c>
       <c r="G68">
-        <v>88</v>
-      </c>
-      <c r="H68">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C69" t="s">
         <v>172</v>
@@ -2725,25 +2524,22 @@
       <c r="D69">
         <v>1</v>
       </c>
-      <c r="E69" t="s">
-        <v>172</v>
+      <c r="E69">
+        <v>44</v>
       </c>
       <c r="F69">
         <v>44</v>
       </c>
       <c r="G69">
-        <v>44</v>
-      </c>
-      <c r="H69">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C70" t="s">
         <v>173</v>
@@ -2751,48 +2547,42 @@
       <c r="D70">
         <v>1</v>
       </c>
-      <c r="E70" t="s">
-        <v>173</v>
+      <c r="E70">
+        <v>44</v>
       </c>
       <c r="F70">
         <v>44</v>
       </c>
       <c r="G70">
-        <v>44</v>
-      </c>
-      <c r="H70">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
         <v>174</v>
       </c>
       <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>174</v>
+        <v>2</v>
+      </c>
+      <c r="E71">
+        <v>88</v>
       </c>
       <c r="F71">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G71">
-        <v>44</v>
-      </c>
-      <c r="H71">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
         <v>103</v>
@@ -2803,22 +2593,19 @@
       <c r="D72">
         <v>1</v>
       </c>
-      <c r="E72" t="s">
-        <v>175</v>
+      <c r="E72">
+        <v>44</v>
       </c>
       <c r="F72">
         <v>44</v>
       </c>
       <c r="G72">
-        <v>44</v>
-      </c>
-      <c r="H72">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73" t="s">
         <v>103</v>
@@ -2829,22 +2616,19 @@
       <c r="D73">
         <v>1</v>
       </c>
-      <c r="E73" t="s">
-        <v>176</v>
+      <c r="E73">
+        <v>44</v>
       </c>
       <c r="F73">
         <v>44</v>
       </c>
       <c r="G73">
-        <v>44</v>
-      </c>
-      <c r="H73">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B74" t="s">
         <v>103</v>
@@ -2855,22 +2639,19 @@
       <c r="D74">
         <v>1</v>
       </c>
-      <c r="E74" t="s">
-        <v>177</v>
+      <c r="E74">
+        <v>44</v>
       </c>
       <c r="F74">
         <v>44</v>
       </c>
       <c r="G74">
-        <v>44</v>
-      </c>
-      <c r="H74">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" t="s">
         <v>103</v>
@@ -2881,51 +2662,45 @@
       <c r="D75">
         <v>1</v>
       </c>
-      <c r="E75" t="s">
-        <v>178</v>
+      <c r="E75">
+        <v>44</v>
       </c>
       <c r="F75">
         <v>44</v>
       </c>
       <c r="G75">
-        <v>44</v>
-      </c>
-      <c r="H75">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C76" t="s">
         <v>179</v>
       </c>
       <c r="D76">
-        <v>2</v>
-      </c>
-      <c r="E76" t="s">
-        <v>179</v>
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>44</v>
       </c>
       <c r="F76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G76">
-        <v>88</v>
-      </c>
-      <c r="H76">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
         <v>180</v>
@@ -2933,51 +2708,45 @@
       <c r="D77">
         <v>3</v>
       </c>
-      <c r="E77" t="s">
-        <v>180</v>
+      <c r="E77">
+        <v>132</v>
       </c>
       <c r="F77">
         <v>132</v>
       </c>
       <c r="G77">
-        <v>132</v>
-      </c>
-      <c r="H77">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" t="s">
         <v>181</v>
       </c>
       <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>181</v>
+        <v>2</v>
+      </c>
+      <c r="E78">
+        <v>88</v>
       </c>
       <c r="F78">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G78">
-        <v>44</v>
-      </c>
-      <c r="H78">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
         <v>182</v>
@@ -2985,25 +2754,22 @@
       <c r="D79">
         <v>1</v>
       </c>
-      <c r="E79" t="s">
-        <v>182</v>
+      <c r="E79">
+        <v>44</v>
       </c>
       <c r="F79">
         <v>44</v>
       </c>
       <c r="G79">
-        <v>44</v>
-      </c>
-      <c r="H79">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C80" t="s">
         <v>183</v>
@@ -3011,22 +2777,19 @@
       <c r="D80">
         <v>1</v>
       </c>
-      <c r="E80" t="s">
-        <v>183</v>
+      <c r="E80">
+        <v>44</v>
       </c>
       <c r="F80">
         <v>44</v>
       </c>
       <c r="G80">
-        <v>44</v>
-      </c>
-      <c r="H80">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" t="s">
         <v>103</v>
@@ -3037,77 +2800,68 @@
       <c r="D81">
         <v>1</v>
       </c>
-      <c r="E81" t="s">
-        <v>184</v>
+      <c r="E81">
+        <v>44</v>
       </c>
       <c r="F81">
         <v>44</v>
       </c>
       <c r="G81">
-        <v>44</v>
-      </c>
-      <c r="H81">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
         <v>185</v>
       </c>
       <c r="D82">
-        <v>2</v>
-      </c>
-      <c r="E82" t="s">
-        <v>185</v>
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>44</v>
       </c>
       <c r="F82">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G82">
-        <v>88</v>
-      </c>
-      <c r="H82">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
         <v>186</v>
       </c>
       <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83" t="s">
-        <v>186</v>
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>88</v>
       </c>
       <c r="F83">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G83">
-        <v>44</v>
-      </c>
-      <c r="H83">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C84" t="s">
         <v>187</v>
@@ -3115,59 +2869,73 @@
       <c r="D84">
         <v>1</v>
       </c>
-      <c r="E84" t="s">
-        <v>187</v>
+      <c r="E84">
+        <v>44</v>
       </c>
       <c r="F84">
         <v>44</v>
       </c>
       <c r="G84">
-        <v>44</v>
-      </c>
-      <c r="H84">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
         <v>188</v>
       </c>
       <c r="D85">
-        <v>4</v>
-      </c>
-      <c r="E85" t="s">
-        <v>188</v>
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G85">
-        <v>176</v>
-      </c>
-      <c r="H85">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C86" t="s">
         <v>189</v>
       </c>
-      <c r="E86" t="s">
-        <v>189</v>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86">
+        <v>176</v>
       </c>
       <c r="F86">
+        <v>176</v>
+      </c>
+      <c r="G86">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="193">
   <si>
     <t>clues</t>
   </si>
@@ -82,6 +82,9 @@
     <t>SPIMB002241</t>
   </si>
   <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
     <t>BCIMB000092</t>
   </si>
   <si>
@@ -97,171 +100,171 @@
     <t>SPIMB002842</t>
   </si>
   <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
     <t>SPIMB002195</t>
   </si>
   <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
     <t>NTIMB001292</t>
   </si>
   <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
   </si>
   <si>
     <t>SPIMB002101</t>
   </si>
   <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
     <t>TSIMB000876</t>
   </si>
   <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
     <t>TSIMB000910</t>
   </si>
   <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
     <t>VZIMB002366</t>
   </si>
   <si>
@@ -271,24 +274,24 @@
     <t>VZIMB002885</t>
   </si>
   <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
     <t>VZIMB002890</t>
   </si>
   <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
     <t>VZIMB005632</t>
   </si>
   <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
     <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB007616</t>
   </si>
   <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -322,12 +325,12 @@
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
-    <t>TAMAULIPAS</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
@@ -376,6 +379,9 @@
     <t>CENTRO DE SALUD DORACELI</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
     <t>FRACCIONAMIENTO MAR</t>
   </si>
   <si>
@@ -391,171 +397,171 @@
     <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD 6 DE JUNIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
     <t>TEPIC, COL. CUAUHTÉMOC</t>
   </si>
   <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
   </si>
   <si>
     <t>16 DE septiembre</t>
   </si>
   <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. CHULAVISTA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
@@ -565,22 +571,22 @@
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
     <t>CHICHIGAPA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -944,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -975,10 +981,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -998,10 +1004,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1021,10 +1027,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1044,10 +1050,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1067,10 +1073,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1090,10 +1096,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1113,10 +1119,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1136,10 +1142,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1159,10 +1165,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1182,10 +1188,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1205,10 +1211,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1228,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1251,10 +1257,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1274,10 +1280,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1297,10 +1303,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1320,22 +1326,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F17">
         <v>88</v>
       </c>
       <c r="G17">
-        <v>68.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1343,22 +1349,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G18">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1366,22 +1372,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F19">
         <v>44</v>
       </c>
       <c r="G19">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1389,22 +1395,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1412,22 +1418,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F21">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G21">
-        <v>87.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1435,22 +1441,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="F22">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="G22">
-        <v>94.3</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1458,10 +1464,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1481,10 +1487,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1504,10 +1510,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1527,19 +1533,19 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>261</v>
+        <v>87</v>
       </c>
       <c r="F26">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G26">
         <v>98.90000000000001</v>
@@ -1550,19 +1556,19 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F27">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G27">
         <v>98.90000000000001</v>
@@ -1573,10 +1579,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -1596,10 +1602,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -1619,10 +1625,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D30">
         <v>14</v>
@@ -1642,10 +1648,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1665,10 +1671,10 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1688,10 +1694,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1711,10 +1717,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1734,10 +1740,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1757,10 +1763,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1780,10 +1786,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1803,10 +1809,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1826,10 +1832,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1849,10 +1855,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1872,10 +1878,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1895,10 +1901,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1918,10 +1924,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1941,10 +1947,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1964,10 +1970,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1987,10 +1993,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2010,10 +2016,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2033,10 +2039,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2056,10 +2062,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2079,10 +2085,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2102,10 +2108,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2125,10 +2131,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2148,10 +2154,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2171,10 +2177,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2194,10 +2200,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2217,19 +2223,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2240,19 +2246,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2263,10 +2269,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C58" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2286,10 +2292,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2309,10 +2315,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C60" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -2332,10 +2338,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2355,10 +2361,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2378,10 +2384,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2401,10 +2407,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2424,10 +2430,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2447,10 +2453,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2470,10 +2476,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2493,10 +2499,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -2516,10 +2522,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C69" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2539,10 +2545,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2562,10 +2568,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -2585,19 +2591,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C72" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F72">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -2611,7 +2617,7 @@
         <v>103</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2634,7 +2640,7 @@
         <v>103</v>
       </c>
       <c r="C74" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2657,7 +2663,7 @@
         <v>103</v>
       </c>
       <c r="C75" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2680,7 +2686,7 @@
         <v>103</v>
       </c>
       <c r="C76" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2700,19 +2706,19 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C77" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F77">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G77">
         <v>100</v>
@@ -2723,19 +2729,19 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F78">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -2746,19 +2752,19 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C79" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F79">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G79">
         <v>100</v>
@@ -2769,10 +2775,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2795,7 +2801,7 @@
         <v>103</v>
       </c>
       <c r="C81" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2815,10 +2821,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2838,19 +2844,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F83">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -2861,10 +2867,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C84" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -2884,19 +2890,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C85" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -2907,19 +2913,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C86" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F86">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -2930,12 +2936,35 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C87" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="D87">
+        <v>4</v>
       </c>
       <c r="E87">
+        <v>176</v>
+      </c>
+      <c r="F87">
+        <v>176</v>
+      </c>
+      <c r="G87">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" t="s">
+        <v>192</v>
+      </c>
+      <c r="E88">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="197">
   <si>
     <t>clues</t>
   </si>
@@ -55,9 +55,15 @@
     <t>QRIMB001536</t>
   </si>
   <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
     <t>MNIMB001316</t>
   </si>
   <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
     <t>MCIMB002261</t>
   </si>
   <si>
@@ -82,213 +88,213 @@
     <t>SPIMB002241</t>
   </si>
   <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
     <t>TSIMB003401</t>
   </si>
   <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
   </si>
   <si>
     <t>TSIMB000876</t>
   </si>
   <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
   </si>
   <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
     <t>VZIMB005632</t>
   </si>
   <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
     <t>VZIMB007616</t>
   </si>
   <si>
@@ -310,6 +316,9 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
@@ -319,18 +328,15 @@
     <t>CHIAPAS</t>
   </si>
   <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA</t>
+  </si>
+  <si>
     <t>TAMAULIPAS</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
@@ -352,9 +358,15 @@
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD ACALPICAN</t>
   </si>
   <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
     <t>SAN MIGUEL DE LOS JAGUEYES</t>
   </si>
   <si>
@@ -379,211 +391,211 @@
     <t>CENTRO DE SALUD DORACELI</t>
   </si>
   <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. CHULAVISTA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
@@ -950,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -981,10 +993,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1004,10 +1016,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1027,10 +1039,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1050,10 +1062,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1073,10 +1085,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1096,10 +1108,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1119,22 +1131,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>44</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1142,10 +1154,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1165,22 +1177,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>44</v>
       </c>
       <c r="G10">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1188,22 +1200,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1211,22 +1223,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>44</v>
       </c>
       <c r="G12">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1234,22 +1246,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>44</v>
       </c>
       <c r="G13">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1257,22 +1269,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>15.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1280,22 +1292,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>31.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1306,19 +1318,19 @@
         <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G16">
-        <v>53.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1326,22 +1338,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F17">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G17">
-        <v>59.1</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1352,19 +1364,19 @@
         <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F18">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G18">
-        <v>68.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1372,22 +1384,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G19">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1395,22 +1407,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1418,22 +1430,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1441,22 +1453,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F22">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G22">
-        <v>87.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1464,22 +1476,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="F23">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G23">
-        <v>95.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1487,22 +1499,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F24">
         <v>44</v>
       </c>
       <c r="G24">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1510,10 +1522,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1533,22 +1545,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1556,19 +1568,19 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>261</v>
+        <v>87</v>
       </c>
       <c r="F27">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>98.90000000000001</v>
@@ -1579,22 +1591,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="F28">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="G28">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1602,10 +1614,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -1625,22 +1637,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F30">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G30">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1648,22 +1660,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F31">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1671,10 +1683,10 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1694,10 +1706,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1717,10 +1729,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1740,10 +1752,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1763,10 +1775,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1786,10 +1798,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1809,10 +1821,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1832,10 +1844,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1855,10 +1867,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1878,10 +1890,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1901,10 +1913,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1924,10 +1936,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1947,10 +1959,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1970,10 +1982,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1993,10 +2005,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2016,10 +2028,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2039,10 +2051,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2062,10 +2074,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2085,10 +2097,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2108,10 +2120,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2131,10 +2143,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2154,10 +2166,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2177,10 +2189,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2200,10 +2212,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2223,10 +2235,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2246,10 +2258,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2269,19 +2281,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F58">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -2292,10 +2304,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2315,10 +2327,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -2338,10 +2350,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2361,10 +2373,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2384,10 +2396,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2407,10 +2419,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2430,10 +2442,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2453,10 +2465,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2476,10 +2488,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2499,10 +2511,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -2522,10 +2534,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2545,10 +2557,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2568,10 +2580,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -2591,10 +2603,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -2614,19 +2626,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C73" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -2637,10 +2649,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2660,10 +2672,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C75" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2683,10 +2695,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2706,19 +2718,19 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F77">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G77">
         <v>100</v>
@@ -2729,10 +2741,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D78">
         <v>3</v>
@@ -2752,19 +2764,19 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C79" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F79">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G79">
         <v>100</v>
@@ -2775,10 +2787,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2798,10 +2810,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C81" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2821,10 +2833,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2844,10 +2856,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2867,19 +2879,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F84">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -2890,19 +2902,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -2913,19 +2925,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -2936,19 +2948,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F87">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -2959,12 +2971,58 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>192</v>
+        <v>194</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
       </c>
       <c r="E88">
+        <v>44</v>
+      </c>
+      <c r="F88">
+        <v>44</v>
+      </c>
+      <c r="G88">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>176</v>
+      </c>
+      <c r="F89">
+        <v>176</v>
+      </c>
+      <c r="G89">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" t="s">
+        <v>98</v>
+      </c>
+      <c r="C90" t="s">
+        <v>196</v>
+      </c>
+      <c r="E90">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="199">
   <si>
     <t>clues</t>
   </si>
@@ -82,6 +82,9 @@
     <t>NTIMB000131</t>
   </si>
   <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
     <t>VZIMB005475</t>
   </si>
   <si>
@@ -106,198 +109,198 @@
     <t>QRIMB001664</t>
   </si>
   <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
     <t>SPIMB000445</t>
   </si>
   <si>
-    <t>NTIMB001280</t>
+    <t>ZSIMB001641</t>
   </si>
   <si>
     <t>QRIMB001652</t>
   </si>
   <si>
-    <t>ZSIMB001641</t>
+    <t>SPIMB002562</t>
   </si>
   <si>
     <t>SPIMB003146</t>
   </si>
   <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
     <t>VZIMB002395</t>
   </si>
   <si>
     <t>NTIMB002651</t>
   </si>
   <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
     <t>QRIMB000136</t>
   </si>
   <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
     <t>QRIMB000906</t>
   </si>
   <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
   </si>
   <si>
     <t>QRIMB001676</t>
   </si>
   <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
     <t>SPIMB000993</t>
   </si>
   <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
     <t>SPIMB001331</t>
   </si>
   <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
   </si>
   <si>
     <t>SPIMB002830</t>
   </si>
   <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
   </si>
   <si>
     <t>VZIMB002366</t>
   </si>
   <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB005632</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -385,6 +388,9 @@
     <t>EL CARRIZAL</t>
   </si>
   <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
     <t>BARRA DE CHACHALACAS</t>
   </si>
   <si>
@@ -409,196 +415,196 @@
     <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
   </si>
   <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
     <t>AURELIO MANRIQUE</t>
   </si>
   <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+    <t>CENTRO DE SALUD ZACATECAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL UCUM</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
+    <t>CENTRO DE SALUD TERCERAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD VILLA CACTUS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
   </si>
   <si>
     <t>CINCO DE MAYO (EL CIRUELO)</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL POLYUC</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
     <t>PONCIANO ARRIAGA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
     <t>NUEVO TAMPAON</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
     <t>C.S. URBANO ANÁHUAC</t>
   </si>
   <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -962,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -993,10 +999,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1016,10 +1022,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1039,10 +1045,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1062,10 +1068,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1085,10 +1091,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1108,10 +1114,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1131,10 +1137,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1154,10 +1160,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1177,10 +1183,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1200,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1223,10 +1229,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1246,10 +1252,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1269,10 +1275,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1292,10 +1298,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1315,10 +1321,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1338,22 +1344,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>31.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1361,22 +1367,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>53.8</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1387,19 +1393,19 @@
         <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F19">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G19">
-        <v>68.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1407,22 +1413,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F20">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G20">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1430,22 +1436,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1453,22 +1459,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1476,22 +1482,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G23">
-        <v>87.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1499,22 +1505,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G24">
-        <v>95.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1522,22 +1528,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25">
         <v>44</v>
       </c>
       <c r="G25">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1545,10 +1551,10 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1568,22 +1574,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F27">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1591,10 +1597,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1614,22 +1620,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F29">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1637,10 +1643,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -1660,22 +1666,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F31">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G31">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1683,22 +1689,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1706,10 +1712,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1729,19 +1735,19 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F34">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -1752,19 +1758,19 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F35">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -1775,10 +1781,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1798,10 +1804,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1821,10 +1827,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1844,10 +1850,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1867,10 +1873,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1890,10 +1896,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1913,10 +1919,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1936,19 +1942,19 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F43">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -1959,19 +1965,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F44">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -1982,10 +1988,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2005,19 +2011,19 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F46">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -2028,19 +2034,19 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F47">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G47">
         <v>100</v>
@@ -2051,10 +2057,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2074,10 +2080,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2097,10 +2103,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2120,10 +2126,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2143,10 +2149,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2166,10 +2172,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2189,10 +2195,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2212,10 +2218,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2235,19 +2241,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2258,19 +2264,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2281,10 +2287,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2304,10 +2310,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2327,19 +2333,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F60">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2350,19 +2356,19 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F61">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G61">
         <v>100</v>
@@ -2373,10 +2379,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2396,19 +2402,19 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F63">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G63">
         <v>100</v>
@@ -2419,19 +2425,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F64">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G64">
         <v>100</v>
@@ -2442,10 +2448,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2465,10 +2471,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2488,19 +2494,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F67">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -2511,19 +2517,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2534,19 +2540,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -2557,19 +2563,19 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C70" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F70">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G70">
         <v>100</v>
@@ -2580,19 +2586,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C71" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F71">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -2603,19 +2609,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F72">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -2626,10 +2632,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C73" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -2649,10 +2655,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2672,10 +2678,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2695,19 +2701,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -2718,19 +2724,19 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F77">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G77">
         <v>100</v>
@@ -2741,19 +2747,19 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F78">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -2764,10 +2770,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2787,10 +2793,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2810,10 +2816,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C81" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2833,10 +2839,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C82" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2856,10 +2862,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C83" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2879,10 +2885,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C84" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2902,19 +2908,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F85">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -2925,10 +2931,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -2948,10 +2954,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2971,10 +2977,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C88" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -2994,19 +3000,19 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F89">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G89">
         <v>100</v>
@@ -3017,12 +3023,35 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="D90">
+        <v>4</v>
       </c>
       <c r="E90">
+        <v>176</v>
+      </c>
+      <c r="F90">
+        <v>176</v>
+      </c>
+      <c r="G90">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" t="s">
+        <v>198</v>
+      </c>
+      <c r="E91">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -40,33 +40,33 @@
     <t>CCIMB000102</t>
   </si>
   <si>
+    <t>MCIMB003941</t>
+  </si>
+  <si>
+    <t>MCIMB000926</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
     <t>BSIMB000030</t>
   </si>
   <si>
-    <t>MCIMB000926</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>MCIMB003941</t>
-  </si>
-  <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
     <t>NTIMB001345</t>
   </si>
   <si>
@@ -310,21 +310,21 @@
     <t>CAMPECHE</t>
   </si>
   <si>
+    <t>MEXICO</t>
+  </si>
+  <si>
+    <t>QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
-    <t>MEXICO</t>
-  </si>
-  <si>
-    <t>QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>MICHOACAN DE OCAMPO</t>
-  </si>
-  <si>
     <t>NAYARIT</t>
   </si>
   <si>
@@ -346,31 +346,31 @@
     <t>CENTRO DE SALUD CASTAMAY</t>
   </si>
   <si>
+    <t>CIUDAD LAGO</t>
+  </si>
+  <si>
+    <t>COL. MÉXICO NUEVO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. MÉXICO NUEVO</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>CIUDAD LAGO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
   </si>
   <si>
     <t>TEPIC, COL. 2 DE AGOSTO</t>
@@ -1045,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
         <v>111</v>
@@ -1068,7 +1068,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
         <v>112</v>
@@ -1146,13 +1146,13 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>44</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1160,7 +1160,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
         <v>117</v>
@@ -1206,7 +1206,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
         <v>118</v>
@@ -1252,7 +1252,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
         <v>120</v>
@@ -1275,7 +1275,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
         <v>121</v>
@@ -1344,7 +1344,7 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
         <v>124</v>
@@ -1367,7 +1367,7 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
         <v>125</v>
@@ -1528,7 +1528,7 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
         <v>132</v>
@@ -1620,7 +1620,7 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
         <v>136</v>
@@ -1689,7 +1689,7 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
         <v>139</v>
@@ -1735,7 +1735,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
         <v>141</v>
@@ -1758,7 +1758,7 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>142</v>
@@ -1781,7 +1781,7 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>143</v>
@@ -1804,7 +1804,7 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
         <v>144</v>
@@ -1827,7 +1827,7 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
         <v>145</v>
@@ -1850,7 +1850,7 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
         <v>146</v>
@@ -1873,7 +1873,7 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
         <v>147</v>
@@ -1896,7 +1896,7 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
         <v>148</v>
@@ -1919,7 +1919,7 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>149</v>
@@ -1942,7 +1942,7 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
         <v>150</v>
@@ -1965,7 +1965,7 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
         <v>151</v>
@@ -1988,7 +1988,7 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
         <v>152</v>
@@ -2011,7 +2011,7 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
         <v>153</v>
@@ -2034,7 +2034,7 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
         <v>154</v>
@@ -2057,7 +2057,7 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
         <v>155</v>
@@ -2080,7 +2080,7 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
         <v>156</v>
@@ -2126,7 +2126,7 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
         <v>158</v>
@@ -2149,7 +2149,7 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
         <v>159</v>
@@ -2172,7 +2172,7 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
         <v>160</v>
@@ -2195,7 +2195,7 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
         <v>161</v>
@@ -2839,7 +2839,7 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
         <v>189</v>
@@ -2862,7 +2862,7 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
         <v>190</v>
@@ -2885,7 +2885,7 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C84" t="s">
         <v>191</v>
@@ -2908,7 +2908,7 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
         <v>192</v>
@@ -2931,7 +2931,7 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C86" t="s">
         <v>193</v>
@@ -2954,7 +2954,7 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
         <v>194</v>
@@ -2977,7 +2977,7 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
         <v>195</v>
@@ -3000,7 +3000,7 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" t="s">
         <v>196</v>
@@ -3023,7 +3023,7 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C90" t="s">
         <v>197</v>
@@ -3046,7 +3046,7 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C91" t="s">
         <v>198</v>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="203">
   <si>
     <t>clues</t>
   </si>
@@ -97,6 +97,9 @@
     <t>SPIMB000433</t>
   </si>
   <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
     <t>SPIMB000701</t>
   </si>
   <si>
@@ -109,154 +112,175 @@
     <t>QRIMB001664</t>
   </si>
   <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
     <t>NTIMB001280</t>
   </si>
   <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
     <t>ZSIMB001641</t>
   </si>
   <si>
     <t>QRIMB001652</t>
   </si>
   <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
     <t>SPIMB002562</t>
   </si>
   <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
     <t>VZIMB002395</t>
   </si>
   <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
     <t>NTIMB002651</t>
   </si>
   <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
     <t>QRIMB000730</t>
   </si>
   <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
   </si>
   <si>
     <t>QRIMB001635</t>
   </si>
   <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
   </si>
   <si>
     <t>SPIMB000264</t>
   </si>
   <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
   </si>
   <si>
     <t>SPIMB000993</t>
   </si>
   <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
   </si>
   <si>
     <t>SPIMB002760</t>
   </si>
   <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
   </si>
   <si>
     <t>TSIMB003401</t>
@@ -265,42 +289,24 @@
     <t>TSIMB001646</t>
   </si>
   <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
+    <t>VZIMB005632</t>
   </si>
   <si>
     <t>VZIMB002890</t>
   </si>
   <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
     <t>VZIMB002885</t>
   </si>
   <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
     <t>VZIMB007616</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -403,6 +409,9 @@
     <t>PLAN DE IGUALA</t>
   </si>
   <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
     <t>DR. JUAN H. SANCHEZ</t>
   </si>
   <si>
@@ -415,154 +424,175 @@
     <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
   </si>
   <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
     <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
   </si>
   <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD ZACATECAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL UCUM</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD TERCERAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
     <t>CINCO DE MAYO (EL CIRUELO)</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL PUCTÉ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
   </si>
   <si>
     <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
   </si>
   <si>
     <t>COL. JUÁREZ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
   </si>
   <si>
     <t>PONCIANO ARRIAGA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
   </si>
   <si>
     <t>SAN RAFAEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
@@ -571,40 +601,22 @@
     <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>CHICHIGAPA</t>
   </si>
   <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
     <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -968,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -999,10 +1011,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1022,10 +1034,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1045,10 +1057,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1068,10 +1080,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1091,10 +1103,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1114,10 +1126,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1137,10 +1149,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1160,10 +1172,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1183,10 +1195,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1206,10 +1218,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1229,10 +1241,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1252,10 +1264,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1275,10 +1287,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1298,10 +1310,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1321,10 +1333,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1344,10 +1356,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1367,10 +1379,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1390,10 +1402,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1413,10 +1425,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1436,10 +1448,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1462,19 +1474,19 @@
         <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>79.5</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1485,19 +1497,19 @@
         <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1505,22 +1517,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>87.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1528,22 +1540,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G25">
-        <v>95.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1551,22 +1563,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26">
         <v>44</v>
       </c>
       <c r="G26">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1574,10 +1586,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1597,22 +1609,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="F28">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G28">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1620,19 +1632,19 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F29">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G29">
         <v>98.90000000000001</v>
@@ -1643,22 +1655,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F30">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1666,10 +1678,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -1689,22 +1701,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F32">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G32">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1712,22 +1724,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F33">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G33">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1735,19 +1747,19 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F34">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -1758,10 +1770,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1781,10 +1793,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1804,10 +1816,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1827,10 +1839,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1850,10 +1862,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1873,10 +1885,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1896,10 +1908,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1919,10 +1931,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1942,10 +1954,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -1965,19 +1977,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F44">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -1988,19 +2000,19 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F45">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G45">
         <v>100</v>
@@ -2011,10 +2023,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2034,19 +2046,19 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F47">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G47">
         <v>100</v>
@@ -2057,10 +2069,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2080,10 +2092,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2103,19 +2115,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F50">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2126,10 +2138,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2149,10 +2161,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2172,10 +2184,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2195,10 +2207,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2218,19 +2230,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F55">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G55">
         <v>100</v>
@@ -2241,19 +2253,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2264,19 +2276,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2287,10 +2299,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2310,10 +2322,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2333,10 +2345,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2356,19 +2368,19 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F61">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G61">
         <v>100</v>
@@ -2379,19 +2391,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2402,10 +2414,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2425,19 +2437,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F64">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G64">
         <v>100</v>
@@ -2448,19 +2460,19 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F65">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G65">
         <v>100</v>
@@ -2471,19 +2483,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2494,19 +2506,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F67">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -2517,19 +2529,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F68">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2540,19 +2552,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -2563,10 +2575,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C70" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -2586,19 +2598,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F71">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -2609,10 +2621,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C72" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2632,19 +2644,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C73" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -2655,10 +2667,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C74" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2678,10 +2690,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2701,19 +2713,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C76" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -2724,10 +2736,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2747,10 +2759,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2770,10 +2782,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2793,10 +2805,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C80" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2819,7 +2831,7 @@
         <v>107</v>
       </c>
       <c r="C81" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2839,19 +2851,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F82">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -2862,19 +2874,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C83" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F83">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -2885,10 +2897,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C84" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2908,19 +2920,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C85" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -2931,19 +2943,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C86" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -2954,10 +2966,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C87" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2977,19 +2989,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C88" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3000,10 +3012,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3023,19 +3035,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F90">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3046,12 +3058,58 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>44</v>
+      </c>
+      <c r="F91">
+        <v>44</v>
+      </c>
+      <c r="G91">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" t="s">
+        <v>201</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>176</v>
+      </c>
+      <c r="F92">
+        <v>176</v>
+      </c>
+      <c r="G92">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
         <v>98</v>
       </c>
-      <c r="C91" t="s">
-        <v>198</v>
-      </c>
-      <c r="E91">
+      <c r="B93" t="s">
+        <v>100</v>
+      </c>
+      <c r="C93" t="s">
+        <v>202</v>
+      </c>
+      <c r="E93">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="229">
   <si>
     <t>clues</t>
   </si>
@@ -40,138 +40,228 @@
     <t>CCIMB000102</t>
   </si>
   <si>
+    <t>MCIMB000926</t>
+  </si>
+  <si>
     <t>MCIMB003941</t>
   </si>
   <si>
-    <t>MCIMB000926</t>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
   </si>
   <si>
     <t>MCIMB000214</t>
   </si>
   <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
   </si>
   <si>
     <t>QRIMB001524</t>
   </si>
   <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
     <t>QRIMB001483</t>
   </si>
   <si>
-    <t>QRIMB001430</t>
+    <t>QRIMB001635</t>
   </si>
   <si>
     <t>QRIMB000730</t>
   </si>
   <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
     <t>QRIMB000906</t>
   </si>
   <si>
@@ -181,126 +271,75 @@
     <t>QRIMB000993</t>
   </si>
   <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
   </si>
   <si>
     <t>SPIMB002731</t>
   </si>
   <si>
-    <t>SPIMB002545</t>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
   </si>
   <si>
     <t>SPIMB002533</t>
   </si>
   <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
     <t>SPIMB002101</t>
   </si>
   <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
     <t>SPIMB000993</t>
   </si>
   <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
   </si>
   <si>
     <t>TSIMB003401</t>
   </si>
   <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
     <t>VZIMB005632</t>
   </si>
   <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
     <t>VZIMB007505</t>
   </si>
   <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
@@ -325,165 +364,255 @@
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
     <t>NAYARIT</t>
   </si>
   <si>
     <t>CHIAPAS</t>
   </si>
   <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
-    <t>TAMAULIPAS</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CASTAMAY</t>
   </si>
   <si>
+    <t>COL. MÉXICO NUEVO</t>
+  </si>
+  <si>
     <t>CIUDAD LAGO</t>
   </si>
   <si>
-    <t>COL. MÉXICO NUEVO</t>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
   </si>
   <si>
     <t>SAN PEDRO TEPETITLÁN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL EL TESORO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD URBANO TULUM</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL PUCTÉ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
   </si>
   <si>
@@ -493,124 +622,73 @@
     <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD LOS MAGUEYES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
     <t>16 DE septiembre</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
     <t>PONCIANO ARRIAGA</t>
   </si>
   <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
@@ -980,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1011,10 +1089,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1034,10 +1112,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1057,10 +1135,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1080,10 +1158,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1103,10 +1181,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1126,22 +1204,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1149,10 +1227,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1172,10 +1250,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1195,10 +1273,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1218,22 +1296,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1241,22 +1319,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>44</v>
       </c>
       <c r="G12">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1264,10 +1342,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1287,10 +1365,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1310,10 +1388,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1333,10 +1411,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1356,10 +1434,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1379,22 +1457,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>44</v>
       </c>
       <c r="G18">
-        <v>31.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1402,22 +1480,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="F19">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>53.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1425,22 +1503,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G20">
-        <v>68.2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1448,22 +1526,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>70.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1471,22 +1549,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="F22">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G22">
-        <v>72.7</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1494,22 +1572,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>79.5</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1517,22 +1595,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G24">
-        <v>81.8</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1540,22 +1618,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="F25">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>87.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1563,22 +1641,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F26">
         <v>44</v>
       </c>
       <c r="G26">
-        <v>95.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1586,22 +1664,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>97.7</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1609,22 +1687,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>97.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1632,22 +1710,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G29">
-        <v>98.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1655,22 +1733,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="F30">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="G30">
-        <v>98.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1678,22 +1756,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="F31">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G31">
-        <v>99.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1701,22 +1779,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="F32">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>99.40000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1724,22 +1802,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>615</v>
+        <v>43</v>
       </c>
       <c r="F33">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G33">
-        <v>99.8</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1747,22 +1825,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F34">
         <v>44</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1770,22 +1848,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F35">
         <v>44</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1793,22 +1871,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="F36">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1816,22 +1894,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="F37">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1839,22 +1917,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F38">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1862,22 +1940,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F39">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G39">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1885,22 +1963,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F40">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1908,10 +1986,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1931,19 +2009,19 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F42">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -1954,19 +2032,19 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F43">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -1977,19 +2055,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F44">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -2000,19 +2078,19 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F45">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G45">
         <v>100</v>
@@ -2023,19 +2101,19 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F46">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -2046,10 +2124,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2069,19 +2147,19 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F48">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G48">
         <v>100</v>
@@ -2092,19 +2170,19 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F49">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G49">
         <v>100</v>
@@ -2115,19 +2193,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F50">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2138,19 +2216,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2161,10 +2239,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2184,10 +2262,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2207,19 +2285,19 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F54">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G54">
         <v>100</v>
@@ -2230,19 +2308,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F55">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G55">
         <v>100</v>
@@ -2253,10 +2331,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2276,19 +2354,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2299,10 +2377,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2322,10 +2400,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C59" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2345,10 +2423,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2368,10 +2446,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2391,19 +2469,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2414,10 +2492,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2437,10 +2515,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C64" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2460,19 +2538,19 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F65">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G65">
         <v>100</v>
@@ -2483,10 +2561,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -2506,10 +2584,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C67" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2529,19 +2607,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2552,19 +2630,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -2575,19 +2653,19 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F70">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G70">
         <v>100</v>
@@ -2598,19 +2676,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F71">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -2621,10 +2699,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C72" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2644,10 +2722,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2667,19 +2745,19 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C74" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F74">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G74">
         <v>100</v>
@@ -2690,10 +2768,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2713,19 +2791,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -2736,10 +2814,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C77" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2759,19 +2837,19 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C78" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F78">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -2782,19 +2860,19 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F79">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G79">
         <v>100</v>
@@ -2805,10 +2883,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C80" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2828,10 +2906,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C81" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2851,19 +2929,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C82" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F82">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -2874,19 +2952,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C83" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F83">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -2897,10 +2975,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C84" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2920,10 +2998,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C85" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2943,19 +3021,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -2966,10 +3044,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2989,19 +3067,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F88">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3012,10 +3090,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C89" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3035,10 +3113,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3058,10 +3136,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3081,19 +3159,19 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C92" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E92">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F92">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G92">
         <v>100</v>
@@ -3104,12 +3182,311 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>215</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
       </c>
       <c r="E93">
+        <v>44</v>
+      </c>
+      <c r="F93">
+        <v>44</v>
+      </c>
+      <c r="G93">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" t="s">
+        <v>115</v>
+      </c>
+      <c r="C94" t="s">
+        <v>216</v>
+      </c>
+      <c r="D94">
+        <v>3</v>
+      </c>
+      <c r="E94">
+        <v>132</v>
+      </c>
+      <c r="F94">
+        <v>132</v>
+      </c>
+      <c r="G94">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" t="s">
+        <v>217</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+      <c r="E95">
+        <v>88</v>
+      </c>
+      <c r="F95">
+        <v>88</v>
+      </c>
+      <c r="G95">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" t="s">
+        <v>121</v>
+      </c>
+      <c r="C96" t="s">
+        <v>218</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96">
+        <v>88</v>
+      </c>
+      <c r="F96">
+        <v>88</v>
+      </c>
+      <c r="G96">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" t="s">
+        <v>121</v>
+      </c>
+      <c r="C97" t="s">
+        <v>219</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>44</v>
+      </c>
+      <c r="F97">
+        <v>44</v>
+      </c>
+      <c r="G97">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" t="s">
+        <v>115</v>
+      </c>
+      <c r="C98" t="s">
+        <v>220</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>44</v>
+      </c>
+      <c r="F98">
+        <v>44</v>
+      </c>
+      <c r="G98">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" t="s">
+        <v>115</v>
+      </c>
+      <c r="C99" t="s">
+        <v>221</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>44</v>
+      </c>
+      <c r="F99">
+        <v>44</v>
+      </c>
+      <c r="G99">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" t="s">
+        <v>120</v>
+      </c>
+      <c r="C100" t="s">
+        <v>222</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>88</v>
+      </c>
+      <c r="F100">
+        <v>88</v>
+      </c>
+      <c r="G100">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" t="s">
+        <v>115</v>
+      </c>
+      <c r="C101" t="s">
+        <v>223</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>44</v>
+      </c>
+      <c r="F101">
+        <v>44</v>
+      </c>
+      <c r="G101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" t="s">
+        <v>115</v>
+      </c>
+      <c r="C102" t="s">
+        <v>224</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102">
+        <v>88</v>
+      </c>
+      <c r="F102">
+        <v>88</v>
+      </c>
+      <c r="G102">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" t="s">
+        <v>115</v>
+      </c>
+      <c r="C103" t="s">
+        <v>225</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>44</v>
+      </c>
+      <c r="F103">
+        <v>44</v>
+      </c>
+      <c r="G103">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104" t="s">
+        <v>226</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>44</v>
+      </c>
+      <c r="F104">
+        <v>44</v>
+      </c>
+      <c r="G104">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" t="s">
+        <v>227</v>
+      </c>
+      <c r="D105">
+        <v>4</v>
+      </c>
+      <c r="E105">
+        <v>176</v>
+      </c>
+      <c r="F105">
+        <v>176</v>
+      </c>
+      <c r="G105">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" t="s">
+        <v>113</v>
+      </c>
+      <c r="C106" t="s">
+        <v>228</v>
+      </c>
+      <c r="E106">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="241">
   <si>
     <t>clues</t>
   </si>
@@ -49,300 +49,318 @@
     <t>QRIMB001536</t>
   </si>
   <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
     <t>VZIMB007160</t>
   </si>
   <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
     <t>MCIMB002261</t>
   </si>
   <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
   </si>
   <si>
     <t>TSIMB000840</t>
   </si>
   <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
   </si>
   <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
+    <t>VZIMB002366</t>
   </si>
   <si>
     <t>TSIMB001646</t>
   </si>
   <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
+    <t>TSIMB003401</t>
   </si>
   <si>
     <t>VZIMB002890</t>
   </si>
   <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
     <t>VZIMB002885</t>
   </si>
   <si>
-    <t>TSIMB003401</t>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
   </si>
   <si>
     <t>VZIMB005632</t>
   </si>
   <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
     <t>VZIMB007505</t>
   </si>
   <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
     <t>VZIMB007616</t>
   </si>
   <si>
@@ -361,30 +379,30 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>MICHOACAN DE OCAMPO</t>
+    <t>CHIAPAS</t>
   </si>
   <si>
     <t>NAYARIT</t>
   </si>
   <si>
-    <t>CHIAPAS</t>
+    <t>SAN LUIS POTOSI</t>
+  </si>
+  <si>
+    <t>BAJA CALIFORNIA</t>
   </si>
   <si>
     <t>TAMAULIPAS</t>
   </si>
   <si>
-    <t>SAN LUIS POTOSI</t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
@@ -400,298 +418,316 @@
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD URSULO GALVÁN</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
     <t>SAN MIGUEL DE LOS JAGUEYES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. PARAISO</t>
   </si>
   <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
     <t>CHICHIGAPA</t>
   </si>
   <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
   </si>
   <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
@@ -1058,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1089,10 +1125,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1112,10 +1148,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1135,10 +1171,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1158,10 +1194,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1181,22 +1217,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>44</v>
       </c>
       <c r="G6">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1204,10 +1240,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1227,22 +1263,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>44</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1250,22 +1286,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>4.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1273,22 +1309,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>44</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1296,22 +1332,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>6.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1319,22 +1355,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>44</v>
       </c>
       <c r="G12">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1342,22 +1378,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>44</v>
       </c>
       <c r="G13">
-        <v>9.1</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1365,22 +1401,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1388,22 +1424,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>11.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1411,22 +1447,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>15.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1434,22 +1470,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1457,22 +1493,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1480,22 +1516,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F19">
         <v>44</v>
       </c>
       <c r="G19">
-        <v>25</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1503,22 +1539,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F20">
         <v>132</v>
       </c>
       <c r="G20">
-        <v>26.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1526,22 +1562,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F21">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G21">
-        <v>31.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1549,22 +1585,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="F22">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G22">
-        <v>40.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1572,22 +1608,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>47.7</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1595,22 +1631,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>53.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1618,22 +1654,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F25">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>68.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1641,22 +1677,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G26">
-        <v>70.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1664,22 +1700,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>79.5</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1687,22 +1723,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>81.8</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1710,22 +1746,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F29">
         <v>44</v>
       </c>
       <c r="G29">
-        <v>84.09999999999999</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1733,22 +1769,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="F30">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G30">
-        <v>87.3</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1756,22 +1792,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="F31">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G31">
-        <v>87.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1779,22 +1815,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>42</v>
+        <v>261</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G32">
-        <v>95.5</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1802,22 +1838,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="F33">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G33">
-        <v>97.7</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1825,22 +1861,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="F34">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G34">
-        <v>97.7</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1848,22 +1884,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1871,22 +1907,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>87</v>
+        <v>615</v>
       </c>
       <c r="F36">
-        <v>88</v>
+        <v>616</v>
       </c>
       <c r="G36">
-        <v>98.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1894,22 +1930,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>261</v>
+        <v>44</v>
       </c>
       <c r="F37">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G37">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1917,22 +1953,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="F38">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G38">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1940,22 +1976,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="F39">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G39">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1963,22 +1999,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F40">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G40">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1986,19 +2022,19 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F41">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -2009,19 +2045,19 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F42">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -2032,10 +2068,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2055,10 +2091,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2078,10 +2114,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2101,10 +2137,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2124,10 +2160,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2147,10 +2183,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2170,10 +2206,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2193,19 +2229,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F50">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2216,19 +2252,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2239,19 +2275,19 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F52">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2262,19 +2298,19 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C53" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F53">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G53">
         <v>100</v>
@@ -2285,19 +2321,19 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F54">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G54">
         <v>100</v>
@@ -2308,10 +2344,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2331,10 +2367,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2354,19 +2390,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2377,10 +2413,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2400,10 +2436,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2423,10 +2459,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2446,10 +2482,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C61" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2469,10 +2505,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2492,10 +2528,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2515,10 +2551,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2538,10 +2574,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2561,19 +2597,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C66" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2584,19 +2620,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F67">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -2607,10 +2643,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2630,19 +2666,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C69" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -2653,10 +2689,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C70" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2676,19 +2712,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F71">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -2699,10 +2735,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C72" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2722,10 +2758,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2745,10 +2781,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -2768,19 +2804,19 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F75">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G75">
         <v>100</v>
@@ -2791,10 +2827,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -2814,10 +2850,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2837,19 +2873,19 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F78">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -2860,10 +2896,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C79" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -2883,19 +2919,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F80">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -2906,19 +2942,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F81">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -2929,10 +2965,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2952,10 +2988,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2975,10 +3011,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C84" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -2998,10 +3034,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3021,19 +3057,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3044,10 +3080,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C87" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3067,10 +3103,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C88" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3090,10 +3126,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C89" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3113,10 +3149,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3136,10 +3172,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C91" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3159,10 +3195,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C92" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3182,10 +3218,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C93" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3205,19 +3241,19 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F94">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -3228,19 +3264,19 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C95" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F95">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G95">
         <v>100</v>
@@ -3251,10 +3287,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -3274,10 +3310,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3297,19 +3333,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C98" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F98">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3320,19 +3356,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C99" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F99">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3343,19 +3379,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C100" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3366,19 +3402,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C101" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3389,19 +3425,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C102" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3412,10 +3448,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C103" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3435,10 +3471,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C104" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3458,19 +3494,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C105" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="F105">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3481,12 +3517,150 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" t="s">
+        <v>234</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>44</v>
+      </c>
+      <c r="F106">
+        <v>44</v>
+      </c>
+      <c r="G106">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>123</v>
+      </c>
+      <c r="C107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>44</v>
+      </c>
+      <c r="F107">
+        <v>44</v>
+      </c>
+      <c r="G107">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
         <v>113</v>
       </c>
-      <c r="C106" t="s">
-        <v>228</v>
-      </c>
-      <c r="E106">
+      <c r="B108" t="s">
+        <v>123</v>
+      </c>
+      <c r="C108" t="s">
+        <v>236</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>44</v>
+      </c>
+      <c r="F108">
+        <v>44</v>
+      </c>
+      <c r="G108">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" t="s">
+        <v>123</v>
+      </c>
+      <c r="C109" t="s">
+        <v>237</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+      <c r="E109">
+        <v>88</v>
+      </c>
+      <c r="F109">
+        <v>88</v>
+      </c>
+      <c r="G109">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" t="s">
+        <v>123</v>
+      </c>
+      <c r="C110" t="s">
+        <v>238</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>44</v>
+      </c>
+      <c r="F110">
+        <v>44</v>
+      </c>
+      <c r="G110">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" t="s">
+        <v>123</v>
+      </c>
+      <c r="C111" t="s">
+        <v>239</v>
+      </c>
+      <c r="D111">
+        <v>4</v>
+      </c>
+      <c r="E111">
+        <v>176</v>
+      </c>
+      <c r="F111">
+        <v>176</v>
+      </c>
+      <c r="G111">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112" t="s">
+        <v>240</v>
+      </c>
+      <c r="E112">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="257">
   <si>
     <t>clues</t>
   </si>
@@ -43,18 +43,24 @@
     <t>MCIMB000926</t>
   </si>
   <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
     <t>MNIMB001316</t>
   </si>
   <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
     <t>MCIMB003591</t>
   </si>
   <si>
@@ -76,253 +82,274 @@
     <t>MCIMB006835</t>
   </si>
   <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
     <t>NTIMB001345</t>
   </si>
   <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
   </si>
   <si>
     <t>QRIMB000375</t>
   </si>
   <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
     <t>NTIMB002050</t>
   </si>
   <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
   </si>
   <si>
     <t>QRIMB001990</t>
   </si>
   <si>
-    <t>SPIMB000264</t>
+    <t>QRIMB001944</t>
   </si>
   <si>
     <t>QRIMB001710</t>
   </si>
   <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
   </si>
   <si>
     <t>SPIMB002760</t>
   </si>
   <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
+    <t>VZIMB002412</t>
   </si>
   <si>
     <t>VZIMB002400</t>
@@ -331,30 +358,27 @@
     <t>VZIMB002366</t>
   </si>
   <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
     <t>TSIMB001646</t>
   </si>
   <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
+    <t>VZIMB005632</t>
   </si>
   <si>
     <t>VZIMB005656</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
@@ -379,12 +403,12 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
@@ -412,18 +436,24 @@
     <t>COL. MÉXICO NUEVO</t>
   </si>
   <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD ACALPICAN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
     <t>SAN BARTOLOME TLALTELULCO</t>
   </si>
   <si>
@@ -445,253 +475,274 @@
     <t>PALMAR GRANDE</t>
   </si>
   <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
     <t>TEPIC, COL. 2 DE AGOSTO</t>
   </si>
   <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
   </si>
   <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
     <t>EL PORVENIR</t>
   </si>
   <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
   </si>
   <si>
-    <t>COL. JUÁREZ</t>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
   </si>
   <si>
     <t>SAN RAFAEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
@@ -700,28 +751,25 @@
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
@@ -1094,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1125,10 +1173,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1148,10 +1196,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1171,10 +1219,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1194,10 +1242,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1217,22 +1265,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>44</v>
       </c>
       <c r="G6">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1240,22 +1288,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1263,22 +1311,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>44</v>
       </c>
       <c r="G8">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1286,22 +1334,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1309,10 +1357,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1332,22 +1380,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1355,22 +1403,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>44</v>
       </c>
       <c r="G12">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1378,22 +1426,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>44</v>
       </c>
       <c r="G13">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1401,22 +1449,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>18.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1424,22 +1472,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>20.5</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1447,22 +1495,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>25</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1470,22 +1518,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>31.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1493,22 +1541,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>40.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1516,22 +1564,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G19">
-        <v>43.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1539,22 +1587,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G20">
-        <v>53.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1562,22 +1610,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F21">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G21">
-        <v>68.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1585,22 +1633,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>70.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1608,22 +1656,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>72.7</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1631,22 +1679,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G24">
-        <v>79.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1654,22 +1702,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F25">
         <v>44</v>
       </c>
       <c r="G25">
-        <v>81.8</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1677,22 +1725,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="F26">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>87.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1700,22 +1748,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>95.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1723,22 +1771,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>97.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1746,22 +1794,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="F29">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G29">
-        <v>97.7</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1769,22 +1817,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="F30">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>97.7</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1792,22 +1840,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F31">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G31">
-        <v>98.90000000000001</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1815,22 +1863,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>261</v>
+        <v>42</v>
       </c>
       <c r="F32">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>98.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1838,22 +1886,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F33">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G33">
-        <v>99.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1861,22 +1909,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="F34">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G34">
-        <v>99.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1884,22 +1932,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G35">
-        <v>99.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1907,22 +1955,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>615</v>
+        <v>87</v>
       </c>
       <c r="F36">
-        <v>616</v>
+        <v>88</v>
       </c>
       <c r="G36">
-        <v>99.8</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1930,22 +1978,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="F37">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1953,22 +2001,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="F38">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1976,22 +2024,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F39">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G39">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1999,22 +2047,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F40">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2022,22 +2070,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>88</v>
+        <v>615</v>
       </c>
       <c r="F41">
-        <v>88</v>
+        <v>616</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2045,10 +2093,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2068,10 +2116,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2091,10 +2139,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2114,10 +2162,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2137,10 +2185,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2160,10 +2208,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2183,19 +2231,19 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F48">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G48">
         <v>100</v>
@@ -2206,10 +2254,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2229,19 +2277,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C50" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F50">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2252,10 +2300,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2275,10 +2323,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -2298,19 +2346,19 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F53">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G53">
         <v>100</v>
@@ -2321,10 +2369,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2344,10 +2392,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2367,19 +2415,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2390,19 +2438,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F57">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2413,10 +2461,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2436,19 +2484,19 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F59">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G59">
         <v>100</v>
@@ -2459,10 +2507,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2482,10 +2530,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2505,10 +2553,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2528,10 +2576,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2551,10 +2599,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2574,10 +2622,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2597,10 +2645,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C66" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2620,19 +2668,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C67" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F67">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -2643,19 +2691,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C68" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F68">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2666,10 +2714,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C69" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2689,19 +2737,19 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F70">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G70">
         <v>100</v>
@@ -2712,19 +2760,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F71">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -2735,19 +2783,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C72" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F72">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -2758,19 +2806,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -2781,10 +2829,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -2804,19 +2852,19 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C75" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F75">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G75">
         <v>100</v>
@@ -2827,19 +2875,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C76" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -2850,10 +2898,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2873,10 +2921,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C78" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2896,19 +2944,19 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F79">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G79">
         <v>100</v>
@@ -2919,19 +2967,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F80">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -2942,19 +2990,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C81" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F81">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -2965,10 +3013,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2988,10 +3036,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3011,10 +3059,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -3034,19 +3082,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -3057,10 +3105,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C86" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3080,19 +3128,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3103,10 +3151,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3126,10 +3174,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C89" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3149,19 +3197,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C90" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F90">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3172,10 +3220,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C91" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3195,10 +3243,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3218,19 +3266,19 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C93" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F93">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G93">
         <v>100</v>
@@ -3241,19 +3289,19 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C94" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F94">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -3264,10 +3312,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3287,19 +3335,19 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F96">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G96">
         <v>100</v>
@@ -3310,10 +3358,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C97" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3333,19 +3381,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C98" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F98">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3356,19 +3404,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C99" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F99">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3379,10 +3427,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3402,19 +3450,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3425,10 +3473,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C102" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3448,10 +3496,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C103" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3471,10 +3519,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C104" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3494,19 +3542,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F105">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3517,19 +3565,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C106" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F106">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3540,19 +3588,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C107" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F107">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3563,19 +3611,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F108">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3586,19 +3634,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C109" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F109">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -3609,19 +3657,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C110" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F110">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -3632,19 +3680,19 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C111" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E111">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F111">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G111">
         <v>100</v>
@@ -3655,12 +3703,196 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
+        <v>136</v>
+      </c>
+      <c r="C112" t="s">
+        <v>248</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+      <c r="E112">
+        <v>88</v>
+      </c>
+      <c r="F112">
+        <v>88</v>
+      </c>
+      <c r="G112">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>136</v>
+      </c>
+      <c r="C113" t="s">
+        <v>249</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>44</v>
+      </c>
+      <c r="F113">
+        <v>44</v>
+      </c>
+      <c r="G113">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
         <v>119</v>
       </c>
-      <c r="C112" t="s">
-        <v>240</v>
-      </c>
-      <c r="E112">
+      <c r="B114" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" t="s">
+        <v>250</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>44</v>
+      </c>
+      <c r="F114">
+        <v>44</v>
+      </c>
+      <c r="G114">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" t="s">
+        <v>131</v>
+      </c>
+      <c r="C115" t="s">
+        <v>251</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>44</v>
+      </c>
+      <c r="F115">
+        <v>44</v>
+      </c>
+      <c r="G115">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" t="s">
+        <v>131</v>
+      </c>
+      <c r="C116" t="s">
+        <v>252</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>44</v>
+      </c>
+      <c r="F116">
+        <v>44</v>
+      </c>
+      <c r="G116">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117" t="s">
+        <v>253</v>
+      </c>
+      <c r="D117">
+        <v>2</v>
+      </c>
+      <c r="E117">
+        <v>88</v>
+      </c>
+      <c r="F117">
+        <v>88</v>
+      </c>
+      <c r="G117">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" t="s">
+        <v>254</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>44</v>
+      </c>
+      <c r="F118">
+        <v>44</v>
+      </c>
+      <c r="G118">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" t="s">
+        <v>131</v>
+      </c>
+      <c r="C119" t="s">
+        <v>255</v>
+      </c>
+      <c r="D119">
+        <v>4</v>
+      </c>
+      <c r="E119">
+        <v>176</v>
+      </c>
+      <c r="F119">
+        <v>176</v>
+      </c>
+      <c r="G119">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+      <c r="E120">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="268">
   <si>
     <t>clues</t>
   </si>
@@ -49,304 +49,334 @@
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
     <t>MCIMB008730</t>
   </si>
   <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
   </si>
   <si>
     <t>NTIMB000341</t>
   </si>
   <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
   </si>
   <si>
     <t>NTIMB001345</t>
   </si>
   <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
   </si>
   <si>
     <t>MCIMB006654</t>
   </si>
   <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
     <t>TSIMB000292</t>
   </si>
   <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
   </si>
   <si>
     <t>SPIMB002101</t>
   </si>
   <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
     <t>TSIMB001132</t>
   </si>
   <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
     <t>TSIMB000951</t>
   </si>
   <si>
     <t>TSIMB000910</t>
   </si>
   <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
     <t>TSIMB000905</t>
   </si>
   <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
   </si>
   <si>
     <t>VZIMB002412</t>
@@ -358,27 +388,15 @@
     <t>VZIMB002366</t>
   </si>
   <si>
-    <t>VZIMB002885</t>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
   </si>
   <si>
     <t>VZIMB005620</t>
   </si>
   <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
@@ -403,12 +421,12 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
-    <t>MICHOACAN DE OCAMPO</t>
-  </si>
-  <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
@@ -421,12 +439,12 @@
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
-    <t>TAMAULIPAS</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
@@ -442,304 +460,331 @@
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
     <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
   </si>
   <si>
     <t>SANTA MARÍA DE PICACHOS</t>
   </si>
   <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
   </si>
   <si>
     <t>TEPIC, COL. 2 DE AGOSTO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
   </si>
   <si>
     <t>LA LAGUNA</t>
   </si>
   <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
   </si>
   <si>
     <t>16 DE septiembre</t>
   </si>
   <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD EL MOQUETITO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD LAS BLANCAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
@@ -751,25 +796,13 @@
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>LA CONCEPCIÓN</t>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
   </si>
   <si>
     <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
@@ -1142,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1173,10 +1206,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1196,10 +1229,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1219,10 +1252,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1242,10 +1275,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1265,10 +1298,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1288,22 +1321,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1311,10 +1344,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1334,10 +1367,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1357,10 +1390,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1380,10 +1413,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1403,10 +1436,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1426,10 +1459,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1449,10 +1482,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1472,10 +1505,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1495,10 +1528,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1518,22 +1551,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F17">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G17">
-        <v>25</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1541,22 +1574,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F18">
         <v>44</v>
       </c>
       <c r="G18">
-        <v>31.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1564,22 +1597,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>40.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1587,22 +1620,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="F20">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G20">
-        <v>43.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1610,22 +1643,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G21">
-        <v>53.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1633,22 +1666,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="F22">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G22">
-        <v>61.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1656,10 +1689,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1679,22 +1712,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F24">
         <v>88</v>
       </c>
       <c r="G24">
-        <v>68.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1702,22 +1735,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1725,22 +1758,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F26">
         <v>44</v>
       </c>
       <c r="G26">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1748,22 +1781,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1771,10 +1804,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1794,10 +1827,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1817,22 +1850,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G30">
-        <v>93.2</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1840,22 +1873,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1863,22 +1896,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1886,10 +1919,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1909,10 +1942,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1932,22 +1965,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1955,19 +1988,19 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F36">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G36">
         <v>98.90000000000001</v>
@@ -1978,19 +2011,19 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>261</v>
+        <v>87</v>
       </c>
       <c r="F37">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G37">
         <v>98.90000000000001</v>
@@ -2001,22 +2034,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F38">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G38">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2024,22 +2057,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F39">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G39">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2047,10 +2080,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -2070,22 +2103,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D41">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F41">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G41">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2093,22 +2126,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F42">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2116,10 +2149,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2139,19 +2172,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F44">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -2162,10 +2195,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2185,10 +2218,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2208,10 +2241,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2231,19 +2264,19 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F48">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G48">
         <v>100</v>
@@ -2254,10 +2287,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C49" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2277,10 +2310,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2300,10 +2333,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2323,19 +2356,19 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F52">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2346,10 +2379,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2369,10 +2402,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2392,10 +2425,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2418,16 +2451,16 @@
         <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2438,19 +2471,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2461,10 +2494,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C58" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2484,19 +2517,19 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F59">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G59">
         <v>100</v>
@@ -2507,19 +2540,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F60">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2530,10 +2563,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C61" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2553,19 +2586,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2576,10 +2609,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C63" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2599,10 +2632,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2622,10 +2655,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2645,10 +2678,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2668,19 +2701,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F67">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -2691,19 +2724,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C68" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F68">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2714,19 +2747,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -2737,19 +2770,19 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C70" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F70">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G70">
         <v>100</v>
@@ -2760,10 +2793,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -2783,19 +2816,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F72">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -2806,10 +2839,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C73" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -2829,19 +2862,19 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F74">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G74">
         <v>100</v>
@@ -2852,10 +2885,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2875,10 +2908,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2898,10 +2931,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2921,10 +2954,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2944,10 +2977,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2967,10 +3000,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C80" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2990,10 +3023,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C81" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3013,19 +3046,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F82">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -3036,10 +3069,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3059,19 +3092,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C84" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F84">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3082,19 +3115,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C85" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -3108,7 +3141,7 @@
         <v>134</v>
       </c>
       <c r="C86" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3128,10 +3161,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C87" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D87">
         <v>2</v>
@@ -3151,10 +3184,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C88" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3174,10 +3207,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C89" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3197,19 +3230,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C90" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F90">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3220,10 +3253,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C91" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3243,19 +3276,19 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C92" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F92">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G92">
         <v>100</v>
@@ -3269,16 +3302,16 @@
         <v>134</v>
       </c>
       <c r="C93" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F93">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G93">
         <v>100</v>
@@ -3289,10 +3322,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C94" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -3312,10 +3345,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C95" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3335,10 +3368,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C96" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3358,10 +3391,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C97" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3381,10 +3414,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3404,10 +3437,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C99" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3427,10 +3460,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C100" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3450,10 +3483,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C101" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3473,19 +3506,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C102" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F102">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3496,10 +3529,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3519,10 +3552,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C104" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3542,19 +3575,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3565,19 +3598,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C106" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F106">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3588,19 +3621,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C107" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F107">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3611,19 +3644,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C108" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F108">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3634,10 +3667,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C109" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3657,19 +3690,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C110" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F110">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -3680,10 +3713,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C111" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3703,19 +3736,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -3726,10 +3759,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C113" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3749,10 +3782,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3772,10 +3805,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3795,19 +3828,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C116" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E116">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F116">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G116">
         <v>100</v>
@@ -3818,19 +3851,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C117" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E117">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F117">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G117">
         <v>100</v>
@@ -3841,19 +3874,19 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C118" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F118">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G118">
         <v>100</v>
@@ -3864,19 +3897,19 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C119" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D119">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F119">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G119">
         <v>100</v>
@@ -3887,12 +3920,150 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" t="s">
+        <v>261</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>44</v>
+      </c>
+      <c r="F120">
+        <v>44</v>
+      </c>
+      <c r="G120">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" t="s">
+        <v>262</v>
+      </c>
+      <c r="D121">
+        <v>3</v>
+      </c>
+      <c r="E121">
+        <v>132</v>
+      </c>
+      <c r="F121">
+        <v>132</v>
+      </c>
+      <c r="G121">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
         <v>127</v>
       </c>
-      <c r="C120" t="s">
-        <v>256</v>
-      </c>
-      <c r="E120">
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
+        <v>263</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>44</v>
+      </c>
+      <c r="F122">
+        <v>44</v>
+      </c>
+      <c r="G122">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" t="s">
+        <v>264</v>
+      </c>
+      <c r="D123">
+        <v>2</v>
+      </c>
+      <c r="E123">
+        <v>88</v>
+      </c>
+      <c r="F123">
+        <v>88</v>
+      </c>
+      <c r="G123">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" t="s">
+        <v>265</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>44</v>
+      </c>
+      <c r="F124">
+        <v>44</v>
+      </c>
+      <c r="G124">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" t="s">
+        <v>266</v>
+      </c>
+      <c r="D125">
+        <v>4</v>
+      </c>
+      <c r="E125">
+        <v>176</v>
+      </c>
+      <c r="F125">
+        <v>176</v>
+      </c>
+      <c r="G125">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" t="s">
+        <v>133</v>
+      </c>
+      <c r="C126" t="s">
+        <v>267</v>
+      </c>
+      <c r="E126">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="282">
   <si>
     <t>clues</t>
   </si>
@@ -49,21 +49,27 @@
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
     <t>MNIMB001316</t>
   </si>
   <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
     <t>MCIMB003591</t>
   </si>
   <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
     <t>BSIMB000136</t>
   </si>
   <si>
@@ -73,154 +79,340 @@
     <t>CSIMB003651</t>
   </si>
   <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
     <t>VZIMB005661</t>
   </si>
   <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
   </si>
   <si>
     <t>MCIMB001503</t>
   </si>
   <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
   </si>
   <si>
     <t>TSIMB003046</t>
   </si>
   <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>BCIMB000314</t>
@@ -229,183 +421,12 @@
     <t>MCIMB002261</t>
   </si>
   <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -421,10 +442,13 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
+    <t>NAYARIT</t>
   </si>
   <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
@@ -433,18 +457,15 @@
     <t>CHIAPAS</t>
   </si>
   <si>
-    <t>NAYARIT</t>
-  </si>
-  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA</t>
+  </si>
+  <si>
     <t>TAMAULIPAS</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
@@ -460,21 +481,27 @@
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD ACALPICAN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
     <t>SAN BARTOLOME TLALTELULCO</t>
   </si>
   <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
   </si>
   <si>
@@ -484,154 +511,337 @@
     <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
   </si>
   <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
     <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
   </si>
   <si>
     <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
   </si>
   <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>VALLE DE LA TRINIDAD</t>
@@ -640,178 +850,10 @@
     <t>SAN MIGUEL DE LOS JAGUEYES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1175,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1206,10 +1248,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1229,10 +1271,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1252,10 +1294,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1275,10 +1317,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1298,10 +1340,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1321,22 +1363,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1344,10 +1386,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1367,10 +1409,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1390,22 +1432,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>44</v>
       </c>
       <c r="G10">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1413,10 +1455,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1436,10 +1478,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1459,22 +1501,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C13" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>44</v>
       </c>
       <c r="G13">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1482,22 +1524,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1505,22 +1547,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1528,22 +1570,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1551,22 +1593,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G17">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1574,22 +1616,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>44</v>
       </c>
       <c r="G18">
-        <v>25</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1597,22 +1639,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G19">
-        <v>31.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1620,22 +1662,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="F20">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G20">
-        <v>41.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1643,22 +1685,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>43.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1666,22 +1708,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C22" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F22">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G22">
-        <v>53.8</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1689,22 +1731,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F23">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G23">
-        <v>63.6</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1712,22 +1754,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>63.6</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1735,22 +1777,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F25">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G25">
-        <v>68.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1758,22 +1800,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F26">
         <v>44</v>
       </c>
       <c r="G26">
-        <v>70.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1781,22 +1823,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C27" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F27">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>79.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1804,22 +1846,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>81.8</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1827,22 +1869,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="F29">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G29">
-        <v>87.3</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1850,22 +1892,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F30">
         <v>44</v>
       </c>
       <c r="G30">
-        <v>90.90000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1873,22 +1915,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>95.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1896,22 +1938,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G32">
-        <v>97.7</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1919,22 +1961,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>97.7</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1942,22 +1984,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34">
         <v>44</v>
       </c>
       <c r="G34">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1965,22 +2007,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G35">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1988,22 +2030,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="F36">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G36">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2011,22 +2053,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G37">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2034,10 +2076,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2060,19 +2102,19 @@
         <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F39">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G39">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2080,22 +2122,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="F40">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="G40">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2103,22 +2145,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F41">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G41">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2126,22 +2168,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>615</v>
+        <v>131</v>
       </c>
       <c r="F42">
-        <v>616</v>
+        <v>132</v>
       </c>
       <c r="G42">
-        <v>99.8</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2149,22 +2191,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F43">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2172,22 +2214,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="F44">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2195,22 +2237,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="F45">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2218,22 +2260,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F46">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2241,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2264,10 +2306,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2287,19 +2329,19 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F49">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G49">
         <v>100</v>
@@ -2310,10 +2352,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2333,19 +2375,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C51" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2356,10 +2398,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2379,19 +2421,19 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F53">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G53">
         <v>100</v>
@@ -2402,10 +2444,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2425,10 +2467,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2448,10 +2490,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2471,19 +2513,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F57">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2494,10 +2536,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C58" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2517,10 +2559,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C59" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2540,19 +2582,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F60">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2563,19 +2605,19 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F61">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G61">
         <v>100</v>
@@ -2586,19 +2628,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2609,10 +2651,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2632,10 +2674,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2655,10 +2697,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2678,19 +2720,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C66" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2701,19 +2743,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F67">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -2724,19 +2766,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C68" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F68">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2747,19 +2789,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C69" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -2770,19 +2812,19 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C70" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F70">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G70">
         <v>100</v>
@@ -2793,19 +2835,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C71" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F71">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -2816,10 +2858,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2839,19 +2881,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -2862,10 +2904,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2885,10 +2927,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C75" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2908,10 +2950,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2931,10 +2973,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2954,10 +2996,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C78" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2977,10 +3019,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C79" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3000,10 +3042,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C80" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3023,10 +3065,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C81" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3046,10 +3088,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C82" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -3069,10 +3111,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C83" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3092,10 +3134,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C84" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3115,10 +3157,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C85" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3138,10 +3180,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C86" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3161,19 +3203,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C87" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3184,10 +3226,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3207,19 +3249,19 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C89" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F89">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G89">
         <v>100</v>
@@ -3230,10 +3272,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C90" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3253,19 +3295,19 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C91" t="s">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F91">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G91">
         <v>100</v>
@@ -3276,19 +3318,19 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C92" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F92">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G92">
         <v>100</v>
@@ -3299,10 +3341,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C93" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3322,19 +3364,19 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C94" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F94">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -3345,19 +3387,19 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C95" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F95">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G95">
         <v>100</v>
@@ -3368,19 +3410,19 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C96" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F96">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G96">
         <v>100</v>
@@ -3391,19 +3433,19 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C97" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F97">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G97">
         <v>100</v>
@@ -3414,10 +3456,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C98" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3437,19 +3479,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C99" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F99">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3460,19 +3502,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C100" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3483,10 +3525,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C101" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3506,19 +3548,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C102" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3529,10 +3571,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C103" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3552,19 +3594,19 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C104" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F104">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -3575,10 +3617,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C105" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -3598,19 +3640,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C106" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F106">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3621,10 +3663,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C107" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3644,19 +3686,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C108" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3667,10 +3709,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C109" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3690,10 +3732,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C110" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3713,10 +3755,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C111" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3736,10 +3778,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C112" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3759,10 +3801,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C113" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3782,10 +3824,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C114" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3805,19 +3847,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C115" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F115">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -3828,19 +3870,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C116" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E116">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F116">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G116">
         <v>100</v>
@@ -3851,19 +3893,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C117" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F117">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G117">
         <v>100</v>
@@ -3874,19 +3916,19 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F118">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G118">
         <v>100</v>
@@ -3897,19 +3939,19 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C119" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F119">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G119">
         <v>100</v>
@@ -3920,19 +3962,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F120">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -3943,10 +3985,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C121" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -3966,10 +4008,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -3989,19 +4031,19 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C123" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F123">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G123">
         <v>100</v>
@@ -4012,10 +4054,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C124" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4035,19 +4077,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C125" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E125">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="F125">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G125">
         <v>100</v>
@@ -4058,12 +4100,173 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
+        <v>145</v>
+      </c>
+      <c r="C126" t="s">
+        <v>274</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>44</v>
+      </c>
+      <c r="F126">
+        <v>44</v>
+      </c>
+      <c r="G126">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" t="s">
+        <v>145</v>
+      </c>
+      <c r="C127" t="s">
+        <v>275</v>
+      </c>
+      <c r="D127">
+        <v>2</v>
+      </c>
+      <c r="E127">
+        <v>88</v>
+      </c>
+      <c r="F127">
+        <v>88</v>
+      </c>
+      <c r="G127">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
         <v>133</v>
       </c>
-      <c r="C126" t="s">
-        <v>267</v>
-      </c>
-      <c r="E126">
+      <c r="B128" t="s">
+        <v>148</v>
+      </c>
+      <c r="C128" t="s">
+        <v>276</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>44</v>
+      </c>
+      <c r="F128">
+        <v>44</v>
+      </c>
+      <c r="G128">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" t="s">
+        <v>140</v>
+      </c>
+      <c r="C129" t="s">
+        <v>277</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>44</v>
+      </c>
+      <c r="F129">
+        <v>44</v>
+      </c>
+      <c r="G129">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" t="s">
+        <v>145</v>
+      </c>
+      <c r="C130" t="s">
+        <v>278</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>44</v>
+      </c>
+      <c r="F130">
+        <v>44</v>
+      </c>
+      <c r="G130">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131" t="s">
+        <v>279</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>44</v>
+      </c>
+      <c r="F131">
+        <v>44</v>
+      </c>
+      <c r="G131">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" t="s">
+        <v>145</v>
+      </c>
+      <c r="C132" t="s">
+        <v>280</v>
+      </c>
+      <c r="D132">
+        <v>4</v>
+      </c>
+      <c r="E132">
+        <v>176</v>
+      </c>
+      <c r="F132">
+        <v>176</v>
+      </c>
+      <c r="G132">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" t="s">
+        <v>140</v>
+      </c>
+      <c r="C133" t="s">
+        <v>281</v>
+      </c>
+      <c r="E133">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="298">
   <si>
     <t>clues</t>
   </si>
@@ -49,378 +49,402 @@
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
     <t>MCIMB006770</t>
   </si>
   <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
   </si>
   <si>
     <t>MCIMB006736</t>
   </si>
   <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
   </si>
   <si>
     <t>VZIMB005661</t>
   </si>
   <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
   </si>
   <si>
     <t>VZIMB005632</t>
   </si>
   <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
     <t>VZIMB007616</t>
   </si>
   <si>
@@ -481,373 +505,397 @@
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
     <t>DR. JORGE JIMÉNEZ CANTU</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
   </si>
   <si>
     <t>PRADO IXTACALA</t>
   </si>
   <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
   </si>
   <si>
     <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
   </si>
   <si>
     <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
@@ -1217,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1248,10 +1296,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1271,10 +1319,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1294,10 +1342,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1317,10 +1365,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1340,10 +1388,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1363,22 +1411,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1386,10 +1434,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1409,22 +1457,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1432,22 +1480,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1455,10 +1503,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1478,10 +1526,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1501,10 +1549,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1524,10 +1572,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1547,10 +1595,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1570,10 +1618,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1593,22 +1641,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1616,10 +1664,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1639,10 +1687,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -1662,10 +1710,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1685,22 +1733,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F21">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G21">
-        <v>31.8</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1708,10 +1756,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1731,22 +1779,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F23">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G23">
-        <v>36.4</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1754,22 +1802,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G24">
-        <v>43.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1777,22 +1825,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1800,22 +1848,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1823,22 +1871,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1846,22 +1894,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1869,22 +1917,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F29">
         <v>44</v>
       </c>
       <c r="G29">
-        <v>70.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1892,22 +1940,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="F30">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G30">
-        <v>79.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1915,22 +1963,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1938,22 +1986,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>192</v>
+        <v>42</v>
       </c>
       <c r="F32">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>87.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1961,22 +2009,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1984,22 +2032,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F34">
         <v>44</v>
       </c>
       <c r="G34">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2007,10 +2055,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2030,10 +2078,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2053,22 +2101,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F37">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G37">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2076,10 +2124,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2099,19 +2147,19 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F39">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G39">
         <v>98.90000000000001</v>
@@ -2122,19 +2170,19 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>261</v>
+        <v>87</v>
       </c>
       <c r="F40">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G40">
         <v>98.90000000000001</v>
@@ -2145,22 +2193,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F41">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G41">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2168,22 +2216,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F42">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G42">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2191,10 +2239,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -2214,22 +2262,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F44">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G44">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2237,10 +2285,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -2260,22 +2308,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D46">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E46">
-        <v>615</v>
+        <v>263</v>
       </c>
       <c r="F46">
-        <v>616</v>
+        <v>264</v>
       </c>
       <c r="G46">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2283,22 +2331,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F47">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2306,10 +2354,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2329,19 +2377,19 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F49">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G49">
         <v>100</v>
@@ -2352,19 +2400,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F50">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2375,19 +2423,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2398,10 +2446,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C52" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2421,19 +2469,19 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F53">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G53">
         <v>100</v>
@@ -2444,10 +2492,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2467,10 +2515,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2490,19 +2538,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F56">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2513,10 +2561,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2536,10 +2584,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C58" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2559,10 +2607,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2582,19 +2630,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F60">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2605,19 +2653,19 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F61">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G61">
         <v>100</v>
@@ -2628,10 +2676,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C62" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2651,19 +2699,19 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F63">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G63">
         <v>100</v>
@@ -2674,10 +2722,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2697,10 +2745,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2720,19 +2768,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C66" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2743,10 +2791,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2766,19 +2814,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C68" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2789,10 +2837,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C69" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2812,10 +2860,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C70" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2835,10 +2883,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2858,10 +2906,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2881,10 +2929,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2904,10 +2952,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2927,10 +2975,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2950,10 +2998,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2973,19 +3021,19 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C77" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F77">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G77">
         <v>100</v>
@@ -2996,10 +3044,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3019,10 +3067,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3042,10 +3090,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C80" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3065,10 +3113,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3088,19 +3136,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F82">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -3111,10 +3159,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C83" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3134,19 +3182,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C84" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F84">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3157,10 +3205,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C85" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3180,19 +3228,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C86" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F86">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3203,19 +3251,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C87" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3226,19 +3274,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C88" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3249,19 +3297,19 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C89" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F89">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G89">
         <v>100</v>
@@ -3272,10 +3320,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3295,10 +3343,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C91" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -3318,19 +3366,19 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C92" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F92">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G92">
         <v>100</v>
@@ -3341,10 +3389,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C93" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3364,10 +3412,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3387,19 +3435,19 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C95" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F95">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G95">
         <v>100</v>
@@ -3410,19 +3458,19 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C96" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F96">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G96">
         <v>100</v>
@@ -3433,10 +3481,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C97" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -3456,19 +3504,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C98" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F98">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3479,10 +3527,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C99" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -3502,19 +3550,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C100" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3525,10 +3573,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C101" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3548,19 +3596,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C102" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F102">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3571,10 +3619,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C103" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3594,19 +3642,19 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C104" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F104">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -3617,19 +3665,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C105" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3640,10 +3688,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C106" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3663,10 +3711,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C107" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3686,10 +3734,10 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C108" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -3709,10 +3757,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C109" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3732,10 +3780,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C110" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3755,19 +3803,19 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F111">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G111">
         <v>100</v>
@@ -3778,19 +3826,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C112" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -3801,10 +3849,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C113" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3824,10 +3872,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C114" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3847,19 +3895,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C115" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F115">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -3870,19 +3918,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C116" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F116">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G116">
         <v>100</v>
@@ -3893,10 +3941,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C117" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -3916,19 +3964,19 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C118" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F118">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G118">
         <v>100</v>
@@ -3939,19 +3987,19 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C119" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F119">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G119">
         <v>100</v>
@@ -3962,19 +4010,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F120">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -3985,19 +4033,19 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C121" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F121">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G121">
         <v>100</v>
@@ -4008,10 +4056,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C122" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4031,19 +4079,19 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C123" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F123">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G123">
         <v>100</v>
@@ -4054,19 +4102,19 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C124" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E124">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F124">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G124">
         <v>100</v>
@@ -4077,10 +4125,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C125" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D125">
         <v>3</v>
@@ -4100,19 +4148,19 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C126" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E126">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F126">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G126">
         <v>100</v>
@@ -4123,19 +4171,19 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C127" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F127">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G127">
         <v>100</v>
@@ -4149,7 +4197,7 @@
         <v>148</v>
       </c>
       <c r="C128" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4169,10 +4217,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C129" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4192,10 +4240,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4215,10 +4263,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C131" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4238,19 +4286,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C132" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E132">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F132">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4261,12 +4309,196 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
+        <v>153</v>
+      </c>
+      <c r="C133" t="s">
+        <v>289</v>
+      </c>
+      <c r="D133">
+        <v>3</v>
+      </c>
+      <c r="E133">
+        <v>132</v>
+      </c>
+      <c r="F133">
+        <v>132</v>
+      </c>
+      <c r="G133">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" t="s">
+        <v>153</v>
+      </c>
+      <c r="C134" t="s">
+        <v>290</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>44</v>
+      </c>
+      <c r="F134">
+        <v>44</v>
+      </c>
+      <c r="G134">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
         <v>140</v>
       </c>
-      <c r="C133" t="s">
-        <v>281</v>
-      </c>
-      <c r="E133">
+      <c r="B135" t="s">
+        <v>153</v>
+      </c>
+      <c r="C135" t="s">
+        <v>291</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+      <c r="E135">
+        <v>88</v>
+      </c>
+      <c r="F135">
+        <v>88</v>
+      </c>
+      <c r="G135">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" t="s">
+        <v>153</v>
+      </c>
+      <c r="C136" t="s">
+        <v>292</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>44</v>
+      </c>
+      <c r="F136">
+        <v>44</v>
+      </c>
+      <c r="G136">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" t="s">
+        <v>153</v>
+      </c>
+      <c r="C137" t="s">
+        <v>293</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>44</v>
+      </c>
+      <c r="F137">
+        <v>44</v>
+      </c>
+      <c r="G137">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" t="s">
+        <v>153</v>
+      </c>
+      <c r="C138" t="s">
+        <v>294</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>44</v>
+      </c>
+      <c r="F138">
+        <v>44</v>
+      </c>
+      <c r="G138">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" t="s">
+        <v>153</v>
+      </c>
+      <c r="C139" t="s">
+        <v>295</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>44</v>
+      </c>
+      <c r="F139">
+        <v>44</v>
+      </c>
+      <c r="G139">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" t="s">
+        <v>153</v>
+      </c>
+      <c r="C140" t="s">
+        <v>296</v>
+      </c>
+      <c r="D140">
+        <v>4</v>
+      </c>
+      <c r="E140">
+        <v>176</v>
+      </c>
+      <c r="F140">
+        <v>176</v>
+      </c>
+      <c r="G140">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" t="s">
+        <v>148</v>
+      </c>
+      <c r="C141" t="s">
+        <v>297</v>
+      </c>
+      <c r="E141">
         <v>1</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -55,408 +55,408 @@
     <t>BSIMB000030</t>
   </si>
   <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
     <t>MNIMB001316</t>
   </si>
   <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
     <t>MCIMB006724</t>
   </si>
   <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
     <t>MCIMB003842</t>
   </si>
   <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB007942</t>
   </si>
   <si>
     <t>MCIMB007226</t>
   </si>
   <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>VZIMB007942</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
@@ -511,403 +511,403 @@
     <t>CENTRO DE SALUD BENITO JUÁREZ</t>
   </si>
   <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD ACALPICAN</t>
   </si>
   <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
     <t>EL TENAYO</t>
   </si>
   <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
     <t>EL MOLINITO</t>
   </si>
   <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
   <si>
     <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1434,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
         <v>165</v>
@@ -1457,7 +1457,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
         <v>166</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1486,16 +1486,16 @@
         <v>167</v>
       </c>
       <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="E10">
-        <v>14</v>
-      </c>
       <c r="F10">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1503,7 +1503,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
         <v>168</v>
@@ -1526,7 +1526,7 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
         <v>169</v>
@@ -1572,7 +1572,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
         <v>171</v>
@@ -1581,13 +1581,13 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1595,7 +1595,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
         <v>172</v>
@@ -1604,13 +1604,13 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1618,7 +1618,7 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C16" t="s">
         <v>173</v>
@@ -1627,13 +1627,13 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>15.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1641,22 +1641,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
         <v>174</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F17">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G17">
-        <v>15.9</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1670,16 +1670,16 @@
         <v>175</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1693,16 +1693,16 @@
         <v>176</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="F19">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>21.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1710,7 +1710,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
         <v>177</v>
@@ -1719,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1733,22 +1733,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
         <v>178</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G21">
-        <v>29.1</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1756,7 +1756,7 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
         <v>179</v>
@@ -1765,13 +1765,13 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>31.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1779,22 +1779,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
         <v>180</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F23">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G23">
-        <v>43.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1802,22 +1802,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
         <v>181</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1825,22 +1825,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
         <v>182</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1848,22 +1848,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C26" t="s">
         <v>183</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1880,13 +1880,13 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1894,7 +1894,7 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
         <v>185</v>
@@ -1903,13 +1903,13 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1917,22 +1917,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
         <v>186</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="F29">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G29">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1940,22 +1940,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
         <v>187</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G30">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1963,7 +1963,7 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C31" t="s">
         <v>188</v>
@@ -1972,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1986,7 +1986,7 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C32" t="s">
         <v>189</v>
@@ -1995,13 +1995,13 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2009,7 +2009,7 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
         <v>190</v>
@@ -2018,13 +2018,13 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2032,7 +2032,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
         <v>191</v>
@@ -2055,22 +2055,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
         <v>192</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2078,22 +2078,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
         <v>193</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F36">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G36">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2124,19 +2124,19 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
         <v>195</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F38">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G38">
         <v>98.90000000000001</v>
@@ -2147,22 +2147,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
         <v>196</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>261</v>
+        <v>131</v>
       </c>
       <c r="F39">
-        <v>264</v>
+        <v>132</v>
       </c>
       <c r="G39">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2176,16 +2176,16 @@
         <v>197</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="F40">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="G40">
-        <v>98.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2199,16 +2199,16 @@
         <v>198</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F41">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G41">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2216,7 +2216,7 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C42" t="s">
         <v>199</v>
@@ -2239,22 +2239,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
         <v>200</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F43">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G43">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2285,22 +2285,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
         <v>202</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>219</v>
+        <v>615</v>
       </c>
       <c r="F45">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G45">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2314,16 +2314,16 @@
         <v>203</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>263</v>
+        <v>44</v>
       </c>
       <c r="F46">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G46">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2331,22 +2331,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
         <v>204</v>
       </c>
       <c r="D47">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F47">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G47">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2377,7 +2377,7 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
         <v>206</v>
@@ -2406,13 +2406,13 @@
         <v>207</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="F50">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2429,13 +2429,13 @@
         <v>208</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2590,13 +2590,13 @@
         <v>215</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F58">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -2607,7 +2607,7 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C59" t="s">
         <v>216</v>
@@ -2636,13 +2636,13 @@
         <v>217</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F60">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2653,7 +2653,7 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
         <v>218</v>
@@ -2676,19 +2676,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C62" t="s">
         <v>219</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2705,13 +2705,13 @@
         <v>220</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F63">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G63">
         <v>100</v>
@@ -2745,7 +2745,7 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
         <v>222</v>
@@ -2768,19 +2768,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C66" t="s">
         <v>223</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2906,7 +2906,7 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C72" t="s">
         <v>229</v>
@@ -2929,7 +2929,7 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C73" t="s">
         <v>230</v>
@@ -3004,13 +3004,13 @@
         <v>233</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -3027,13 +3027,13 @@
         <v>234</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F77">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G77">
         <v>100</v>
@@ -3136,7 +3136,7 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C82" t="s">
         <v>239</v>
@@ -3165,13 +3165,13 @@
         <v>240</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F83">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -3234,13 +3234,13 @@
         <v>243</v>
       </c>
       <c r="D86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F86">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3257,13 +3257,13 @@
         <v>244</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3274,19 +3274,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C88" t="s">
         <v>245</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F88">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3326,13 +3326,13 @@
         <v>247</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F90">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3372,13 +3372,13 @@
         <v>249</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F92">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G92">
         <v>100</v>
@@ -3418,13 +3418,13 @@
         <v>251</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F94">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -3487,13 +3487,13 @@
         <v>254</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F97">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G97">
         <v>100</v>
@@ -3504,19 +3504,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C98" t="s">
         <v>255</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F98">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3553,7 +3553,7 @@
         <v>155</v>
       </c>
       <c r="C100" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3576,7 +3576,7 @@
         <v>155</v>
       </c>
       <c r="C101" t="s">
-        <v>257</v>
+        <v>192</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3602,13 +3602,13 @@
         <v>258</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3619,19 +3619,19 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C103" t="s">
         <v>259</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F103">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G103">
         <v>100</v>
@@ -3671,13 +3671,13 @@
         <v>261</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3717,13 +3717,13 @@
         <v>263</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F107">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3734,7 +3734,7 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
         <v>264</v>
@@ -3780,7 +3780,7 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
         <v>266</v>
@@ -3832,13 +3832,13 @@
         <v>268</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -3970,13 +3970,13 @@
         <v>274</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F118">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G118">
         <v>100</v>
@@ -3993,13 +3993,13 @@
         <v>275</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F119">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G119">
         <v>100</v>
@@ -4056,19 +4056,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C122" t="s">
         <v>278</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F122">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4148,19 +4148,19 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C126" t="s">
         <v>282</v>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F126">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G126">
         <v>100</v>
@@ -4171,7 +4171,7 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C127" t="s">
         <v>283</v>
@@ -4315,13 +4315,13 @@
         <v>289</v>
       </c>
       <c r="D133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F133">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4361,13 +4361,13 @@
         <v>291</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4407,13 +4407,13 @@
         <v>293</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F137">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4453,13 +4453,13 @@
         <v>295</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4498,8 +4498,17 @@
       <c r="C141" t="s">
         <v>297</v>
       </c>
+      <c r="D141">
+        <v>5</v>
+      </c>
       <c r="E141">
-        <v>1</v>
+        <v>221</v>
+      </c>
+      <c r="F141">
+        <v>220</v>
+      </c>
+      <c r="G141">
+        <v>100.5</v>
       </c>
     </row>
   </sheetData>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="304">
   <si>
     <t>clues</t>
   </si>
@@ -55,405 +55,414 @@
     <t>BSIMB000030</t>
   </si>
   <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
     <t>MCIMB008800</t>
   </si>
   <si>
-    <t>MNIMB001316</t>
+    <t>MCIMB004122</t>
   </si>
   <si>
     <t>MCIMB003591</t>
   </si>
   <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
     <t>NTIMB000522</t>
   </si>
   <si>
     <t>VZIMB002260</t>
   </si>
   <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
     <t>CSIMB003651</t>
   </si>
   <si>
     <t>NTIMB000131</t>
   </si>
   <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
     <t>MCIMB006835</t>
   </si>
   <si>
     <t>MCIMB003760</t>
   </si>
   <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
     <t>MCIMB006724</t>
   </si>
   <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
   </si>
   <si>
     <t>NTIMB000546</t>
   </si>
   <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
   </si>
   <si>
     <t>MCIMB000214</t>
   </si>
   <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
   </si>
   <si>
     <t>VZIMB002412</t>
   </si>
   <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
     <t>VZIMB002366</t>
   </si>
   <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB007942</t>
   </si>
   <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007942</t>
-  </si>
-  <si>
     <t>MCIMB007226</t>
   </si>
   <si>
@@ -511,400 +520,409 @@
     <t>CENTRO DE SALUD BENITO JUÁREZ</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
     <t>SANTA MARÍA OZUMBILLA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
+    <t>LA COLMENA</t>
   </si>
   <si>
     <t>SAN BARTOLOME TLALTELULCO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
     <t>MESA DEL NAYAR</t>
   </si>
   <si>
     <t>CUAUTLAPAN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
   </si>
   <si>
     <t>EL CARRIZAL</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
     <t>PALMAR GRANDE</t>
   </si>
   <si>
     <t>LAS HUERTAS</t>
   </si>
   <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
     <t>EL TENAYO</t>
   </si>
   <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>UZETA</t>
   </si>
   <si>
     <t>SANTA TERESA</t>
   </si>
   <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
   </si>
   <si>
     <t>SAN PEDRO TEPETITLÁN</t>
   </si>
   <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
   <si>
     <t>SAN PABLO DE LAS SALINAS</t>
@@ -1265,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1296,10 +1314,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1319,10 +1337,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1342,10 +1360,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1365,10 +1383,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1388,10 +1406,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1411,10 +1429,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1434,10 +1452,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1460,7 +1478,7 @@
         <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1480,22 +1498,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>44</v>
       </c>
       <c r="G10">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1503,10 +1521,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1529,7 +1547,7 @@
         <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1549,10 +1567,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1572,22 +1590,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1595,22 +1613,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1618,22 +1636,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1641,22 +1659,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G17">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1664,22 +1682,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>22.7</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1687,22 +1705,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G19">
-        <v>25</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1710,22 +1728,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>31.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1733,22 +1751,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>43.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1756,22 +1774,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>47.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1779,22 +1797,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G23">
-        <v>53.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1802,22 +1820,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G24">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1828,19 +1846,19 @@
         <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>68.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1848,22 +1866,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1871,22 +1889,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1894,22 +1912,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C28" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1917,22 +1935,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C29" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F29">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G29">
-        <v>87.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1940,22 +1958,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="F30">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G30">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1963,22 +1981,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>95.5</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1986,22 +2004,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2009,10 +2027,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2032,10 +2050,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2058,19 +2076,19 @@
         <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G35">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2078,10 +2096,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2101,10 +2119,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2124,10 +2142,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -2147,22 +2165,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F39">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G39">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2170,22 +2188,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F40">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G40">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2193,10 +2211,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C41" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2216,10 +2234,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2239,22 +2257,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F43">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G43">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2262,10 +2280,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -2285,22 +2303,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>615</v>
+        <v>219</v>
       </c>
       <c r="F45">
-        <v>616</v>
+        <v>220</v>
       </c>
       <c r="G45">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2308,22 +2326,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F46">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2331,10 +2349,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2354,19 +2372,19 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E48">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F48">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G48">
         <v>100</v>
@@ -2377,10 +2395,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C49" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2400,19 +2418,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="F50">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2423,19 +2441,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2446,19 +2464,19 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E52">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F52">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2469,10 +2487,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C53" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2492,10 +2510,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2515,10 +2533,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2538,10 +2556,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -2561,10 +2579,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2584,19 +2602,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F58">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -2607,10 +2625,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2630,19 +2648,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C60" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F60">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2653,10 +2671,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2676,19 +2694,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2699,10 +2717,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2722,10 +2740,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2745,10 +2763,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2768,19 +2786,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C66" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2791,10 +2809,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2814,10 +2832,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2837,10 +2855,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C69" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2860,10 +2878,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2883,10 +2901,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2906,10 +2924,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2929,10 +2947,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C73" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2952,10 +2970,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2975,10 +2993,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2998,19 +3016,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -3021,10 +3039,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C77" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3044,19 +3062,19 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C78" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F78">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -3067,10 +3085,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C79" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3090,10 +3108,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C80" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3113,19 +3131,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C81" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F81">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -3136,10 +3154,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3159,19 +3177,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F83">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -3182,19 +3200,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F84">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3205,19 +3223,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C85" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -3228,10 +3246,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -3251,19 +3269,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3274,10 +3292,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3297,10 +3315,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3320,10 +3338,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C90" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -3343,19 +3361,19 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F91">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G91">
         <v>100</v>
@@ -3366,10 +3384,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3389,10 +3407,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C93" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3412,19 +3430,19 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C94" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F94">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -3435,10 +3453,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C95" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3458,10 +3476,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C96" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3481,10 +3499,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C97" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3504,10 +3522,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C98" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3527,19 +3545,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C99" t="s">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F99">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3550,19 +3568,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C100" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3573,10 +3591,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C101" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3596,10 +3614,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C102" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3619,19 +3637,19 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C103" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F103">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G103">
         <v>100</v>
@@ -3642,10 +3660,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C104" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3665,10 +3683,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C105" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -3688,10 +3706,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C106" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3711,19 +3729,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C107" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F107">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3734,10 +3752,10 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C108" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -3757,19 +3775,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C109" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F109">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -3780,10 +3798,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3803,10 +3821,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -3826,19 +3844,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C112" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -3849,19 +3867,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C113" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F113">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -3872,19 +3890,19 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C114" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F114">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G114">
         <v>100</v>
@@ -3895,10 +3913,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C115" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3918,10 +3936,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C116" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -3941,10 +3959,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C117" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -3964,10 +3982,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C118" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -3987,19 +4005,19 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C119" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F119">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G119">
         <v>100</v>
@@ -4010,10 +4028,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C120" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4033,10 +4051,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4056,19 +4074,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C122" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F122">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4079,19 +4097,19 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C123" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F123">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G123">
         <v>100</v>
@@ -4102,19 +4120,19 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C124" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F124">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G124">
         <v>100</v>
@@ -4125,19 +4143,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C125" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F125">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G125">
         <v>100</v>
@@ -4148,10 +4166,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C126" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4171,10 +4189,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C127" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4194,10 +4212,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4217,10 +4235,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4240,10 +4258,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C130" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4263,19 +4281,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C131" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F131">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4286,19 +4304,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C132" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F132">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4309,19 +4327,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F133">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4332,19 +4350,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C134" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E134">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F134">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4355,10 +4373,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C135" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4378,10 +4396,10 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C136" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -4401,19 +4419,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C137" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F137">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4424,10 +4442,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C138" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4447,19 +4465,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C139" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4470,19 +4488,19 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C140" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E140">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F140">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G140">
         <v>100</v>
@@ -4493,21 +4511,90 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
+        <v>156</v>
+      </c>
+      <c r="C141" t="s">
+        <v>300</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+      <c r="E141">
+        <v>88</v>
+      </c>
+      <c r="F141">
+        <v>88</v>
+      </c>
+      <c r="G141">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>147</v>
+      </c>
+      <c r="B142" t="s">
+        <v>156</v>
+      </c>
+      <c r="C142" t="s">
+        <v>301</v>
+      </c>
+      <c r="D142">
+        <v>4</v>
+      </c>
+      <c r="E142">
+        <v>176</v>
+      </c>
+      <c r="F142">
+        <v>176</v>
+      </c>
+      <c r="G142">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
         <v>148</v>
       </c>
-      <c r="C141" t="s">
-        <v>297</v>
-      </c>
-      <c r="D141">
+      <c r="B143" t="s">
+        <v>156</v>
+      </c>
+      <c r="C143" t="s">
+        <v>302</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>44</v>
+      </c>
+      <c r="F143">
+        <v>44</v>
+      </c>
+      <c r="G143">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" t="s">
+        <v>151</v>
+      </c>
+      <c r="C144" t="s">
+        <v>303</v>
+      </c>
+      <c r="D144">
         <v>5</v>
       </c>
-      <c r="E141">
+      <c r="E144">
         <v>221</v>
       </c>
-      <c r="F141">
+      <c r="F144">
         <v>220</v>
       </c>
-      <c r="G141">
+      <c r="G144">
         <v>100.5</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -49,18 +49,18 @@
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
     <t>BSIMB000030</t>
   </si>
   <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
     <t>MCIMB004122</t>
   </si>
   <si>
@@ -178,294 +178,294 @@
     <t>MCIMB006770</t>
   </si>
   <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
     <t>MCIMB007243</t>
   </si>
   <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
+    <t>NTIMB000184</t>
   </si>
   <si>
     <t>NTIMB000341</t>
   </si>
   <si>
-    <t>NTIMB000184</t>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
   </si>
   <si>
     <t>NTIMB000546</t>
   </si>
   <si>
-    <t>MCIMB008660</t>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
   </si>
   <si>
     <t>SPIMB001331</t>
   </si>
   <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
   </si>
   <si>
     <t>TSIMB000840</t>
   </si>
   <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
   </si>
   <si>
     <t>TSIMB003046</t>
   </si>
   <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
   </si>
   <si>
     <t>TSIMB003640</t>
   </si>
   <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
   </si>
   <si>
     <t>VZIMB005661</t>
   </si>
   <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB007616</t>
   </si>
   <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
+    <t>VZIMB007604</t>
   </si>
   <si>
     <t>VZIMB007942</t>
   </si>
   <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
-    <t>MICHOACAN DE OCAMPO</t>
-  </si>
-  <si>
     <t>NAYARIT</t>
   </si>
   <si>
@@ -514,18 +514,18 @@
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD BENITO JUÁREZ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
-  </si>
-  <si>
     <t>LA COLMENA</t>
   </si>
   <si>
@@ -643,289 +643,289 @@
     <t>DR. JORGE JIMÉNEZ CANTU</t>
   </si>
   <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
     <t>VALLE DE BRAVO</t>
   </si>
   <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
+    <t>UZETA</t>
   </si>
   <si>
     <t>SANTA MARÍA DE PICACHOS</t>
   </si>
   <si>
-    <t>UZETA</t>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
   </si>
   <si>
     <t>SANTA TERESA</t>
   </si>
   <si>
-    <t>ALBORADA</t>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
   </si>
   <si>
     <t>NUEVO TAMPAON</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. PARAISO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD SOLISEÑO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
   </si>
   <si>
     <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
         <v>166</v>
@@ -1429,7 +1429,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
         <v>167</v>
@@ -1438,13 +1438,13 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1452,7 +1452,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
         <v>168</v>
@@ -1475,7 +1475,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
         <v>169</v>
@@ -1544,7 +1544,7 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" t="s">
         <v>172</v>
@@ -2694,7 +2694,7 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C62" t="s">
         <v>222</v>
@@ -2769,13 +2769,13 @@
         <v>225</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F65">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G65">
         <v>100</v>
@@ -2786,7 +2786,7 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
         <v>226</v>
@@ -2855,7 +2855,7 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
         <v>229</v>
@@ -2953,13 +2953,13 @@
         <v>233</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -3137,13 +3137,13 @@
         <v>241</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F81">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -3522,7 +3522,7 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C98" t="s">
         <v>258</v>
@@ -3896,13 +3896,13 @@
         <v>273</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F114">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G114">
         <v>100</v>
@@ -4080,13 +4080,13 @@
         <v>281</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F122">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4264,13 +4264,13 @@
         <v>289</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F130">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G130">
         <v>100</v>
@@ -4327,19 +4327,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C133" t="s">
         <v>292</v>
       </c>
       <c r="D133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F133">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4540,13 +4540,13 @@
         <v>301</v>
       </c>
       <c r="D142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E142">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F142">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G142">
         <v>100</v>
@@ -4580,22 +4580,22 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C144" t="s">
         <v>303</v>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E144">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="F144">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G144">
-        <v>100.5</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="308">
   <si>
     <t>clues</t>
   </si>
@@ -277,192 +277,198 @@
     <t>NTIMB000546</t>
   </si>
   <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
     <t>QRIMB001524</t>
   </si>
   <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
   </si>
   <si>
     <t>SPIMB001331</t>
   </si>
   <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
   </si>
   <si>
     <t>SPIMB002545</t>
   </si>
   <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
   </si>
   <si>
     <t>TSIMB000840</t>
   </si>
   <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
     <t>TSIMB000864</t>
   </si>
   <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
     <t>TSIMB000951</t>
   </si>
   <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
     <t>TSIMB000910</t>
   </si>
   <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
     <t>TSIMB003046</t>
   </si>
   <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
     <t>TSIMB003401</t>
   </si>
   <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB002412</t>
   </si>
   <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -742,187 +748,193 @@
     <t>SANTA TERESA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL EL TESORO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
   </si>
   <si>
     <t>NUEVO TAMPAON</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
   </si>
   <si>
     <t>CENTRO DE SALUD SAN ANTONIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. PARAISO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD EL MOQUETITO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD EL CONTROL</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1283,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1314,10 +1326,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1337,10 +1349,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1360,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1383,10 +1395,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1406,10 +1418,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1429,10 +1441,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1452,10 +1464,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1475,10 +1487,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1498,10 +1510,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1521,10 +1533,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1544,10 +1556,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1567,10 +1579,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1590,10 +1602,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1613,10 +1625,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1636,10 +1648,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1659,10 +1671,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1682,10 +1694,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1705,10 +1717,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -1728,10 +1740,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1751,10 +1763,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1774,10 +1786,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1797,10 +1809,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1820,10 +1832,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1843,10 +1855,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1866,10 +1878,10 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1889,10 +1901,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1912,10 +1924,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1935,10 +1947,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1958,10 +1970,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1981,10 +1993,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2004,10 +2016,10 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2027,10 +2039,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2050,10 +2062,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2073,10 +2085,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2096,10 +2108,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2119,10 +2131,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2142,10 +2154,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -2165,10 +2177,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2188,10 +2200,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2211,10 +2223,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2234,10 +2246,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2257,10 +2269,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -2280,10 +2292,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -2303,10 +2315,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -2326,10 +2338,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D46">
         <v>14</v>
@@ -2349,10 +2361,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2372,10 +2384,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D48">
         <v>6</v>
@@ -2395,10 +2407,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2418,10 +2430,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2441,10 +2453,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2464,10 +2476,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D52">
         <v>6</v>
@@ -2487,10 +2499,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2510,10 +2522,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2533,10 +2545,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2556,10 +2568,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -2579,10 +2591,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2602,10 +2614,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2625,10 +2637,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2648,10 +2660,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -2671,10 +2683,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2694,10 +2706,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C62" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2717,10 +2729,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C63" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2740,10 +2752,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2763,10 +2775,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D65">
         <v>5</v>
@@ -2786,10 +2798,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2809,10 +2821,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2832,10 +2844,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2855,10 +2867,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2878,10 +2890,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2901,10 +2913,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2924,10 +2936,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2947,10 +2959,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -2970,10 +2982,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C74" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2993,10 +3005,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3016,10 +3028,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3039,10 +3051,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3062,10 +3074,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C78" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3085,10 +3097,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C79" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3108,10 +3120,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C80" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3131,10 +3143,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3154,19 +3166,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F82">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -3177,19 +3189,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C83" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F83">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -3200,19 +3212,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F84">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3223,10 +3235,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C85" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -3246,10 +3258,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C86" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -3269,19 +3281,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C87" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3292,19 +3304,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3315,10 +3327,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C89" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3338,19 +3350,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C90" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F90">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3361,10 +3373,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C91" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3384,10 +3396,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C92" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3407,10 +3419,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C93" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3430,10 +3442,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3453,10 +3465,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3476,10 +3488,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C96" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3499,10 +3511,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C97" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3522,19 +3534,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C98" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F98">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3545,10 +3557,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C99" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3568,10 +3580,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C100" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -3591,10 +3603,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C101" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3614,10 +3626,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C102" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3637,10 +3649,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3660,10 +3672,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3683,19 +3695,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C105" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3706,10 +3718,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C106" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3729,19 +3741,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C107" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F107">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3752,19 +3764,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C108" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F108">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3775,10 +3787,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C109" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -3798,19 +3810,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C110" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F110">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -3821,19 +3833,19 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C111" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F111">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G111">
         <v>100</v>
@@ -3844,19 +3856,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C112" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -3867,19 +3879,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C113" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F113">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -3893,7 +3905,7 @@
         <v>160</v>
       </c>
       <c r="C114" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3916,7 +3928,7 @@
         <v>160</v>
       </c>
       <c r="C115" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3936,10 +3948,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C116" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -3959,10 +3971,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C117" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -3982,10 +3994,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C118" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4005,10 +4017,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C119" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4028,10 +4040,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C120" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4051,10 +4063,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C121" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4074,19 +4086,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C122" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F122">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4097,10 +4109,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C123" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4120,10 +4132,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C124" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4143,19 +4155,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C125" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F125">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G125">
         <v>100</v>
@@ -4166,10 +4178,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C126" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4189,10 +4201,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4212,10 +4224,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C128" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4235,10 +4247,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C129" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4258,10 +4270,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C130" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D130">
         <v>3</v>
@@ -4281,19 +4293,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C131" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F131">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4304,19 +4316,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C132" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F132">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4327,19 +4339,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C133" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F133">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4350,19 +4362,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C134" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F134">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4373,10 +4385,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4396,10 +4408,10 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C136" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -4419,19 +4431,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C137" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F137">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4442,10 +4454,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C138" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4465,19 +4477,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C139" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F139">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4488,10 +4500,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C140" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4511,19 +4523,19 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C141" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F141">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G141">
         <v>100</v>
@@ -4534,19 +4546,19 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C142" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F142">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G142">
         <v>100</v>
@@ -4557,10 +4569,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C143" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4580,21 +4592,67 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C144" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>44</v>
+      </c>
+      <c r="F144">
+        <v>44</v>
+      </c>
+      <c r="G144">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" t="s">
+        <v>158</v>
+      </c>
+      <c r="C145" t="s">
+        <v>306</v>
+      </c>
+      <c r="D145">
+        <v>3</v>
+      </c>
+      <c r="E145">
+        <v>132</v>
+      </c>
+      <c r="F145">
+        <v>132</v>
+      </c>
+      <c r="G145">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" t="s">
+        <v>158</v>
+      </c>
+      <c r="C146" t="s">
+        <v>307</v>
+      </c>
+      <c r="D146">
         <v>4</v>
       </c>
-      <c r="E144">
+      <c r="E146">
         <v>176</v>
       </c>
-      <c r="F144">
+      <c r="F146">
         <v>176</v>
       </c>
-      <c r="G144">
+      <c r="G146">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="312">
   <si>
     <t>clues</t>
   </si>
@@ -82,393 +82,399 @@
     <t>NTIMB000131</t>
   </si>
   <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
     <t>MCIMB006625</t>
   </si>
   <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
     <t>MCIMB006770</t>
   </si>
   <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
     <t>MCIMB008660</t>
   </si>
   <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
   </si>
   <si>
     <t>MCIMB004081</t>
   </si>
   <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
   </si>
   <si>
     <t>TSIMB001132</t>
   </si>
   <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
   </si>
   <si>
     <t>VZIMB002366</t>
   </si>
   <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -553,388 +559,394 @@
     <t>EL CARRIZAL</t>
   </si>
   <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD CARACOLES</t>
   </si>
   <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
     <t>DR. JORGE JIMÉNEZ CANTU</t>
   </si>
   <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
     <t>ALBORADA</t>
   </si>
   <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
   </si>
   <si>
     <t>COL. JORGE JIMÉNEZ CANTU</t>
   </si>
   <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1295,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1326,10 +1338,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1349,10 +1361,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1372,10 +1384,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1395,10 +1407,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1418,10 +1430,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1441,10 +1453,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1464,10 +1476,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1487,10 +1499,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1510,10 +1522,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1533,10 +1545,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1556,10 +1568,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1579,10 +1591,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1602,10 +1614,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1625,10 +1637,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1648,10 +1660,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1671,10 +1683,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1694,22 +1706,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1717,22 +1729,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="F19">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>21.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1740,22 +1752,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1763,22 +1775,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>31.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1786,22 +1798,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>43.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1809,22 +1821,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="F23">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G23">
-        <v>47.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1835,19 +1847,19 @@
         <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1855,22 +1867,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1878,22 +1890,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1901,22 +1913,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F27">
         <v>44</v>
       </c>
       <c r="G27">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1924,22 +1936,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1950,19 +1962,19 @@
         <v>162</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="F29">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G29">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1970,22 +1982,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G30">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1993,22 +2005,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2016,22 +2028,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2039,10 +2051,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2062,10 +2074,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C34" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2085,22 +2097,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2108,10 +2120,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C36" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2131,10 +2143,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2154,10 +2166,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -2177,22 +2189,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C39" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F39">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G39">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2200,22 +2212,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F40">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G40">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2223,10 +2235,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2246,10 +2258,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2269,22 +2281,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F43">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G43">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2292,10 +2304,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -2315,22 +2327,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>219</v>
+        <v>615</v>
       </c>
       <c r="F45">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G45">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2338,22 +2350,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D46">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F46">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G46">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2361,10 +2373,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C47" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2384,10 +2396,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C48" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D48">
         <v>6</v>
@@ -2407,19 +2419,19 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F49">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G49">
         <v>100</v>
@@ -2430,19 +2442,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F50">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2453,10 +2465,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2476,10 +2488,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D52">
         <v>6</v>
@@ -2499,10 +2511,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C53" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2522,10 +2534,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C54" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2545,10 +2557,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C55" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2568,10 +2580,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -2591,10 +2603,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C57" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2614,19 +2626,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C58" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F58">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -2637,10 +2649,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2660,19 +2672,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F60">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2683,10 +2695,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2706,10 +2718,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2729,10 +2741,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2752,10 +2764,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2775,10 +2787,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D65">
         <v>5</v>
@@ -2798,10 +2810,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2821,10 +2833,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C67" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2844,10 +2856,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2867,10 +2879,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2890,10 +2902,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2913,10 +2925,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2936,10 +2948,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2959,10 +2971,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -2982,10 +2994,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3005,10 +3017,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3028,10 +3040,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3051,10 +3063,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3074,10 +3086,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3097,10 +3109,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3120,10 +3132,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3143,10 +3155,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3166,19 +3178,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F82">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -3189,19 +3201,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F83">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -3212,10 +3224,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C84" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -3235,10 +3247,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C85" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -3258,19 +3270,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C86" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3281,19 +3293,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C87" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F87">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3304,19 +3316,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C88" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F88">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3327,10 +3339,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C89" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3350,10 +3362,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C90" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3373,10 +3385,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C91" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3396,10 +3408,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C92" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3419,10 +3431,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C93" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3442,10 +3454,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C94" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3465,10 +3477,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C95" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3488,10 +3500,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C96" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3511,10 +3523,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C97" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3534,19 +3546,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F98">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3557,10 +3569,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C99" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3580,19 +3592,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C100" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3603,19 +3615,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C101" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3626,10 +3638,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C102" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3649,10 +3661,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C103" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3672,10 +3684,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C104" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3695,10 +3707,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C105" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3718,19 +3730,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C106" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F106">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3741,10 +3753,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C107" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -3764,10 +3776,10 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C108" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -3787,19 +3799,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C109" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F109">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -3810,10 +3822,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C110" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -3833,10 +3845,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C111" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3856,10 +3868,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C112" t="s">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3879,19 +3891,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C113" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F113">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -3902,10 +3914,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C114" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3925,10 +3937,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C115" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3948,19 +3960,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C116" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F116">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G116">
         <v>100</v>
@@ -3974,7 +3986,7 @@
         <v>162</v>
       </c>
       <c r="C117" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -3994,10 +4006,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C118" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4017,10 +4029,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C119" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4040,10 +4052,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C120" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4063,10 +4075,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C121" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4086,10 +4098,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C122" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4109,10 +4121,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C123" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4132,10 +4144,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C124" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4155,10 +4167,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C125" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4178,10 +4190,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C126" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4201,10 +4213,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C127" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4224,10 +4236,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C128" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4247,10 +4259,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C129" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4270,19 +4282,19 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C130" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F130">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G130">
         <v>100</v>
@@ -4293,19 +4305,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C131" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4316,19 +4328,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C132" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F132">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4339,10 +4351,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C133" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -4362,10 +4374,10 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C134" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4385,10 +4397,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C135" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4408,19 +4420,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C136" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F136">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4431,10 +4443,10 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D137">
         <v>3</v>
@@ -4454,10 +4466,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C138" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4477,10 +4489,10 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C139" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -4500,10 +4512,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C140" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4523,10 +4535,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C141" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4546,19 +4558,19 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C142" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F142">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G142">
         <v>100</v>
@@ -4569,19 +4581,19 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C143" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F143">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G143">
         <v>100</v>
@@ -4592,10 +4604,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4615,10 +4627,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C145" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D145">
         <v>3</v>
@@ -4638,21 +4650,67 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C146" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>44</v>
+      </c>
+      <c r="F146">
+        <v>44</v>
+      </c>
+      <c r="G146">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>152</v>
+      </c>
+      <c r="B147" t="s">
+        <v>160</v>
+      </c>
+      <c r="C147" t="s">
+        <v>310</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>44</v>
+      </c>
+      <c r="F147">
+        <v>44</v>
+      </c>
+      <c r="G147">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>153</v>
+      </c>
+      <c r="B148" t="s">
+        <v>160</v>
+      </c>
+      <c r="C148" t="s">
+        <v>311</v>
+      </c>
+      <c r="D148">
         <v>4</v>
       </c>
-      <c r="E146">
+      <c r="E148">
         <v>176</v>
       </c>
-      <c r="F146">
+      <c r="F148">
         <v>176</v>
       </c>
-      <c r="G146">
+      <c r="G148">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="335">
   <si>
     <t>clues</t>
   </si>
@@ -43,166 +43,367 @@
     <t>MCIMB000926</t>
   </si>
   <si>
+    <t>MCIMB003941</t>
+  </si>
+  <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MCIMB004122</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>OCIMB002392</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
     <t>MCIMB006741</t>
   </si>
   <si>
-    <t>MCIMB003941</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>MCIMB004122</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
   </si>
   <si>
     <t>MCIMB004110</t>
   </si>
   <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
     <t>MCIMB003883</t>
   </si>
   <si>
-    <t>MCIMB006625</t>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
   </si>
   <si>
     <t>MCIMB006770</t>
   </si>
   <si>
-    <t>MCIMB006753</t>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
   </si>
   <si>
     <t>NTIMB000546</t>
   </si>
   <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
   </si>
   <si>
     <t>MCIMB003813</t>
@@ -211,190 +412,55 @@
     <t>MCIMB002261</t>
   </si>
   <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
   </si>
   <si>
     <t>SPIMB002830</t>
   </si>
   <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
     <t>SPIMB002760</t>
   </si>
   <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
     <t>SPIMB002545</t>
   </si>
   <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
     <t>TSIMB000876</t>
   </si>
   <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
   </si>
   <si>
     <t>TSIMB000910</t>
@@ -403,39 +469,6 @@
     <t>TSIMB000905</t>
   </si>
   <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
     <t>VZIMB002885</t>
   </si>
   <si>
@@ -445,36 +478,36 @@
     <t>VZIMB002400</t>
   </si>
   <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
     <t>VZIMB003264</t>
   </si>
   <si>
-    <t>VZIMB005620</t>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
   </si>
   <si>
     <t>VZIMB005656</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
+    <t>VZIMB007604</t>
   </si>
   <si>
     <t>VZIMB007505</t>
   </si>
   <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
     <t>VZIMB007616</t>
   </si>
   <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -493,18 +526,21 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>SAN LUIS POTOSI</t>
+  </si>
+  <si>
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
     <t>CHIAPAS</t>
   </si>
   <si>
-    <t>SAN LUIS POTOSI</t>
-  </si>
-  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
@@ -520,166 +556,364 @@
     <t>COL. MÉXICO NUEVO</t>
   </si>
   <si>
+    <t>CIUDAD LAGO</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>LA COLMENA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>SAN JUAN YUTA</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
     <t>SANTA CECILIA</t>
   </si>
   <si>
-    <t>CIUDAD LAGO</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>LA COLMENA</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
   </si>
   <si>
     <t>INDEPENDENCIA</t>
   </si>
   <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
     <t>RINCÓN VERDE</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
   </si>
   <si>
     <t>DR. JORGE JIMÉNEZ CANTU</t>
   </si>
   <si>
-    <t>SAN JUANICO</t>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
   </si>
   <si>
     <t>SANTA TERESA</t>
   </si>
   <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
   </si>
   <si>
     <t>SAN RAFAEL CHAMAPA</t>
@@ -688,187 +922,55 @@
     <t>SAN MIGUEL DE LOS JAGUEYES</t>
   </si>
   <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
   </si>
   <si>
     <t>C.S. URBANO ANÁHUAC</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
     <t>SAN RAFAEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD SAN ANTONIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. CHULAVISTA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD EL CONTROL</t>
@@ -877,39 +979,6 @@
     <t>CENTRO DE SALUD LAS BLANCAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
@@ -919,34 +988,34 @@
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
     <t>ORIZABA</t>
   </si>
   <si>
-    <t>LAS BAJADAS</t>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
     <t>VARGAS</t>
   </si>
   <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
+    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
     <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1307,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1338,10 +1407,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1361,10 +1430,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1384,10 +1453,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1407,10 +1476,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1430,10 +1499,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1453,22 +1522,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1476,10 +1545,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1499,22 +1568,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1522,10 +1591,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1545,10 +1614,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1568,10 +1637,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1591,10 +1660,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1614,10 +1683,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1637,22 +1706,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1660,22 +1729,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1683,22 +1752,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1706,22 +1775,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1729,22 +1798,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G19">
-        <v>25</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1752,10 +1821,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1775,10 +1844,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1798,10 +1867,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1821,10 +1890,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1844,10 +1913,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1867,10 +1936,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1890,10 +1959,10 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1913,10 +1982,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1936,10 +2005,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1959,10 +2028,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1982,10 +2051,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2005,10 +2074,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2028,10 +2097,10 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2051,10 +2120,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2074,10 +2143,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2097,22 +2166,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C35" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G35">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2120,22 +2189,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F36">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G36">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2143,22 +2212,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G37">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2166,22 +2235,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="F38">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G38">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2189,22 +2258,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F39">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G39">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2212,22 +2281,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F40">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G40">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2235,22 +2304,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F41">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G41">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2258,22 +2327,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="F42">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="G42">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2281,22 +2350,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="F43">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="G43">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2304,22 +2373,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F44">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G44">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2327,22 +2396,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F45">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G45">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2350,22 +2419,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F46">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2373,22 +2442,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="F47">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2396,22 +2465,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="F48">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2419,22 +2488,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E49">
-        <v>88</v>
+        <v>615</v>
       </c>
       <c r="F49">
-        <v>88</v>
+        <v>616</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2442,19 +2511,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F50">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2465,10 +2534,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2488,19 +2557,19 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F52">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2511,10 +2580,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2534,19 +2603,19 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F54">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G54">
         <v>100</v>
@@ -2557,10 +2626,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2580,19 +2649,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F56">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G56">
         <v>100</v>
@@ -2603,10 +2672,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2626,19 +2695,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F58">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -2649,10 +2718,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2672,10 +2741,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2695,10 +2764,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C61" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2718,10 +2787,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C62" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2741,10 +2810,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2764,19 +2833,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C64" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F64">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G64">
         <v>100</v>
@@ -2787,19 +2856,19 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="F65">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="G65">
         <v>100</v>
@@ -2810,10 +2879,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2833,10 +2902,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2856,19 +2925,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C68" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F68">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2879,10 +2948,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C69" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2902,10 +2971,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C70" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2925,10 +2994,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C71" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2948,10 +3017,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2971,19 +3040,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -2994,10 +3063,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3017,10 +3086,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3040,19 +3109,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F76">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -3063,10 +3132,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3086,19 +3155,19 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F78">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -3109,19 +3178,19 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E79">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F79">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G79">
         <v>100</v>
@@ -3132,10 +3201,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3155,10 +3224,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3178,19 +3247,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C82" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F82">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G82">
         <v>100</v>
@@ -3201,19 +3270,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F83">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G83">
         <v>100</v>
@@ -3224,19 +3293,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C84" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F84">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3247,19 +3316,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C85" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -3270,19 +3339,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C86" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3293,19 +3362,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C87" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F87">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -3316,10 +3385,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C88" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3339,10 +3408,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C89" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3362,10 +3431,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C90" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3385,10 +3454,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C91" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3408,10 +3477,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C92" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3431,10 +3500,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C93" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3454,10 +3523,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C94" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3477,10 +3546,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3500,10 +3569,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C96" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3523,10 +3592,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3546,10 +3615,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C98" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3569,10 +3638,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C99" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3592,19 +3661,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C100" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3615,19 +3684,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C101" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3638,19 +3707,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C102" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F102">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3661,10 +3730,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C103" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3684,19 +3753,19 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C104" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F104">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -3707,19 +3776,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C105" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3730,19 +3799,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C106" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F106">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3753,19 +3822,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C107" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F107">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3776,10 +3845,10 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C108" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -3799,10 +3868,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C109" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3822,19 +3891,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C110" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F110">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -3845,10 +3914,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C111" t="s">
-        <v>201</v>
+        <v>287</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3868,10 +3937,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C112" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3891,19 +3960,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C113" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F113">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -3914,19 +3983,19 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C114" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F114">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G114">
         <v>100</v>
@@ -3937,19 +4006,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C115" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F115">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -3960,19 +4029,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C116" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F116">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G116">
         <v>100</v>
@@ -3983,10 +4052,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C117" t="s">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4006,19 +4075,19 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C118" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F118">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G118">
         <v>100</v>
@@ -4029,10 +4098,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C119" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4052,19 +4121,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C120" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F120">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -4075,10 +4144,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C121" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4098,19 +4167,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C122" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F122">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4121,10 +4190,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C123" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4144,10 +4213,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C124" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4167,19 +4236,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C125" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F125">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G125">
         <v>100</v>
@@ -4190,10 +4259,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C126" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4213,10 +4282,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C127" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4236,10 +4305,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C128" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4259,10 +4328,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C129" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4282,10 +4351,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C130" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4305,19 +4374,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C131" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4328,10 +4397,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C132" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4351,19 +4420,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C133" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F133">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4374,19 +4443,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C134" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F134">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4397,10 +4466,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C135" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4420,19 +4489,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C136" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F136">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4443,19 +4512,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C137" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F137">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4466,19 +4535,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C138" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F138">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G138">
         <v>100</v>
@@ -4489,19 +4558,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C139" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="D139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F139">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4512,10 +4581,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C140" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4535,19 +4604,19 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C141" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F141">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G141">
         <v>100</v>
@@ -4558,10 +4627,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C142" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4581,19 +4650,19 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C143" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F143">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G143">
         <v>100</v>
@@ -4604,10 +4673,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C144" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4627,19 +4696,19 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C145" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F145">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G145">
         <v>100</v>
@@ -4650,10 +4719,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C146" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4673,19 +4742,19 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C147" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E147">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F147">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G147">
         <v>100</v>
@@ -4696,21 +4765,274 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
+        <v>173</v>
+      </c>
+      <c r="C148" t="s">
+        <v>323</v>
+      </c>
+      <c r="D148">
+        <v>3</v>
+      </c>
+      <c r="E148">
+        <v>132</v>
+      </c>
+      <c r="F148">
+        <v>132</v>
+      </c>
+      <c r="G148">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" t="s">
+        <v>173</v>
+      </c>
+      <c r="C149" t="s">
+        <v>324</v>
+      </c>
+      <c r="D149">
+        <v>3</v>
+      </c>
+      <c r="E149">
+        <v>132</v>
+      </c>
+      <c r="F149">
+        <v>132</v>
+      </c>
+      <c r="G149">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>155</v>
+      </c>
+      <c r="B150" t="s">
+        <v>173</v>
+      </c>
+      <c r="C150" t="s">
+        <v>325</v>
+      </c>
+      <c r="D150">
+        <v>3</v>
+      </c>
+      <c r="E150">
+        <v>132</v>
+      </c>
+      <c r="F150">
+        <v>132</v>
+      </c>
+      <c r="G150">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>156</v>
+      </c>
+      <c r="B151" t="s">
+        <v>173</v>
+      </c>
+      <c r="C151" t="s">
+        <v>326</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>44</v>
+      </c>
+      <c r="F151">
+        <v>44</v>
+      </c>
+      <c r="G151">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>157</v>
+      </c>
+      <c r="B152" t="s">
+        <v>173</v>
+      </c>
+      <c r="C152" t="s">
+        <v>327</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>44</v>
+      </c>
+      <c r="F152">
+        <v>44</v>
+      </c>
+      <c r="G152">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>158</v>
+      </c>
+      <c r="B153" t="s">
+        <v>173</v>
+      </c>
+      <c r="C153" t="s">
+        <v>328</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>44</v>
+      </c>
+      <c r="F153">
+        <v>44</v>
+      </c>
+      <c r="G153">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>159</v>
+      </c>
+      <c r="B154" t="s">
+        <v>173</v>
+      </c>
+      <c r="C154" t="s">
+        <v>329</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>44</v>
+      </c>
+      <c r="F154">
+        <v>44</v>
+      </c>
+      <c r="G154">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
         <v>160</v>
       </c>
-      <c r="C148" t="s">
-        <v>311</v>
-      </c>
-      <c r="D148">
+      <c r="B155" t="s">
+        <v>173</v>
+      </c>
+      <c r="C155" t="s">
+        <v>330</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>44</v>
+      </c>
+      <c r="F155">
+        <v>44</v>
+      </c>
+      <c r="G155">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B156" t="s">
+        <v>173</v>
+      </c>
+      <c r="C156" t="s">
+        <v>331</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>44</v>
+      </c>
+      <c r="F156">
+        <v>44</v>
+      </c>
+      <c r="G156">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" t="s">
+        <v>173</v>
+      </c>
+      <c r="C157" t="s">
+        <v>332</v>
+      </c>
+      <c r="D157">
+        <v>2</v>
+      </c>
+      <c r="E157">
+        <v>88</v>
+      </c>
+      <c r="F157">
+        <v>88</v>
+      </c>
+      <c r="G157">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>163</v>
+      </c>
+      <c r="B158" t="s">
+        <v>173</v>
+      </c>
+      <c r="C158" t="s">
+        <v>333</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>44</v>
+      </c>
+      <c r="F158">
+        <v>44</v>
+      </c>
+      <c r="G158">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" t="s">
+        <v>173</v>
+      </c>
+      <c r="C159" t="s">
+        <v>334</v>
+      </c>
+      <c r="D159">
         <v>4</v>
       </c>
-      <c r="E148">
+      <c r="E159">
         <v>176</v>
       </c>
-      <c r="F148">
+      <c r="F159">
         <v>176</v>
       </c>
-      <c r="G148">
+      <c r="G159">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="351">
   <si>
     <t>clues</t>
   </si>
@@ -49,6 +49,9 @@
     <t>MCIMB008800</t>
   </si>
   <si>
+    <t>QRIMB001775</t>
+  </si>
+  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
@@ -61,436 +64,460 @@
     <t>MCIMB004122</t>
   </si>
   <si>
+    <t>OCIMB002392</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>VZIMB007855</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
     <t>SPIMB002340</t>
   </si>
   <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>OCIMB002392</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
     <t>SPIMB002195</t>
   </si>
   <si>
     <t>SPIMB002101</t>
   </si>
   <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
     <t>SPIMB001331</t>
   </si>
   <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
   </si>
   <si>
     <t>TSIMB000864</t>
   </si>
   <si>
-    <t>TSIMB000840</t>
+    <t>TSIMB000876</t>
   </si>
   <si>
     <t>TSIMB000292</t>
   </si>
   <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB005661</t>
@@ -499,15 +526,12 @@
     <t>VZIMB005656</t>
   </si>
   <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -526,21 +550,21 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
+    <t>CHIAPAS</t>
+  </si>
+  <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
-    <t>NAYARIT</t>
-  </si>
-  <si>
-    <t>OAXACA</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>CHIAPAS</t>
-  </si>
-  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
@@ -562,6 +586,9 @@
     <t>SANTA MARÍA OZUMBILLA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
@@ -574,433 +601,457 @@
     <t>LA COLMENA</t>
   </si>
   <si>
+    <t>SAN JUAN YUTA</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD FRANCISCO VILLA</t>
   </si>
   <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>SAN JUAN YUTA</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD 6 DE JUNIO</t>
   </si>
   <si>
     <t>16 DE septiembre</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
     <t>NUEVO TAMPAON</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
   </si>
   <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>GRANJA RÍO MEDIO</t>
@@ -1009,13 +1060,10 @@
     <t>VARGAS</t>
   </si>
   <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1376,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1407,10 +1455,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1430,10 +1478,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1453,10 +1501,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1476,10 +1524,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1499,10 +1547,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1522,22 +1570,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1545,10 +1593,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1568,22 +1616,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1591,10 +1639,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1614,10 +1662,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1637,10 +1685,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1660,10 +1708,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1683,22 +1731,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1706,22 +1754,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1729,22 +1777,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1752,22 +1800,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>15.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1775,22 +1823,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1798,22 +1846,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>21.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1821,22 +1869,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>31.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1844,10 +1892,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1867,10 +1915,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1890,10 +1938,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1913,10 +1961,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1936,10 +1984,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1959,10 +2007,10 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1982,10 +2030,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2005,10 +2053,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C28" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2028,10 +2076,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -2051,10 +2099,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C30" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2074,10 +2122,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C31" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2097,22 +2145,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>43</v>
+        <v>343</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G32">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2120,10 +2168,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C33" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2143,10 +2191,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2166,10 +2214,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2189,10 +2237,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C36" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2212,10 +2260,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2235,22 +2283,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>43</v>
+        <v>261</v>
       </c>
       <c r="F38">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G38">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2258,10 +2306,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2281,10 +2329,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2304,10 +2352,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2327,22 +2375,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>261</v>
+        <v>131</v>
       </c>
       <c r="F42">
-        <v>264</v>
+        <v>132</v>
       </c>
       <c r="G42">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2350,22 +2398,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C43" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F43">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G43">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2373,10 +2421,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -2396,10 +2444,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2419,22 +2467,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F46">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G46">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2442,10 +2490,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C47" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D47">
         <v>5</v>
@@ -2465,22 +2513,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E48">
-        <v>219</v>
+        <v>615</v>
       </c>
       <c r="F48">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G48">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2488,22 +2536,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F49">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G49">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2511,19 +2559,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F50">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -2534,19 +2582,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C51" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -2557,19 +2605,19 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F52">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2580,10 +2628,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2603,19 +2651,19 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F54">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G54">
         <v>100</v>
@@ -2626,10 +2674,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C55" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2649,10 +2697,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C56" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2672,10 +2720,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2695,10 +2743,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2718,19 +2766,19 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F59">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G59">
         <v>100</v>
@@ -2741,19 +2789,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F60">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2764,10 +2812,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C61" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2787,19 +2835,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E62">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F62">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2810,19 +2858,19 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E63">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F63">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G63">
         <v>100</v>
@@ -2833,19 +2881,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F64">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G64">
         <v>100</v>
@@ -2856,19 +2904,19 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C65" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F65">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G65">
         <v>100</v>
@@ -2879,19 +2927,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C66" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F66">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2902,10 +2950,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2925,19 +2973,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C68" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F68">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G68">
         <v>100</v>
@@ -2948,10 +2996,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C69" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2971,10 +3019,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C70" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2994,10 +3042,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C71" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3017,10 +3065,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C72" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3040,19 +3088,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C73" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F73">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -3063,10 +3111,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C74" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3086,10 +3134,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C75" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3109,19 +3157,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C76" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F76">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G76">
         <v>100</v>
@@ -3132,10 +3180,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C77" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3155,10 +3203,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C78" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3178,19 +3226,19 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F79">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G79">
         <v>100</v>
@@ -3201,10 +3249,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C80" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3224,10 +3272,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C81" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3247,10 +3295,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3270,10 +3318,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3293,10 +3341,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3316,10 +3364,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3339,10 +3387,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -3362,10 +3410,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3385,10 +3433,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C88" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3408,10 +3456,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C89" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3431,10 +3479,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3454,10 +3502,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C91" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3477,10 +3525,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C92" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3500,10 +3548,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C93" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3523,10 +3571,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C94" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3546,10 +3594,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C95" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3569,10 +3617,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C96" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3592,10 +3640,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C97" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3615,10 +3663,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C98" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3638,19 +3686,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C99" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F99">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3661,19 +3709,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C100" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F100">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3684,10 +3732,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C101" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3707,19 +3755,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C102" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F102">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3730,19 +3778,19 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C103" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F103">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G103">
         <v>100</v>
@@ -3753,19 +3801,19 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C104" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F104">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -3776,10 +3824,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C105" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -3799,10 +3847,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C106" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3822,10 +3870,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C107" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3845,19 +3893,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C108" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3868,10 +3916,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C109" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3891,10 +3939,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C110" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3914,10 +3962,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C111" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3937,10 +3985,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C112" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3960,10 +4008,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C113" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3983,19 +4031,19 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C114" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F114">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G114">
         <v>100</v>
@@ -4006,19 +4054,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C115" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F115">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -4029,10 +4077,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C116" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4052,19 +4100,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C117" t="s">
-        <v>215</v>
+        <v>301</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F117">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G117">
         <v>100</v>
@@ -4075,19 +4123,19 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C118" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F118">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G118">
         <v>100</v>
@@ -4098,10 +4146,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C119" t="s">
-        <v>294</v>
+        <v>224</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4121,19 +4169,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C120" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F120">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -4144,10 +4192,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C121" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4167,19 +4215,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C122" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F122">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4190,10 +4238,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C123" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4213,10 +4261,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C124" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4236,19 +4284,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C125" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F125">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G125">
         <v>100</v>
@@ -4259,10 +4307,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C126" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4282,10 +4330,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C127" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4305,10 +4353,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C128" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4328,10 +4376,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C129" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4351,10 +4399,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C130" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4374,19 +4422,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4397,19 +4445,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C132" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F132">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4420,10 +4468,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C133" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4443,19 +4491,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C134" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F134">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4466,10 +4514,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C135" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4489,19 +4537,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C136" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4512,19 +4560,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C137" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F137">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4535,10 +4583,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C138" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -4558,10 +4606,10 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4581,10 +4629,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C140" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4604,19 +4652,19 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C141" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F141">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G141">
         <v>100</v>
@@ -4627,10 +4675,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C142" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4650,10 +4698,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C143" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4673,19 +4721,19 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C144" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F144">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -4696,10 +4744,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C145" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4719,19 +4767,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C146" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F146">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G146">
         <v>100</v>
@@ -4742,19 +4790,19 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C147" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F147">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G147">
         <v>100</v>
@@ -4765,19 +4813,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C148" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F148">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G148">
         <v>100</v>
@@ -4788,19 +4836,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C149" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E149">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F149">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G149">
         <v>100</v>
@@ -4811,10 +4859,10 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C150" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -4834,19 +4882,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C151" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E151">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F151">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G151">
         <v>100</v>
@@ -4857,10 +4905,10 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C152" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -4880,19 +4928,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C153" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F153">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -4903,10 +4951,10 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C154" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -4926,10 +4974,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C155" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -4949,19 +4997,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C156" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E156">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F156">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G156">
         <v>100</v>
@@ -4972,19 +5020,19 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F157">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G157">
         <v>100</v>
@@ -4995,10 +5043,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C158" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5018,21 +5066,205 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C159" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>44</v>
+      </c>
+      <c r="F159">
+        <v>44</v>
+      </c>
+      <c r="G159">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>165</v>
+      </c>
+      <c r="B160" t="s">
+        <v>184</v>
+      </c>
+      <c r="C160" t="s">
+        <v>343</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>44</v>
+      </c>
+      <c r="F160">
+        <v>44</v>
+      </c>
+      <c r="G160">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" t="s">
+        <v>184</v>
+      </c>
+      <c r="C161" t="s">
+        <v>344</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>44</v>
+      </c>
+      <c r="F161">
+        <v>44</v>
+      </c>
+      <c r="G161">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>167</v>
+      </c>
+      <c r="B162" t="s">
+        <v>180</v>
+      </c>
+      <c r="C162" t="s">
+        <v>345</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162">
+        <v>88</v>
+      </c>
+      <c r="F162">
+        <v>88</v>
+      </c>
+      <c r="G162">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>168</v>
+      </c>
+      <c r="B163" t="s">
+        <v>180</v>
+      </c>
+      <c r="C163" t="s">
+        <v>346</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>44</v>
+      </c>
+      <c r="F163">
+        <v>44</v>
+      </c>
+      <c r="G163">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>169</v>
+      </c>
+      <c r="B164" t="s">
+        <v>180</v>
+      </c>
+      <c r="C164" t="s">
+        <v>347</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>44</v>
+      </c>
+      <c r="F164">
+        <v>44</v>
+      </c>
+      <c r="G164">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" t="s">
+        <v>180</v>
+      </c>
+      <c r="C165" t="s">
+        <v>348</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>44</v>
+      </c>
+      <c r="F165">
+        <v>44</v>
+      </c>
+      <c r="G165">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>171</v>
+      </c>
+      <c r="B166" t="s">
+        <v>180</v>
+      </c>
+      <c r="C166" t="s">
+        <v>349</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>44</v>
+      </c>
+      <c r="F166">
+        <v>44</v>
+      </c>
+      <c r="G166">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167" t="s">
+        <v>180</v>
+      </c>
+      <c r="C167" t="s">
+        <v>350</v>
+      </c>
+      <c r="D167">
         <v>4</v>
       </c>
-      <c r="E159">
+      <c r="E167">
         <v>176</v>
       </c>
-      <c r="F159">
+      <c r="F167">
         <v>176</v>
       </c>
-      <c r="G159">
+      <c r="G167">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="357">
   <si>
     <t>clues</t>
   </si>
@@ -49,12 +49,12 @@
     <t>MCIMB008800</t>
   </si>
   <si>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
     <t>QRIMB001775</t>
   </si>
   <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
     <t>MNIMB001316</t>
   </si>
   <si>
@@ -76,6 +76,9 @@
     <t>CSIMB003651</t>
   </si>
   <si>
+    <t>VZIMB000831</t>
+  </si>
+  <si>
     <t>VZIMB007855</t>
   </si>
   <si>
@@ -91,21 +94,24 @@
     <t>VZIMB005475</t>
   </si>
   <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
     <t>VZIMB002260</t>
   </si>
   <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
     <t>SPIMB002241</t>
   </si>
   <si>
     <t>VZIMB007843</t>
   </si>
   <si>
+    <t>TSIMB003372</t>
+  </si>
+  <si>
     <t>BCIMB000092</t>
   </si>
   <si>
@@ -118,6 +124,9 @@
     <t>TSIMB003104</t>
   </si>
   <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
     <t>SPIMB002842</t>
   </si>
   <si>
@@ -130,21 +139,21 @@
     <t>MCIMB004110</t>
   </si>
   <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
     <t>NTIMB000126</t>
   </si>
   <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
     <t>ZSIMB001641</t>
   </si>
   <si>
@@ -160,15 +169,15 @@
     <t>SPIMB002661</t>
   </si>
   <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
     <t>MCIMB003842</t>
   </si>
   <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
     <t>MCIMB007214</t>
   </si>
   <si>
@@ -178,325 +187,340 @@
     <t>VZIMB002395</t>
   </si>
   <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
     <t>MCIMB006671</t>
   </si>
   <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
     <t>MCIMB006654</t>
   </si>
   <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
   </si>
   <si>
     <t>MCIMB004163</t>
   </si>
   <si>
-    <t>MCIMB006683</t>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
   </si>
   <si>
     <t>MCIMB004105</t>
   </si>
   <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
   </si>
   <si>
     <t>QRIMB001961</t>
   </si>
   <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
   </si>
   <si>
     <t>SPIMB002760</t>
   </si>
   <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
   </si>
   <si>
     <t>VZIMB005620</t>
@@ -505,33 +529,18 @@
     <t>VZIMB003264</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
+    <t>VZIMB007604</t>
   </si>
   <si>
     <t>VZIMB007505</t>
   </si>
   <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
     <t>VZIMB005661</t>
   </si>
   <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -565,12 +574,12 @@
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
-    <t>TAMAULIPAS</t>
-  </si>
-  <si>
     <t>ZACATECAS</t>
   </si>
   <si>
@@ -586,12 +595,12 @@
     <t>SANTA MARÍA OZUMBILLA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD ACALPICAN</t>
   </si>
   <si>
@@ -613,6 +622,9 @@
     <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
   </si>
   <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+  </si>
+  <si>
     <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
   </si>
   <si>
@@ -628,21 +640,24 @@
     <t>BARRA DE CHACHALACAS</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
     <t>CUAUTLAPAN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD DORACELI</t>
   </si>
   <si>
     <t>LA ANTIGUA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+  </si>
+  <si>
     <t>FRACCIONAMIENTO MAR</t>
   </si>
   <si>
@@ -655,6 +670,9 @@
     <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
   </si>
   <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
     <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
   </si>
   <si>
@@ -667,21 +685,21 @@
     <t>INDEPENDENCIA</t>
   </si>
   <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
     <t>VALLE DE LA URRACA</t>
   </si>
   <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD ZACATECAS</t>
   </si>
   <si>
@@ -697,15 +715,15 @@
     <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
     <t>EL MOLINITO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
     <t>PRADOS</t>
   </si>
   <si>
@@ -715,322 +733,337 @@
     <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
   </si>
   <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
     <t>SAN PEDRO BARRIENTOS</t>
   </si>
   <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
     <t>LA LAGUNA</t>
   </si>
   <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
   </si>
   <si>
     <t>SAN JOSÉ DEL VIDRIO</t>
   </si>
   <si>
-    <t>LÁZARO CÁRDENAS III</t>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
   </si>
   <si>
     <t>COL. LIBERTAD</t>
   </si>
   <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD URBANO CALDERITAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
   </si>
   <si>
     <t>SAN RAFAEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>LAS BAJADAS</t>
@@ -1039,31 +1072,16 @@
     <t>ORIZABA</t>
   </si>
   <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
     <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1424,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1455,10 +1473,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1478,10 +1496,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1501,10 +1519,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1524,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1547,10 +1565,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1570,10 +1588,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1593,10 +1611,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1616,10 +1634,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1639,10 +1657,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1662,10 +1680,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1685,10 +1703,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1708,10 +1726,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1731,10 +1749,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1754,10 +1772,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1777,22 +1795,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>44</v>
       </c>
       <c r="G16">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1800,22 +1818,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1823,22 +1841,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1846,22 +1864,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G19">
-        <v>31.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1869,22 +1887,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F20">
         <v>44</v>
       </c>
       <c r="G20">
-        <v>43.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1892,10 +1910,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1915,10 +1933,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1938,22 +1956,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G23">
-        <v>53.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1961,22 +1979,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G24">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1987,19 +2005,19 @@
         <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>68.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2007,22 +2025,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>70.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2030,22 +2048,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F27">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>79.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2053,22 +2071,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>81.8</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2076,22 +2094,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="F29">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G29">
-        <v>87.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2099,22 +2117,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C30" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F30">
         <v>44</v>
       </c>
       <c r="G30">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2122,22 +2140,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>95.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2145,22 +2163,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>343</v>
+        <v>192</v>
       </c>
       <c r="F32">
-        <v>352</v>
+        <v>220</v>
       </c>
       <c r="G32">
-        <v>97.40000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2168,22 +2186,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C33" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>97.7</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2191,22 +2209,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34">
         <v>44</v>
       </c>
       <c r="G34">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2214,22 +2232,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>343</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2237,10 +2255,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2260,10 +2278,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2283,22 +2301,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="F38">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G38">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2306,22 +2324,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F39">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G39">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2329,22 +2347,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F40">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G40">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2352,19 +2370,19 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C41" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F41">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G41">
         <v>98.90000000000001</v>
@@ -2375,22 +2393,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F42">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G42">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2398,22 +2416,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F43">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G43">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2421,22 +2439,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C44" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F44">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G44">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2444,22 +2462,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C45" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F45">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G45">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2467,22 +2485,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F46">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G46">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2490,22 +2508,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F47">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G47">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2513,22 +2531,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D48">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F48">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G48">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2536,22 +2554,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="F49">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2559,22 +2577,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="F50">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G50">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2582,22 +2600,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C51" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>220</v>
+        <v>615</v>
       </c>
       <c r="F51">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2605,19 +2623,19 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F52">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2628,10 +2646,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2651,10 +2669,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C54" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2674,19 +2692,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F55">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G55">
         <v>100</v>
@@ -2697,10 +2715,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2720,19 +2738,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2743,10 +2761,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2766,10 +2784,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C59" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2789,19 +2807,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C60" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F60">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G60">
         <v>100</v>
@@ -2812,10 +2830,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2835,10 +2853,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C62" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -2858,19 +2876,19 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="F63">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G63">
         <v>100</v>
@@ -2881,19 +2899,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C64" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E64">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F64">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G64">
         <v>100</v>
@@ -2904,10 +2922,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2927,19 +2945,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C66" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F66">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -2950,10 +2968,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2973,10 +2991,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2996,10 +3014,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3019,10 +3037,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C70" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3042,10 +3060,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3065,19 +3083,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F72">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -3088,19 +3106,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C73" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F73">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -3111,10 +3129,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3134,10 +3152,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3157,10 +3175,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3180,10 +3198,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3203,10 +3221,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C78" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3226,10 +3244,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C79" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3249,10 +3267,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C80" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3272,19 +3290,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F81">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -3295,10 +3313,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3318,10 +3336,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3341,10 +3359,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3364,10 +3382,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3387,19 +3405,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3410,10 +3428,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C87" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3433,10 +3451,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3456,10 +3474,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C89" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3479,10 +3497,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C90" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3502,10 +3520,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3525,10 +3543,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C92" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3548,10 +3566,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C93" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3571,10 +3589,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C94" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3594,10 +3612,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C95" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3617,10 +3635,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C96" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3640,10 +3658,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C97" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3663,10 +3681,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3686,10 +3704,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C99" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -3709,10 +3727,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C100" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -3732,10 +3750,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C101" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3755,10 +3773,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C102" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -3778,10 +3796,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C103" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -3801,10 +3819,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C104" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3824,10 +3842,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C105" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -3847,10 +3865,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C106" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3870,10 +3888,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C107" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3893,19 +3911,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C108" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F108">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3916,10 +3934,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C109" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3939,10 +3957,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C110" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3962,10 +3980,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C111" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3985,10 +4003,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C112" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -4008,10 +4026,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C113" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4031,19 +4049,19 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C114" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F114">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G114">
         <v>100</v>
@@ -4054,10 +4072,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C115" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4077,10 +4095,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C116" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4100,19 +4118,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C117" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F117">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G117">
         <v>100</v>
@@ -4123,10 +4141,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C118" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4146,10 +4164,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>224</v>
+        <v>306</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4169,10 +4187,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C120" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4192,10 +4210,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C121" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4215,10 +4233,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C122" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4238,10 +4256,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C123" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4261,10 +4279,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C124" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4284,10 +4302,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C125" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4307,10 +4325,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C126" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4330,10 +4348,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C127" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4353,10 +4371,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C128" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4376,10 +4394,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C129" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4399,19 +4417,19 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C130" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F130">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G130">
         <v>100</v>
@@ -4422,19 +4440,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C131" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4445,19 +4463,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C132" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F132">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4468,19 +4486,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C133" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F133">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4491,10 +4509,10 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C134" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4514,10 +4532,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C135" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4537,10 +4555,10 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C136" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -4560,10 +4578,10 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C137" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -4583,19 +4601,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C138" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F138">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G138">
         <v>100</v>
@@ -4606,19 +4624,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C139" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4629,10 +4647,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C140" t="s">
-        <v>323</v>
+        <v>230</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4652,10 +4670,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C141" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4675,10 +4693,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C142" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4698,10 +4716,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C143" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4721,19 +4739,19 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C144" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F144">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -4744,10 +4762,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C145" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4767,10 +4785,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C146" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -4790,19 +4808,19 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C147" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F147">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G147">
         <v>100</v>
@@ -4813,10 +4831,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C148" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -4836,19 +4854,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C149" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E149">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F149">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G149">
         <v>100</v>
@@ -4859,19 +4877,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C150" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E150">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F150">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G150">
         <v>100</v>
@@ -4882,19 +4900,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C151" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E151">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F151">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G151">
         <v>100</v>
@@ -4905,19 +4923,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C152" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F152">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G152">
         <v>100</v>
@@ -4928,19 +4946,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C153" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E153">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F153">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -4951,19 +4969,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C154" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E154">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F154">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G154">
         <v>100</v>
@@ -4974,19 +4992,19 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C155" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E155">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F155">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G155">
         <v>100</v>
@@ -4997,19 +5015,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C156" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F156">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G156">
         <v>100</v>
@@ -5020,10 +5038,10 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C157" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -5043,10 +5061,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C158" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5066,10 +5084,10 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C159" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -5089,10 +5107,10 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C160" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -5112,10 +5130,10 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C161" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -5135,19 +5153,19 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C162" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F162">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G162">
         <v>100</v>
@@ -5158,10 +5176,10 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C163" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -5181,19 +5199,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C164" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F164">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G164">
         <v>100</v>
@@ -5204,10 +5222,10 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C165" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5227,10 +5245,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C166" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -5250,21 +5268,90 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C167" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D167">
+        <v>2</v>
+      </c>
+      <c r="E167">
+        <v>88</v>
+      </c>
+      <c r="F167">
+        <v>88</v>
+      </c>
+      <c r="G167">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>173</v>
+      </c>
+      <c r="B168" t="s">
+        <v>183</v>
+      </c>
+      <c r="C168" t="s">
+        <v>354</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168">
+        <v>44</v>
+      </c>
+      <c r="F168">
+        <v>44</v>
+      </c>
+      <c r="G168">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>174</v>
+      </c>
+      <c r="B169" t="s">
+        <v>183</v>
+      </c>
+      <c r="C169" t="s">
+        <v>355</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169">
+        <v>44</v>
+      </c>
+      <c r="F169">
+        <v>44</v>
+      </c>
+      <c r="G169">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170" t="s">
+        <v>183</v>
+      </c>
+      <c r="C170" t="s">
+        <v>356</v>
+      </c>
+      <c r="D170">
         <v>4</v>
       </c>
-      <c r="E167">
+      <c r="E170">
         <v>176</v>
       </c>
-      <c r="F167">
+      <c r="F170">
         <v>176</v>
       </c>
-      <c r="G167">
+      <c r="G170">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="361">
   <si>
     <t>clues</t>
   </si>
@@ -64,439 +64,463 @@
     <t>MCIMB004122</t>
   </si>
   <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
     <t>OCIMB002392</t>
   </si>
   <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
     <t>CSIMB003651</t>
   </si>
   <si>
+    <t>VZIMB007855</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>TSIMB001144</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003372</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
     <t>VZIMB000831</t>
   </si>
   <si>
-    <t>VZIMB007855</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>TSIMB003372</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
   </si>
   <si>
     <t>SPIMB002731</t>
   </si>
   <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
   </si>
   <si>
     <t>VZIMB002890</t>
@@ -505,16 +529,10 @@
     <t>VZIMB002885</t>
   </si>
   <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB005656</t>
@@ -523,24 +541,12 @@
     <t>VZIMB005632</t>
   </si>
   <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -571,12 +577,12 @@
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
-    <t>TAMAULIPAS</t>
-  </si>
-  <si>
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
@@ -610,436 +616,460 @@
     <t>LA COLMENA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
     <t>SAN JUAN YUTA</t>
   </si>
   <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
   </si>
   <si>
+    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
     <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
   </si>
   <si>
-    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD LOS MAGUEYES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
   </si>
   <si>
     <t>CHICHIGAPA</t>
@@ -1048,16 +1078,10 @@
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>VARGAS</t>
@@ -1066,22 +1090,10 @@
     <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1442,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1473,10 +1485,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1496,10 +1508,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1519,10 +1531,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1542,10 +1554,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1565,10 +1577,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1588,10 +1600,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1611,10 +1623,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1634,10 +1646,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1657,10 +1669,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1680,22 +1692,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1703,10 +1715,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1726,10 +1738,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1749,22 +1761,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>44</v>
       </c>
       <c r="G14">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1772,10 +1784,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1795,10 +1807,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1818,10 +1830,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1841,10 +1853,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1864,10 +1876,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -1887,22 +1899,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F20">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G20">
-        <v>31.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1910,22 +1922,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>43.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1936,19 +1948,19 @@
         <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>47.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1956,22 +1968,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>52.3</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1982,19 +1994,19 @@
         <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>53.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2002,22 +2014,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G25">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2025,19 +2037,19 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G26">
         <v>63.6</v>
@@ -2048,10 +2060,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C27" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2071,10 +2083,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C28" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2094,10 +2106,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2117,10 +2129,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2140,22 +2152,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="F31">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G31">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2163,22 +2175,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="F32">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2186,22 +2198,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2209,22 +2221,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>42</v>
+        <v>343</v>
       </c>
       <c r="F34">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G34">
-        <v>95.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2232,22 +2244,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>343</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="G35">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2255,10 +2267,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C36" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2278,10 +2290,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2301,10 +2313,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2324,10 +2336,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2347,22 +2359,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F40">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G40">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2370,10 +2382,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C41" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -2393,10 +2405,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2416,10 +2428,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2439,22 +2451,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C44" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F44">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G44">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2462,22 +2474,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F45">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G45">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2485,10 +2497,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C46" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2508,10 +2520,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -2531,22 +2543,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C48" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F48">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G48">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2554,10 +2566,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -2577,22 +2589,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>219</v>
+        <v>615</v>
       </c>
       <c r="F50">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G50">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2600,22 +2612,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C51" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D51">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G51">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2623,10 +2635,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2646,10 +2658,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2669,10 +2681,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2692,19 +2704,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="F55">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="G55">
         <v>100</v>
@@ -2715,10 +2727,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2738,19 +2750,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2761,10 +2773,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2784,10 +2796,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C59" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2807,10 +2819,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2830,10 +2842,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2853,10 +2865,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C62" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -2876,10 +2888,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C63" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2899,10 +2911,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C64" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D64">
         <v>6</v>
@@ -2922,10 +2934,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C65" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2945,10 +2957,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2968,10 +2980,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2991,10 +3003,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C68" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3014,10 +3026,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3037,10 +3049,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C70" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3060,10 +3072,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3083,10 +3095,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -3106,10 +3118,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C73" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3129,10 +3141,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3152,10 +3164,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3175,10 +3187,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3198,10 +3210,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C77" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3221,10 +3233,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C78" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3244,10 +3256,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C79" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3267,19 +3279,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E80">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F80">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -3290,19 +3302,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F81">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -3313,10 +3325,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3336,10 +3348,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3359,10 +3371,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3382,10 +3394,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3405,10 +3417,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C86" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3428,10 +3440,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3451,10 +3463,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C88" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3474,19 +3486,19 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C89" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F89">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G89">
         <v>100</v>
@@ -3497,10 +3509,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3520,10 +3532,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C91" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3543,10 +3555,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C92" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3566,10 +3578,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3589,10 +3601,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3612,10 +3624,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3635,10 +3647,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3658,10 +3670,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C97" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3681,19 +3693,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C98" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F98">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3704,19 +3716,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C99" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F99">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3727,19 +3739,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C100" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F100">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3750,19 +3762,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C101" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3773,10 +3785,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C102" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -3796,19 +3808,19 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C103" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F103">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G103">
         <v>100</v>
@@ -3819,19 +3831,19 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C104" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F104">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -3842,19 +3854,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C105" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -3865,10 +3877,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C106" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3888,19 +3900,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C107" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F107">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3911,19 +3923,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C108" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3934,10 +3946,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C109" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3957,10 +3969,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C110" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3980,10 +3992,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C111" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4003,10 +4015,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C112" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -4026,10 +4038,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C113" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4049,19 +4061,19 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C114" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F114">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G114">
         <v>100</v>
@@ -4072,19 +4084,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C115" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F115">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -4095,10 +4107,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C116" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4118,10 +4130,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C117" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4141,10 +4153,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C118" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4164,10 +4176,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C119" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4187,10 +4199,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C120" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4210,10 +4222,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C121" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4233,10 +4245,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C122" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4256,10 +4268,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C123" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4279,10 +4291,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C124" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4302,10 +4314,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C125" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4325,10 +4337,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C126" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4348,10 +4360,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C127" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4371,10 +4383,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C128" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4394,10 +4406,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C129" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4417,10 +4429,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C130" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -4440,10 +4452,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C131" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4463,10 +4475,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C132" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4486,19 +4498,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C133" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F133">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4509,10 +4521,10 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C134" t="s">
-        <v>321</v>
+        <v>229</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4532,10 +4544,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C135" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4555,10 +4567,10 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C136" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -4578,10 +4590,10 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C137" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -4601,19 +4613,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C138" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F138">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G138">
         <v>100</v>
@@ -4624,19 +4636,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C139" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4647,10 +4659,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C140" t="s">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4670,10 +4682,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C141" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4693,10 +4705,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C142" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4716,10 +4728,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C143" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4739,10 +4751,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C144" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4762,10 +4774,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C145" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4785,19 +4797,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C146" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F146">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G146">
         <v>100</v>
@@ -4808,10 +4820,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C147" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4831,19 +4843,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C148" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F148">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G148">
         <v>100</v>
@@ -4854,19 +4866,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C149" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E149">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F149">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G149">
         <v>100</v>
@@ -4877,19 +4889,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C150" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F150">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G150">
         <v>100</v>
@@ -4900,10 +4912,10 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C151" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -4923,19 +4935,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C152" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F152">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G152">
         <v>100</v>
@@ -4946,10 +4958,10 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C153" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D153">
         <v>2</v>
@@ -4969,10 +4981,10 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C154" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -4992,19 +5004,19 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C155" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F155">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G155">
         <v>100</v>
@@ -5015,19 +5027,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C156" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E156">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F156">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G156">
         <v>100</v>
@@ -5038,19 +5050,19 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C157" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F157">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G157">
         <v>100</v>
@@ -5061,10 +5073,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C158" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5084,10 +5096,10 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C159" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -5107,10 +5119,10 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -5130,19 +5142,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C161" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F161">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G161">
         <v>100</v>
@@ -5153,19 +5165,19 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E162">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F162">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G162">
         <v>100</v>
@@ -5176,10 +5188,10 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C163" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -5199,19 +5211,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C164" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F164">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G164">
         <v>100</v>
@@ -5222,10 +5234,10 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C165" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5245,10 +5257,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C166" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -5268,10 +5280,10 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C167" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -5291,10 +5303,10 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C168" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -5314,10 +5326,10 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C169" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -5337,21 +5349,67 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C170" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>44</v>
+      </c>
+      <c r="F170">
+        <v>44</v>
+      </c>
+      <c r="G170">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171" t="s">
+        <v>185</v>
+      </c>
+      <c r="C171" t="s">
+        <v>359</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>44</v>
+      </c>
+      <c r="F171">
+        <v>44</v>
+      </c>
+      <c r="G171">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172" t="s">
+        <v>185</v>
+      </c>
+      <c r="C172" t="s">
+        <v>360</v>
+      </c>
+      <c r="D172">
         <v>4</v>
       </c>
-      <c r="E170">
+      <c r="E172">
         <v>176</v>
       </c>
-      <c r="F170">
+      <c r="F172">
         <v>176</v>
       </c>
-      <c r="G170">
+      <c r="G172">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="375">
   <si>
     <t>clues</t>
   </si>
@@ -64,463 +64,499 @@
     <t>MCIMB004122</t>
   </si>
   <si>
+    <t>OCIMB002392</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>ZSIMB001385</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>VZIMB007855</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
     <t>MCIMB010253</t>
   </si>
   <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>OCIMB002392</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>VZIMB007855</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
   </si>
   <si>
     <t>TSIMB001144</t>
   </si>
   <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
   </si>
   <si>
     <t>SPIMB002533</t>
   </si>
   <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
     <t>SPIMB002340</t>
   </si>
   <si>
     <t>SPIMB002521</t>
   </si>
   <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>VZIMB000831</t>
   </si>
   <si>
     <t>TSIMB003401</t>
   </si>
   <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
     <t>TSIMB003372</t>
   </si>
   <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB000831</t>
+    <t>VZIMB003264</t>
   </si>
   <si>
     <t>VZIMB002412</t>
   </si>
   <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
   </si>
   <si>
     <t>VZIMB005620</t>
   </si>
   <si>
-    <t>VZIMB003264</t>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB002890</t>
@@ -529,27 +565,12 @@
     <t>VZIMB002885</t>
   </si>
   <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
+    <t>VZIMB007942</t>
   </si>
   <si>
     <t>VZIMB007616</t>
   </si>
   <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>VZIMB007942</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
@@ -568,6 +589,9 @@
     <t>OAXACA</t>
   </si>
   <si>
+    <t>ZACATECAS</t>
+  </si>
+  <si>
     <t>CHIAPAS</t>
   </si>
   <si>
@@ -577,18 +601,15 @@
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>SAN LUIS POTOSI</t>
+  </si>
+  <si>
+    <t>BAJA CALIFORNIA</t>
+  </si>
+  <si>
     <t>TAMAULIPAS</t>
   </si>
   <si>
-    <t>SAN LUIS POTOSI</t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA</t>
-  </si>
-  <si>
-    <t>ZACATECAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD CASTAMAY</t>
   </si>
   <si>
@@ -616,460 +637,496 @@
     <t>LA COLMENA</t>
   </si>
   <si>
+    <t>SAN JUAN YUTA</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN JUAN CAPISTRANO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
   </si>
   <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>SAN JUAN YUTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
   </si>
   <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD FRANCISCO VILLA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
   </si>
   <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. LAS BRISAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+    <t>ORIZABA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>LAS BAJADAS</t>
   </si>
   <si>
-    <t>ORIZABA</t>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>CHICHIGAPA</t>
@@ -1078,25 +1135,10 @@
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
+    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
   <si>
     <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
 </sst>
 </file>
@@ -1454,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1485,10 +1527,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1508,10 +1550,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1531,10 +1573,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1554,10 +1596,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1577,10 +1619,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1600,10 +1642,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1623,10 +1665,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1646,10 +1688,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1669,10 +1711,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1692,22 +1734,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1715,10 +1757,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1738,10 +1780,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1761,10 +1803,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1784,10 +1826,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1807,10 +1849,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1830,10 +1872,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1853,10 +1895,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1876,10 +1918,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -1899,22 +1941,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G20">
-        <v>23.9</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1922,22 +1964,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>31.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1945,22 +1987,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>43.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1968,22 +2010,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>47.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1991,22 +2033,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G24">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2014,22 +2056,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2037,22 +2079,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2060,22 +2102,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C27" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2083,22 +2125,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2106,22 +2148,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F29">
         <v>44</v>
       </c>
       <c r="G29">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2129,22 +2171,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C30" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30">
         <v>44</v>
       </c>
       <c r="G30">
-        <v>81.8</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2152,10 +2194,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -2175,10 +2217,10 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2198,10 +2240,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2221,10 +2263,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D34">
         <v>8</v>
@@ -2244,10 +2286,10 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2267,10 +2309,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2290,10 +2332,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2313,10 +2355,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2336,10 +2378,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2359,10 +2401,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C40" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2382,10 +2424,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -2405,10 +2447,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C42" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2428,10 +2470,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C43" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2451,10 +2493,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C44" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -2474,10 +2516,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C45" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2497,10 +2539,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C46" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2520,10 +2562,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -2543,10 +2585,10 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -2566,10 +2608,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C49" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -2589,10 +2631,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C50" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D50">
         <v>14</v>
@@ -2612,10 +2654,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2635,10 +2677,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2658,19 +2700,19 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C53" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F53">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G53">
         <v>100</v>
@@ -2681,10 +2723,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2704,10 +2746,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C55" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2727,10 +2769,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2750,10 +2792,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2773,10 +2815,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2796,10 +2838,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2819,10 +2861,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C60" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2842,10 +2884,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C61" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2865,10 +2907,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -2888,10 +2930,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C63" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2911,10 +2953,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D64">
         <v>6</v>
@@ -2934,10 +2976,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C65" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2957,10 +2999,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C66" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2980,10 +3022,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C67" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3003,10 +3045,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3026,19 +3068,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F69">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -3049,10 +3091,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3072,10 +3114,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3095,19 +3137,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F72">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -3118,10 +3160,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3144,7 +3186,7 @@
         <v>186</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3164,10 +3206,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C75" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3187,10 +3229,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3210,10 +3252,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C77" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3233,10 +3275,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3256,10 +3298,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3279,19 +3321,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C80" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F80">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -3302,10 +3344,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C81" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3325,10 +3367,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C82" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3348,10 +3390,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3371,10 +3413,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C84" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3394,10 +3436,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C85" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3417,10 +3459,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C86" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3440,10 +3482,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C87" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3463,10 +3505,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3486,19 +3528,19 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F89">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G89">
         <v>100</v>
@@ -3509,19 +3551,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F90">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3532,10 +3574,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3555,10 +3597,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C92" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3578,10 +3620,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3601,10 +3643,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3624,10 +3666,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C95" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3647,10 +3689,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C96" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3670,10 +3712,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3693,10 +3735,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C98" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -3716,19 +3758,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C99" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F99">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3739,10 +3781,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C100" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3762,10 +3804,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C101" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -3785,19 +3827,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C102" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F102">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -3808,10 +3850,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C103" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3831,19 +3873,19 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C104" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F104">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G104">
         <v>100</v>
@@ -3854,10 +3896,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C105" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3877,10 +3919,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C106" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3900,19 +3942,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C107" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F107">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3923,10 +3965,10 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C108" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -3946,19 +3988,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C109" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F109">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -3969,10 +4011,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C110" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3992,10 +4034,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C111" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4015,19 +4057,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C112" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -4038,19 +4080,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C113" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F113">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -4061,10 +4103,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C114" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4084,19 +4126,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C115" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F115">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -4107,10 +4149,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C116" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4130,10 +4172,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C117" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4153,10 +4195,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C118" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4176,10 +4218,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C119" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4199,10 +4241,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4222,10 +4264,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C121" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4245,10 +4287,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C122" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4268,10 +4310,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C123" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4291,10 +4333,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C124" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4314,10 +4356,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C125" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4337,10 +4379,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C126" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4360,10 +4402,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C127" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4383,10 +4425,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C128" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4406,10 +4448,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C129" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4429,10 +4471,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C130" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -4452,19 +4494,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C131" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4475,10 +4517,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C132" t="s">
-        <v>321</v>
+        <v>236</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4498,10 +4540,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C133" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4521,19 +4563,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C134" t="s">
-        <v>229</v>
+        <v>329</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F134">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4544,10 +4586,10 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C135" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4567,19 +4609,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C136" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F136">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4590,19 +4632,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C137" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F137">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4613,19 +4655,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C138" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F138">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G138">
         <v>100</v>
@@ -4636,19 +4678,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C139" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4659,19 +4701,19 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C140" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F140">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G140">
         <v>100</v>
@@ -4685,7 +4727,7 @@
         <v>187</v>
       </c>
       <c r="C141" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4708,7 +4750,7 @@
         <v>187</v>
       </c>
       <c r="C142" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4728,19 +4770,19 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C143" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F143">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G143">
         <v>100</v>
@@ -4751,10 +4793,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C144" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4774,10 +4816,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C145" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4797,10 +4839,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C146" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4820,10 +4862,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C147" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4843,19 +4885,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C148" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F148">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G148">
         <v>100</v>
@@ -4866,10 +4908,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C149" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -4889,19 +4931,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C150" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F150">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G150">
         <v>100</v>
@@ -4912,19 +4954,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C151" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F151">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G151">
         <v>100</v>
@@ -4935,19 +4977,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C152" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E152">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F152">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G152">
         <v>100</v>
@@ -4958,19 +5000,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C153" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F153">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -4981,19 +5023,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C154" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F154">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G154">
         <v>100</v>
@@ -5004,10 +5046,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C155" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -5027,19 +5069,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C156" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F156">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G156">
         <v>100</v>
@@ -5050,19 +5092,19 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C157" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E157">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F157">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G157">
         <v>100</v>
@@ -5073,10 +5115,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C158" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5096,19 +5138,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C159" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F159">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G159">
         <v>100</v>
@@ -5119,10 +5161,10 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C160" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -5142,19 +5184,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C161" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F161">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G161">
         <v>100</v>
@@ -5165,10 +5207,10 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C162" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D162">
         <v>3</v>
@@ -5188,19 +5230,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C163" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F163">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G163">
         <v>100</v>
@@ -5211,10 +5253,10 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C164" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -5234,10 +5276,10 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C165" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5257,19 +5299,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C166" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F166">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G166">
         <v>100</v>
@@ -5280,10 +5322,10 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C167" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -5303,10 +5345,10 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C168" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -5326,19 +5368,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C169" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F169">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G169">
         <v>100</v>
@@ -5349,10 +5391,10 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -5372,10 +5414,10 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C171" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -5395,21 +5437,182 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C172" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="D172">
+        <v>3</v>
+      </c>
+      <c r="E172">
+        <v>132</v>
+      </c>
+      <c r="F172">
+        <v>132</v>
+      </c>
+      <c r="G172">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173" t="s">
+        <v>193</v>
+      </c>
+      <c r="C173" t="s">
+        <v>368</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>44</v>
+      </c>
+      <c r="F173">
+        <v>44</v>
+      </c>
+      <c r="G173">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>179</v>
+      </c>
+      <c r="B174" t="s">
+        <v>193</v>
+      </c>
+      <c r="C174" t="s">
+        <v>369</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>44</v>
+      </c>
+      <c r="F174">
+        <v>44</v>
+      </c>
+      <c r="G174">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" t="s">
+        <v>193</v>
+      </c>
+      <c r="C175" t="s">
+        <v>370</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="E175">
+        <v>88</v>
+      </c>
+      <c r="F175">
+        <v>88</v>
+      </c>
+      <c r="G175">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" t="s">
+        <v>193</v>
+      </c>
+      <c r="C176" t="s">
+        <v>371</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>44</v>
+      </c>
+      <c r="F176">
+        <v>44</v>
+      </c>
+      <c r="G176">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" t="s">
+        <v>193</v>
+      </c>
+      <c r="C177" t="s">
+        <v>372</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>44</v>
+      </c>
+      <c r="F177">
+        <v>44</v>
+      </c>
+      <c r="G177">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" t="s">
+        <v>193</v>
+      </c>
+      <c r="C178" t="s">
+        <v>373</v>
+      </c>
+      <c r="D178">
         <v>4</v>
       </c>
-      <c r="E172">
+      <c r="E178">
         <v>176</v>
       </c>
-      <c r="F172">
+      <c r="F178">
         <v>176</v>
       </c>
-      <c r="G172">
+      <c r="G178">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" t="s">
+        <v>193</v>
+      </c>
+      <c r="C179" t="s">
+        <v>374</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>44</v>
+      </c>
+      <c r="F179">
+        <v>44</v>
+      </c>
+      <c r="G179">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="377">
   <si>
     <t>clues</t>
   </si>
@@ -49,12 +49,12 @@
     <t>MCIMB008800</t>
   </si>
   <si>
+    <t>QRIMB001775</t>
+  </si>
+  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
-    <t>QRIMB001775</t>
-  </si>
-  <si>
     <t>MNIMB001316</t>
   </si>
   <si>
@@ -64,24 +64,27 @@
     <t>MCIMB004122</t>
   </si>
   <si>
+    <t>NTIMB001700</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
     <t>OCIMB002392</t>
   </si>
   <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
     <t>ZSIMB001385</t>
   </si>
   <si>
+    <t>VZIMB007855</t>
+  </si>
+  <si>
     <t>CSIMB003651</t>
   </si>
   <si>
-    <t>VZIMB007855</t>
-  </si>
-  <si>
     <t>NTIMB000131</t>
   </si>
   <si>
@@ -136,42 +139,42 @@
     <t>MCIMB004110</t>
   </si>
   <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
     <t>MCIMB010200</t>
   </si>
   <si>
-    <t>NTIMB000126</t>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
   </si>
   <si>
     <t>NTIMB001280</t>
   </si>
   <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
+    <t>ZSIMB001641</t>
   </si>
   <si>
     <t>SPIMB000450</t>
   </si>
   <si>
-    <t>ZSIMB001641</t>
+    <t>MCIMB008730</t>
   </si>
   <si>
     <t>QRIMB001652</t>
   </si>
   <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
     <t>SPIMB002661</t>
   </si>
   <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
     <t>MCIMB003842</t>
   </si>
   <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
     <t>SPIMB003146</t>
   </si>
   <si>
@@ -187,273 +190,273 @@
     <t>MCIMB007243</t>
   </si>
   <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
     <t>MCIMB008660</t>
   </si>
   <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>NTIMB001613</t>
-  </si>
-  <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
   </si>
   <si>
     <t>QRIMB001080</t>
   </si>
   <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
     <t>QRIMB001635</t>
   </si>
   <si>
@@ -463,114 +466,114 @@
     <t>SPIMB002731</t>
   </si>
   <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
     <t>SPIMB002760</t>
   </si>
   <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB000831</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003372</t>
   </si>
   <si>
     <t>TSIMB001144</t>
   </si>
   <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
+    <t>VZIMB002890</t>
   </si>
   <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>VZIMB000831</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003372</t>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
   </si>
   <si>
     <t>VZIMB003264</t>
   </si>
   <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
     <t>VZIMB002412</t>
   </si>
   <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB007942</t>
   </si>
   <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
@@ -586,21 +589,21 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
     <t>OAXACA</t>
   </si>
   <si>
     <t>ZACATECAS</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>CHIAPAS</t>
   </si>
   <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>NAYARIT</t>
-  </si>
-  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
@@ -622,12 +625,12 @@
     <t>SANTA MARÍA OZUMBILLA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD ACALPICAN</t>
   </si>
   <si>
@@ -637,24 +640,27 @@
     <t>LA COLMENA</t>
   </si>
   <si>
+    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
     <t>SAN JUAN YUTA</t>
   </si>
   <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD SAN JUAN CAPISTRANO</t>
   </si>
   <si>
+    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
   </si>
   <si>
-    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
-  </si>
-  <si>
     <t>EL CARRIZAL</t>
   </si>
   <si>
@@ -709,42 +715,42 @@
     <t>INDEPENDENCIA</t>
   </si>
   <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
     <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
   </si>
   <si>
-    <t>VALLE DE LA URRACA</t>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
   </si>
   <si>
     <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
   </si>
   <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
+    <t>CENTRO DE SALUD ZACATECAS</t>
   </si>
   <si>
     <t>PONCIANO ARRIAGA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL UCUM</t>
   </si>
   <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
     <t>EL MOLINITO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD VILLA CACTUS</t>
   </si>
   <si>
@@ -760,270 +766,270 @@
     <t>VALLE DE BRAVO</t>
   </si>
   <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
     <t>ALBORADA</t>
   </si>
   <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
-  </si>
-  <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
     <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
   </si>
   <si>
@@ -1033,112 +1039,112 @@
     <t>CENTRO DE SALUD LOS MAGUEYES</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
     <t>SAN RAFAEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+    <t>CHICHIGAPA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
   </si>
   <si>
     <t>ORIZABA</t>
   </si>
   <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
     <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1527,10 +1533,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1550,10 +1556,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1573,10 +1579,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1596,10 +1602,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1619,10 +1625,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1642,10 +1648,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1665,10 +1671,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1688,10 +1694,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1711,10 +1717,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1734,22 +1740,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1757,10 +1763,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1780,10 +1786,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1803,10 +1809,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1826,22 +1832,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1849,10 +1855,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1872,22 +1878,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1895,22 +1901,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>44</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1918,22 +1924,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>21.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1941,22 +1947,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F20">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G20">
-        <v>31.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1964,22 +1970,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>43.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1987,22 +1993,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>47.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2010,22 +2016,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>52.3</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2033,22 +2039,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>53.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2056,22 +2062,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G25">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2079,22 +2085,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>68.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2102,22 +2108,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F27">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2125,22 +2131,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2148,22 +2154,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29">
         <v>44</v>
       </c>
       <c r="G29">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2171,22 +2177,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30">
         <v>44</v>
       </c>
       <c r="G30">
-        <v>84.09999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2194,22 +2200,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G31">
-        <v>87.3</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2217,22 +2223,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G32">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2240,22 +2246,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>95.5</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2263,22 +2269,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>343</v>
+        <v>42</v>
       </c>
       <c r="F34">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="G34">
-        <v>97.40000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2286,22 +2292,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>343</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2309,10 +2315,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2332,10 +2338,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2355,10 +2361,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2378,10 +2384,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2401,22 +2407,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F40">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G40">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2424,10 +2430,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -2447,10 +2453,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2470,10 +2476,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2493,22 +2499,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F44">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G44">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2516,22 +2522,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F45">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G45">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2539,10 +2545,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2562,10 +2568,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -2585,22 +2591,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F48">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G48">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2608,10 +2614,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -2631,22 +2637,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>615</v>
+        <v>219</v>
       </c>
       <c r="F50">
-        <v>616</v>
+        <v>220</v>
       </c>
       <c r="G50">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2654,22 +2660,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2677,10 +2683,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2700,10 +2706,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D53">
         <v>5</v>
@@ -2723,10 +2729,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2746,10 +2752,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2769,10 +2775,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C56" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2792,10 +2798,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2815,10 +2821,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2838,10 +2844,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2861,10 +2867,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2884,10 +2890,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2907,10 +2913,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C62" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -2930,10 +2936,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2953,10 +2959,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D64">
         <v>6</v>
@@ -2976,10 +2982,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2999,10 +3005,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3022,10 +3028,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3045,10 +3051,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3068,10 +3074,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3091,10 +3097,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3114,10 +3120,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3137,10 +3143,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3160,10 +3166,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C73" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3183,10 +3189,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C74" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3206,10 +3212,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3229,10 +3235,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3252,10 +3258,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C77" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3275,10 +3281,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3298,10 +3304,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C79" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3321,10 +3327,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3344,10 +3350,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3367,10 +3373,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C82" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3390,10 +3396,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3413,10 +3419,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3436,10 +3442,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3459,10 +3465,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3482,10 +3488,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3505,10 +3511,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3528,10 +3534,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3551,19 +3557,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F90">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G90">
         <v>100</v>
@@ -3574,19 +3580,19 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F91">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G91">
         <v>100</v>
@@ -3597,10 +3603,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C92" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3620,10 +3626,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3643,10 +3649,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C94" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3666,10 +3672,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3689,10 +3695,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3712,10 +3718,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C97" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3735,19 +3741,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F98">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G98">
         <v>100</v>
@@ -3758,10 +3764,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C99" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3781,19 +3787,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C100" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F100">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3804,19 +3810,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C101" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3827,10 +3833,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3850,10 +3856,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C103" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3873,10 +3879,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C104" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3896,10 +3902,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C105" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3919,10 +3925,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C106" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3942,10 +3948,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C107" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3965,19 +3971,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C108" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F108">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3988,10 +3994,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C109" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -4011,19 +4017,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C110" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F110">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -4034,10 +4040,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C111" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4057,10 +4063,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -4080,10 +4086,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C113" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -4103,10 +4109,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C114" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4126,10 +4132,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C115" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4152,7 +4158,7 @@
         <v>187</v>
       </c>
       <c r="C116" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4172,10 +4178,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C117" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4195,10 +4201,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C118" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4218,10 +4224,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C119" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4241,10 +4247,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C120" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4264,10 +4270,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C121" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4287,10 +4293,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C122" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4310,10 +4316,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C123" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4333,10 +4339,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C124" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4356,10 +4362,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C125" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4379,10 +4385,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C126" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4402,10 +4408,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C127" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4425,10 +4431,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C128" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4448,10 +4454,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C129" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4471,10 +4477,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C130" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -4494,10 +4500,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C131" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -4517,10 +4523,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C132" t="s">
-        <v>236</v>
+        <v>329</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4540,10 +4546,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C133" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4563,19 +4569,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C134" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F134">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4586,19 +4592,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C135" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F135">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4609,10 +4615,10 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C136" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -4632,19 +4638,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C137" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F137">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4655,10 +4661,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C138" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4678,19 +4684,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C139" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4701,19 +4707,19 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C140" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E140">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F140">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G140">
         <v>100</v>
@@ -4724,10 +4730,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C141" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4747,10 +4753,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C142" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4770,19 +4776,19 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C143" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F143">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G143">
         <v>100</v>
@@ -4793,19 +4799,19 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C144" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F144">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -4816,10 +4822,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C145" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4839,10 +4845,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C146" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4862,10 +4868,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C147" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4885,10 +4891,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C148" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -4908,10 +4914,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C149" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -4931,10 +4937,10 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C150" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -4954,19 +4960,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C151" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F151">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G151">
         <v>100</v>
@@ -4977,19 +4983,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C152" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E152">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F152">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G152">
         <v>100</v>
@@ -5000,19 +5006,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C153" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F153">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -5023,10 +5029,10 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C154" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D154">
         <v>2</v>
@@ -5046,10 +5052,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C155" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -5069,10 +5075,10 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C156" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -5092,10 +5098,10 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C157" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -5115,10 +5121,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C158" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5138,19 +5144,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C159" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F159">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G159">
         <v>100</v>
@@ -5161,19 +5167,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C160" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F160">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G160">
         <v>100</v>
@@ -5184,10 +5190,10 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C161" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -5207,10 +5213,10 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C162" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D162">
         <v>3</v>
@@ -5230,19 +5236,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C163" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D163">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E163">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F163">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G163">
         <v>100</v>
@@ -5253,19 +5259,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C164" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F164">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G164">
         <v>100</v>
@@ -5276,10 +5282,10 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C165" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5299,10 +5305,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C166" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -5322,10 +5328,10 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -5345,10 +5351,10 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C168" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -5368,10 +5374,10 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C169" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D169">
         <v>3</v>
@@ -5391,10 +5397,10 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C170" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -5414,19 +5420,19 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F171">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -5437,19 +5443,19 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C172" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E172">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F172">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G172">
         <v>100</v>
@@ -5460,10 +5466,10 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C173" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5483,19 +5489,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C174" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F174">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G174">
         <v>100</v>
@@ -5506,19 +5512,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C175" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F175">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G175">
         <v>100</v>
@@ -5529,10 +5535,10 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C176" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -5552,19 +5558,19 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C177" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E177">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F177">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G177">
         <v>100</v>
@@ -5575,19 +5581,19 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C178" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E178">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F178">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G178">
         <v>100</v>
@@ -5598,10 +5604,10 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C179" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -5613,6 +5619,29 @@
         <v>44</v>
       </c>
       <c r="G179">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" t="s">
+        <v>194</v>
+      </c>
+      <c r="C180" t="s">
+        <v>376</v>
+      </c>
+      <c r="D180">
+        <v>4</v>
+      </c>
+      <c r="E180">
+        <v>176</v>
+      </c>
+      <c r="F180">
+        <v>176</v>
+      </c>
+      <c r="G180">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="379">
   <si>
     <t>clues</t>
   </si>
@@ -64,513 +64,516 @@
     <t>MCIMB004122</t>
   </si>
   <si>
+    <t>OCIMB002392</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>ZSIMB001385</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>VZIMB007855</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB001642</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
     <t>NTIMB001700</t>
   </si>
   <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>OCIMB002392</t>
-  </si>
-  <si>
-    <t>ZSIMB001385</t>
-  </si>
-  <si>
-    <t>VZIMB007855</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>MCIMB009524</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
   </si>
   <si>
     <t>MCIMB007226</t>
   </si>
   <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
   </si>
   <si>
     <t>NTIMB000184</t>
   </si>
   <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>NTIMB001613</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
   </si>
   <si>
     <t>QRIMB001524</t>
   </si>
   <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
     <t>QRIMB001676</t>
   </si>
   <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
     <t>SPIMB002731</t>
   </si>
   <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB000831</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
   </si>
   <si>
     <t>TSIMB003046</t>
   </si>
   <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB000831</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
     <t>TSIMB003372</t>
   </si>
   <si>
     <t>TSIMB001144</t>
   </si>
   <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
     <t>VZIMB002890</t>
   </si>
   <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
   </si>
   <si>
     <t>VZIMB007505</t>
   </si>
   <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -589,21 +592,21 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
+    <t>ZACATECAS</t>
+  </si>
+  <si>
+    <t>CHIAPAS</t>
+  </si>
+  <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>NAYARIT</t>
   </si>
   <si>
-    <t>OAXACA</t>
-  </si>
-  <si>
-    <t>ZACATECAS</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>CHIAPAS</t>
-  </si>
-  <si>
     <t>SAN LUIS POTOSI</t>
   </si>
   <si>
@@ -640,508 +643,511 @@
     <t>LA COLMENA</t>
   </si>
   <si>
+    <t>SAN JUAN YUTA</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN JUAN CAPISTRANO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>LO DE MARCOS</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
     <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>SAN JUAN YUTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN JUAN CAPISTRANO</t>
-  </si>
-  <si>
-    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NAUCALPAN</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
   </si>
   <si>
     <t>SAN PABLO DE LAS SALINAS</t>
   </si>
   <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
   </si>
   <si>
     <t>UZETA</t>
   </si>
   <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL EL TESORO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD LOS MAGUEYES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. LAS BRISAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
   </si>
   <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
     <t>CHICHIGAPA</t>
   </si>
   <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1502,7 +1508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1533,10 +1539,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1556,10 +1562,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1579,10 +1585,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1602,10 +1608,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1625,10 +1631,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1648,10 +1654,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1671,10 +1677,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1694,10 +1700,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1717,10 +1723,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1740,22 +1746,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>44</v>
       </c>
       <c r="G11">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1763,10 +1769,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1786,10 +1792,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1809,10 +1815,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1832,22 +1838,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>44</v>
       </c>
       <c r="G15">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1855,10 +1861,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1878,22 +1884,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>44</v>
       </c>
       <c r="G17">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1901,22 +1907,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>44</v>
       </c>
       <c r="G18">
-        <v>15.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1924,22 +1930,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G19">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1947,22 +1953,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G20">
-        <v>21.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1970,22 +1976,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <v>44</v>
       </c>
       <c r="G21">
-        <v>31.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1993,22 +1999,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>43.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2016,22 +2022,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>47.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2039,22 +2045,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G24">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2062,22 +2068,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2085,22 +2091,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2111,19 +2117,19 @@
         <v>197</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2131,22 +2137,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2154,22 +2160,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F29">
         <v>44</v>
       </c>
       <c r="G29">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2177,22 +2183,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30">
         <v>44</v>
       </c>
       <c r="G30">
-        <v>81.8</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2200,22 +2206,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C31" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="F31">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G31">
-        <v>84.09999999999999</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2226,19 +2232,19 @@
         <v>196</v>
       </c>
       <c r="C32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="F32">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2246,22 +2252,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F33">
         <v>44</v>
       </c>
       <c r="G33">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2272,19 +2278,19 @@
         <v>188</v>
       </c>
       <c r="C34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>42</v>
+        <v>343</v>
       </c>
       <c r="F34">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G34">
-        <v>95.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2292,22 +2298,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C35" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>343</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="G35">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2315,10 +2321,10 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2338,10 +2344,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2364,7 +2370,7 @@
         <v>196</v>
       </c>
       <c r="C38" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2387,7 +2393,7 @@
         <v>188</v>
       </c>
       <c r="C39" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2407,22 +2413,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F40">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G40">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2433,7 +2439,7 @@
         <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -2453,10 +2459,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2476,10 +2482,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2499,22 +2505,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F44">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G44">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2522,22 +2528,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F45">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G45">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2545,10 +2551,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2568,10 +2574,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -2591,22 +2597,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C48" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F48">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G48">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2614,10 +2620,10 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -2637,22 +2643,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>219</v>
+        <v>615</v>
       </c>
       <c r="F50">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G50">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2660,22 +2666,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D51">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F51">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G51">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2683,10 +2689,10 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2706,19 +2712,19 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F53">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G53">
         <v>100</v>
@@ -2729,10 +2735,10 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2752,10 +2758,10 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2775,10 +2781,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2798,10 +2804,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2821,10 +2827,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C58" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2844,10 +2850,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2867,10 +2873,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2890,10 +2896,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2913,10 +2919,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C62" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -2936,10 +2942,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2959,10 +2965,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D64">
         <v>6</v>
@@ -2982,10 +2988,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3005,10 +3011,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3028,10 +3034,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3051,10 +3057,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3074,10 +3080,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3097,10 +3103,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3120,10 +3126,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3143,10 +3149,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3166,10 +3172,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3189,10 +3195,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3212,10 +3218,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3235,10 +3241,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3258,10 +3264,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3281,10 +3287,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C78" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3304,10 +3310,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3327,10 +3333,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3350,10 +3356,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3373,10 +3379,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C82" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3396,10 +3402,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3419,10 +3425,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C84" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3442,10 +3448,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C85" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3465,10 +3471,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3488,10 +3494,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3511,10 +3517,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3534,10 +3540,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3557,10 +3563,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C90" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3580,19 +3586,19 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C91" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F91">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G91">
         <v>100</v>
@@ -3603,10 +3609,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C92" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3626,19 +3632,19 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F93">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G93">
         <v>100</v>
@@ -3649,10 +3655,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3672,10 +3678,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3695,10 +3701,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C96" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3718,10 +3724,10 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C97" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3741,10 +3747,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C98" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3764,19 +3770,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F99">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3787,19 +3793,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C100" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F100">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G100">
         <v>100</v>
@@ -3810,10 +3816,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C101" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3833,10 +3839,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C102" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3856,10 +3862,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C103" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3879,10 +3885,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C104" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3902,10 +3908,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C105" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3925,19 +3931,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C106" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F106">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3948,19 +3954,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C107" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F107">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3971,19 +3977,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C108" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F108">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -3994,10 +4000,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C109" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -4017,19 +4023,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C110" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F110">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -4040,19 +4046,19 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F111">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G111">
         <v>100</v>
@@ -4063,19 +4069,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F112">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -4086,10 +4092,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C113" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -4109,10 +4115,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C114" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4135,16 +4141,16 @@
         <v>188</v>
       </c>
       <c r="C115" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F115">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -4155,10 +4161,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C116" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4178,10 +4184,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C117" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4201,10 +4207,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C118" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4224,10 +4230,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C119" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4247,10 +4253,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C120" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4270,10 +4276,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C121" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4293,10 +4299,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C122" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4316,10 +4322,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C123" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4339,10 +4345,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C124" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4362,10 +4368,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C125" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4385,10 +4391,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C126" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4408,10 +4414,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C127" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4431,10 +4437,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C128" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4454,10 +4460,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C129" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4477,10 +4483,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C130" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -4500,10 +4506,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C131" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -4523,10 +4529,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C132" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4546,10 +4552,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C133" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4569,19 +4575,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C134" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F134">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4592,19 +4598,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C135" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4615,19 +4621,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C136" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4638,19 +4644,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C137" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F137">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4661,10 +4667,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C138" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4684,10 +4690,10 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C139" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4707,10 +4713,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C140" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4730,10 +4736,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C141" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4753,10 +4759,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C142" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4776,10 +4782,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C143" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4799,19 +4805,19 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C144" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F144">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -4822,19 +4828,19 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C145" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F145">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G145">
         <v>100</v>
@@ -4845,10 +4851,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C146" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4868,10 +4874,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C147" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4891,10 +4897,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C148" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -4914,10 +4920,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C149" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -4937,19 +4943,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C150" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E150">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F150">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G150">
         <v>100</v>
@@ -4960,10 +4966,10 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C151" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -4983,10 +4989,10 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C152" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -5006,19 +5012,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C153" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E153">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F153">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -5029,19 +5035,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C154" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F154">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G154">
         <v>100</v>
@@ -5052,10 +5058,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C155" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -5075,10 +5081,10 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C156" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -5098,19 +5104,19 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C157" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F157">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G157">
         <v>100</v>
@@ -5121,10 +5127,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C158" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5144,10 +5150,10 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C159" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -5167,19 +5173,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C160" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F160">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G160">
         <v>100</v>
@@ -5190,10 +5196,10 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C161" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -5213,10 +5219,10 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C162" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D162">
         <v>3</v>
@@ -5236,10 +5242,10 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C163" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -5259,19 +5265,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C164" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F164">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G164">
         <v>100</v>
@@ -5282,19 +5288,19 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C165" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F165">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G165">
         <v>100</v>
@@ -5305,10 +5311,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C166" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -5328,10 +5334,10 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C167" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -5351,19 +5357,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C168" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F168">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G168">
         <v>100</v>
@@ -5374,19 +5380,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C169" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E169">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F169">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G169">
         <v>100</v>
@@ -5397,19 +5403,19 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C170" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F170">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G170">
         <v>100</v>
@@ -5420,19 +5426,19 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C171" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D171">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F171">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -5443,10 +5449,10 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -5466,10 +5472,10 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C173" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5489,19 +5495,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C174" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F174">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G174">
         <v>100</v>
@@ -5512,10 +5518,10 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C175" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -5535,19 +5541,19 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C176" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E176">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F176">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G176">
         <v>100</v>
@@ -5558,10 +5564,10 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C177" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D177">
         <v>3</v>
@@ -5581,10 +5587,10 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C178" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -5604,10 +5610,10 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C179" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -5627,21 +5633,44 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C180" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D180">
+        <v>2</v>
+      </c>
+      <c r="E180">
+        <v>88</v>
+      </c>
+      <c r="F180">
+        <v>88</v>
+      </c>
+      <c r="G180">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" t="s">
+        <v>195</v>
+      </c>
+      <c r="C181" t="s">
+        <v>378</v>
+      </c>
+      <c r="D181">
         <v>4</v>
       </c>
-      <c r="E180">
+      <c r="E181">
         <v>176</v>
       </c>
-      <c r="F180">
+      <c r="F181">
         <v>176</v>
       </c>
-      <c r="G180">
+      <c r="G181">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="441">
   <si>
     <t>clues</t>
   </si>
@@ -46,532 +46,625 @@
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>QRIMB001536</t>
+  </si>
+  <si>
+    <t>QRIMB001775</t>
+  </si>
+  <si>
+    <t>BSIMB000030</t>
+  </si>
+  <si>
+    <t>MNIMB001316</t>
+  </si>
+  <si>
+    <t>MCIMB004122</t>
+  </si>
+  <si>
+    <t>OCIMB002392</t>
+  </si>
+  <si>
+    <t>MCIMB008602</t>
+  </si>
+  <si>
+    <t>BSIMB000136</t>
+  </si>
+  <si>
+    <t>MCIMB003591</t>
+  </si>
+  <si>
+    <t>ZSIMB001385</t>
+  </si>
+  <si>
+    <t>VZIMB007855</t>
+  </si>
+  <si>
+    <t>CSIMB003651</t>
+  </si>
+  <si>
+    <t>MCIMB000943</t>
+  </si>
+  <si>
+    <t>MCIMB008293</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB011962</t>
+  </si>
+  <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB011180</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>MCIMB000716</t>
+  </si>
+  <si>
+    <t>MCIMB006905</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB006642</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB000733</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB008585</t>
+  </si>
+  <si>
+    <t>MCIMB008573</t>
+  </si>
+  <si>
+    <t>MCIMB008544</t>
+  </si>
+  <si>
+    <t>MCIMB008520</t>
+  </si>
+  <si>
+    <t>MCIMB008532</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006876</t>
+  </si>
+  <si>
+    <t>MCIMB006910</t>
+  </si>
+  <si>
+    <t>MCIMB006934</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001642</t>
+  </si>
+  <si>
+    <t>NTIMB001671</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
     <t>MCIMB008800</t>
   </si>
   <si>
-    <t>QRIMB001775</t>
-  </si>
-  <si>
-    <t>QRIMB001536</t>
-  </si>
-  <si>
-    <t>MNIMB001316</t>
-  </si>
-  <si>
-    <t>BSIMB000030</t>
-  </si>
-  <si>
-    <t>MCIMB004122</t>
-  </si>
-  <si>
-    <t>OCIMB002392</t>
-  </si>
-  <si>
-    <t>MCIMB003591</t>
-  </si>
-  <si>
-    <t>BSIMB000136</t>
-  </si>
-  <si>
-    <t>ZSIMB001385</t>
-  </si>
-  <si>
-    <t>CSIMB003651</t>
-  </si>
-  <si>
-    <t>VZIMB007855</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>NTIMB001700</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006852</t>
   </si>
   <si>
     <t>MCIMB006835</t>
   </si>
   <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>MCIMB009524</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
+    <t>MCIMB006823</t>
+  </si>
+  <si>
+    <t>MCIMB006811</t>
+  </si>
+  <si>
+    <t>MCIMB006922</t>
+  </si>
+  <si>
+    <t>MCIMB000692</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
   </si>
   <si>
     <t>MCIMB003801</t>
   </si>
   <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001613</t>
-  </si>
-  <si>
-    <t>NTIMB001642</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001372</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB001051</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
   </si>
   <si>
     <t>QRIMB000136</t>
   </si>
   <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
     <t>QRIMB000240</t>
   </si>
   <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>NTIMB001700</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000835</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB001144</t>
+  </si>
+  <si>
+    <t>TSIMB002585</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001482</t>
+  </si>
+  <si>
+    <t>TSIMB003372</t>
+  </si>
+  <si>
+    <t>TSIMB003343</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
   </si>
   <si>
     <t>QRIMB001483</t>
   </si>
   <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
+    <t>VZIMB002400</t>
   </si>
   <si>
     <t>VZIMB002366</t>
   </si>
   <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
     <t>VZIMB000831</t>
   </si>
   <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
     <t>TSIMB003401</t>
   </si>
   <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB003372</t>
-  </si>
-  <si>
-    <t>TSIMB001144</t>
+    <t>TSIMB003384</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
   </si>
   <si>
     <t>VZIMB002885</t>
   </si>
   <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
     <t>VZIMB007616</t>
   </si>
   <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
+    <t>VZIMB007831</t>
   </si>
   <si>
     <t>VZIMB007942</t>
@@ -586,24 +679,24 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
     <t>OAXACA</t>
   </si>
   <si>
     <t>ZACATECAS</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>CHIAPAS</t>
   </si>
   <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
     <t>NAYARIT</t>
   </si>
   <si>
@@ -625,529 +718,622 @@
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ACALPICAN</t>
+  </si>
+  <si>
+    <t>LA COLMENA</t>
+  </si>
+  <si>
+    <t>SAN JUAN YUTA</t>
+  </si>
+  <si>
+    <t>SAUZ PALO GORDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOME TLALTELULCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN JUAN CAPISTRANO</t>
+  </si>
+  <si>
+    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
+  </si>
+  <si>
+    <t>SAN MARTÍN DE PORRES</t>
+  </si>
+  <si>
+    <t>CALIMAYA NORTE</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>CEAPS SAN ANTONIO LA ISLA LEONARDO BRAVO BICENTENARIO</t>
+  </si>
+  <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>CEAPS SANTA MARÍA RAYÓN BICENTENARIO</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>PALMAR CHICO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO LIMON</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN MARTÍN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>EL REPARO</t>
+  </si>
+  <si>
+    <t>PALO GORDO</t>
+  </si>
+  <si>
+    <t>EL VALLECITO DE COAHUILOTES</t>
+  </si>
+  <si>
+    <t>HERMILTEPEC</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN JUAN CORRAL</t>
+  </si>
+  <si>
+    <t>SANTA ANA ZICATECOYAN</t>
+  </si>
+  <si>
+    <t>TLACOCUSPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>LO DE MARCOS</t>
+  </si>
+  <si>
+    <t>SAN JUAN DE ABAJO</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
     <t>SANTA MARÍA OZUMBILLA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ACALPICAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>LA COLMENA</t>
-  </si>
-  <si>
-    <t>SAN JUAN YUTA</t>
-  </si>
-  <si>
-    <t>SAN BARTOLOME TLALTELULCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN JUAN CAPISTRANO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
-  </si>
-  <si>
-    <t>BOCA DEL RÍO EJIDO 1° DE MAYO</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DE ASIS</t>
   </si>
   <si>
     <t>PALMAR GRANDE</t>
   </si>
   <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NAUCALPAN</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
+    <t>NUEVO COPALTEPEC</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA</t>
+  </si>
+  <si>
+    <t>CINCUENTA ARROBAS</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
   </si>
   <si>
     <t>SAN MATEO (LA PRESA)</t>
   </si>
   <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
-  </si>
-  <si>
-    <t>LO DE MARCOS</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL POLYUC</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL X-PICHIL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LA SOLEDAD</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
   </si>
   <si>
     <t>CENTRO DE SALUD URBANO TULUM</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
     <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
   </si>
   <si>
     <t>LA CONCEPCIÓN</t>
   </si>
   <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
     <t>EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
+    <t>ZAPOAPAN</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1508,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1539,10 +1725,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1562,10 +1748,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1585,10 +1771,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1608,10 +1794,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1631,10 +1817,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1654,22 +1840,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>44</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1677,10 +1863,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1700,22 +1886,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>44</v>
       </c>
       <c r="G9">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1723,22 +1909,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>44</v>
       </c>
       <c r="G10">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1746,10 +1932,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1769,10 +1955,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1792,10 +1978,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1815,10 +2001,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1838,10 +2024,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1861,10 +2047,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1884,10 +2070,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1907,22 +2093,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>44</v>
       </c>
       <c r="G18">
-        <v>18.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1930,22 +2116,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>21.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1953,22 +2139,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G20">
-        <v>31.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1976,22 +2162,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="C21" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F21">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G21">
-        <v>43.2</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1999,22 +2185,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>47.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2022,22 +2208,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="C23" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>52.3</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2045,22 +2231,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>53.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2068,22 +2254,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F25">
         <v>44</v>
       </c>
       <c r="G25">
-        <v>63.6</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2091,22 +2277,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>68.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2114,22 +2300,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="F27">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G27">
-        <v>70.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2137,22 +2323,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F28">
         <v>44</v>
       </c>
       <c r="G28">
-        <v>79.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2160,22 +2346,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F29">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2183,22 +2369,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C30" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F30">
         <v>44</v>
       </c>
       <c r="G30">
-        <v>84.09999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2206,22 +2392,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="F31">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G31">
-        <v>87.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2229,22 +2415,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2252,22 +2438,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="C33" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="F33">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G33">
-        <v>95.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2275,22 +2461,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C34" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>343</v>
+        <v>40</v>
       </c>
       <c r="F34">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="G34">
-        <v>97.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2298,22 +2484,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="C35" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35">
         <v>44</v>
       </c>
       <c r="G35">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2321,22 +2507,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C36" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>43</v>
+        <v>343</v>
       </c>
       <c r="F36">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G36">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2344,10 +2530,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2367,10 +2553,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2390,10 +2576,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2413,22 +2599,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F40">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G40">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2436,22 +2622,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C41" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="F41">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G41">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2459,22 +2645,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="D42">
         <v>2</v>
       </c>
       <c r="E42">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F42">
         <v>88</v>
       </c>
       <c r="G42">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2482,22 +2668,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C43" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="D43">
         <v>2</v>
       </c>
       <c r="E43">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F43">
         <v>88</v>
       </c>
       <c r="G43">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2505,22 +2691,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C44" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F44">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G44">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2528,22 +2714,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C45" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F45">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G45">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2551,22 +2737,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F46">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G46">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2574,22 +2760,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="C47" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="F47">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="G47">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2597,22 +2783,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="F48">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="G48">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2620,22 +2806,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F49">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G49">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2643,22 +2829,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>615</v>
+        <v>175</v>
       </c>
       <c r="F50">
-        <v>616</v>
+        <v>176</v>
       </c>
       <c r="G50">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2666,22 +2852,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C51" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="F51">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2689,22 +2875,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C52" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="F52">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2712,22 +2898,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C53" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="F53">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G53">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2735,22 +2921,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="C54" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E54">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F54">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G54">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2758,19 +2944,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C55" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F55">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G55">
         <v>100</v>
@@ -2781,10 +2967,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2804,19 +2990,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C57" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -2827,10 +3013,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C58" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2850,19 +3036,19 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C59" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F59">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G59">
         <v>100</v>
@@ -2873,10 +3059,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C60" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2896,10 +3082,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2919,19 +3105,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C62" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="D62">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -2942,19 +3128,19 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F63">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G63">
         <v>100</v>
@@ -2965,19 +3151,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C64" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F64">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G64">
         <v>100</v>
@@ -2988,10 +3174,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3011,10 +3197,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3034,10 +3220,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3057,10 +3243,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C68" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3080,19 +3266,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F69">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G69">
         <v>100</v>
@@ -3103,10 +3289,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C70" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3126,10 +3312,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C71" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3149,19 +3335,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C72" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F72">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -3172,10 +3358,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C73" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3195,10 +3381,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C74" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3218,10 +3404,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C75" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3241,10 +3427,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C76" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3264,10 +3450,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3287,10 +3473,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C78" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3310,10 +3496,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C79" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3333,10 +3519,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C80" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3356,10 +3542,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C81" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3379,10 +3565,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C82" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3402,10 +3588,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C83" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3425,19 +3611,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C84" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F84">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3448,10 +3634,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C85" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3471,10 +3657,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C86" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3494,10 +3680,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C87" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3517,10 +3703,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C88" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3540,10 +3726,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3563,10 +3749,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C90" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3586,10 +3772,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C91" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3609,10 +3795,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C92" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3632,19 +3818,19 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C93" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F93">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G93">
         <v>100</v>
@@ -3655,10 +3841,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C94" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3678,10 +3864,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C95" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3701,10 +3887,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C96" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3724,19 +3910,19 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C97" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="F97">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G97">
         <v>100</v>
@@ -3747,10 +3933,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C98" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3770,19 +3956,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C99" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F99">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G99">
         <v>100</v>
@@ -3793,10 +3979,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3816,19 +4002,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C101" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -3839,10 +4025,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C102" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3862,10 +4048,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C103" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3885,10 +4071,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C104" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3908,10 +4094,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="C105" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3931,19 +4117,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C106" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F106">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G106">
         <v>100</v>
@@ -3954,19 +4140,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C107" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F107">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G107">
         <v>100</v>
@@ -3977,19 +4163,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C108" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F108">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -4000,19 +4186,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C109" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E109">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="F109">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -4023,10 +4209,10 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C110" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -4046,19 +4232,19 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F111">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G111">
         <v>100</v>
@@ -4069,10 +4255,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -4092,19 +4278,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C113" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E113">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="F113">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -4115,10 +4301,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C114" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4138,19 +4324,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C115" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E115">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F115">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -4161,10 +4347,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C116" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4184,10 +4370,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C117" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4207,10 +4393,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C118" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4230,10 +4416,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C119" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4253,10 +4439,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C120" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4276,10 +4462,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C121" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4299,10 +4485,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C122" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4322,19 +4508,19 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C123" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F123">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G123">
         <v>100</v>
@@ -4345,10 +4531,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C124" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4368,10 +4554,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C125" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4391,10 +4577,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="C126" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4414,10 +4600,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C127" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4437,10 +4623,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C128" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4460,10 +4646,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C129" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4483,19 +4669,19 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C130" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F130">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G130">
         <v>100</v>
@@ -4506,19 +4692,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C131" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4529,10 +4715,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C132" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4552,19 +4738,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C133" t="s">
-        <v>238</v>
+        <v>362</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F133">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G133">
         <v>100</v>
@@ -4575,10 +4761,10 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C134" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -4598,19 +4784,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C135" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F135">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4621,19 +4807,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C136" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F136">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4644,19 +4830,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C137" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F137">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4667,10 +4853,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C138" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4690,10 +4876,10 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C139" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4713,19 +4899,19 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C140" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F140">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G140">
         <v>100</v>
@@ -4736,10 +4922,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C141" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4759,10 +4945,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C142" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4782,10 +4968,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C143" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4805,10 +4991,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C144" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4828,19 +5014,19 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C145" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="D145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F145">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G145">
         <v>100</v>
@@ -4851,10 +5037,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C146" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4874,10 +5060,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C147" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4897,10 +5083,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C148" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -4920,10 +5106,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C149" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -4943,19 +5129,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C150" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E150">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F150">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G150">
         <v>100</v>
@@ -4966,10 +5152,10 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C151" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -4989,10 +5175,10 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C152" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -5012,10 +5198,10 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C153" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -5035,19 +5221,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C154" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F154">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G154">
         <v>100</v>
@@ -5058,10 +5244,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C155" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -5081,19 +5267,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C156" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F156">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G156">
         <v>100</v>
@@ -5104,19 +5290,19 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C157" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F157">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G157">
         <v>100</v>
@@ -5127,10 +5313,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C158" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5150,10 +5336,10 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C159" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -5173,19 +5359,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C160" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F160">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G160">
         <v>100</v>
@@ -5196,10 +5382,10 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C161" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -5219,19 +5405,19 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C162" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="D162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F162">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G162">
         <v>100</v>
@@ -5242,19 +5428,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C163" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F163">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G163">
         <v>100</v>
@@ -5265,10 +5451,10 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C164" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -5288,19 +5474,19 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C165" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F165">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G165">
         <v>100</v>
@@ -5311,10 +5497,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C166" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -5334,19 +5520,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C167" t="s">
-        <v>364</v>
+        <v>274</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F167">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G167">
         <v>100</v>
@@ -5357,19 +5543,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C168" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F168">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G168">
         <v>100</v>
@@ -5380,19 +5566,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C169" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F169">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G169">
         <v>100</v>
@@ -5403,19 +5589,19 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C170" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="D170">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F170">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G170">
         <v>100</v>
@@ -5426,10 +5612,10 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C171" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -5449,10 +5635,10 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C172" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -5472,10 +5658,10 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C173" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5495,10 +5681,10 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C174" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -5518,10 +5704,10 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="C175" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -5541,19 +5727,19 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C176" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="D176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E176">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F176">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G176">
         <v>100</v>
@@ -5564,19 +5750,19 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C177" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="D177">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E177">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F177">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G177">
         <v>100</v>
@@ -5587,10 +5773,10 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C178" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -5610,19 +5796,19 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C179" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E179">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F179">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G179">
         <v>100</v>
@@ -5633,19 +5819,19 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C180" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F180">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G180">
         <v>100</v>
@@ -5656,21 +5842,734 @@
         <v>186</v>
       </c>
       <c r="B181" t="s">
+        <v>230</v>
+      </c>
+      <c r="C181" t="s">
+        <v>409</v>
+      </c>
+      <c r="D181">
+        <v>2</v>
+      </c>
+      <c r="E181">
+        <v>88</v>
+      </c>
+      <c r="F181">
+        <v>88</v>
+      </c>
+      <c r="G181">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182" t="s">
+        <v>230</v>
+      </c>
+      <c r="C182" t="s">
+        <v>410</v>
+      </c>
+      <c r="D182">
+        <v>2</v>
+      </c>
+      <c r="E182">
+        <v>88</v>
+      </c>
+      <c r="F182">
+        <v>88</v>
+      </c>
+      <c r="G182">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" t="s">
+        <v>230</v>
+      </c>
+      <c r="C183" t="s">
+        <v>411</v>
+      </c>
+      <c r="D183">
+        <v>2</v>
+      </c>
+      <c r="E183">
+        <v>88</v>
+      </c>
+      <c r="F183">
+        <v>88</v>
+      </c>
+      <c r="G183">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184" t="s">
+        <v>230</v>
+      </c>
+      <c r="C184" t="s">
+        <v>412</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>44</v>
+      </c>
+      <c r="F184">
+        <v>44</v>
+      </c>
+      <c r="G184">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" t="s">
+        <v>230</v>
+      </c>
+      <c r="C185" t="s">
+        <v>413</v>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>44</v>
+      </c>
+      <c r="F185">
+        <v>44</v>
+      </c>
+      <c r="G185">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>191</v>
+      </c>
+      <c r="B186" t="s">
+        <v>230</v>
+      </c>
+      <c r="C186" t="s">
+        <v>414</v>
+      </c>
+      <c r="D186">
+        <v>2</v>
+      </c>
+      <c r="E186">
+        <v>88</v>
+      </c>
+      <c r="F186">
+        <v>88</v>
+      </c>
+      <c r="G186">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>192</v>
+      </c>
+      <c r="B187" t="s">
+        <v>230</v>
+      </c>
+      <c r="C187" t="s">
+        <v>415</v>
+      </c>
+      <c r="D187">
+        <v>2</v>
+      </c>
+      <c r="E187">
+        <v>88</v>
+      </c>
+      <c r="F187">
+        <v>88</v>
+      </c>
+      <c r="G187">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>193</v>
+      </c>
+      <c r="B188" t="s">
+        <v>220</v>
+      </c>
+      <c r="C188" t="s">
+        <v>416</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188">
+        <v>44</v>
+      </c>
+      <c r="F188">
+        <v>44</v>
+      </c>
+      <c r="G188">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" t="s">
+        <v>220</v>
+      </c>
+      <c r="C189" t="s">
+        <v>417</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>44</v>
+      </c>
+      <c r="F189">
+        <v>44</v>
+      </c>
+      <c r="G189">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
         <v>195</v>
       </c>
-      <c r="C181" t="s">
-        <v>378</v>
-      </c>
-      <c r="D181">
+      <c r="B190" t="s">
+        <v>220</v>
+      </c>
+      <c r="C190" t="s">
+        <v>418</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>44</v>
+      </c>
+      <c r="F190">
+        <v>44</v>
+      </c>
+      <c r="G190">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>196</v>
+      </c>
+      <c r="B191" t="s">
+        <v>220</v>
+      </c>
+      <c r="C191" t="s">
+        <v>419</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191">
+        <v>44</v>
+      </c>
+      <c r="F191">
+        <v>44</v>
+      </c>
+      <c r="G191">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B192" t="s">
+        <v>220</v>
+      </c>
+      <c r="C192" t="s">
+        <v>420</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192">
+        <v>44</v>
+      </c>
+      <c r="F192">
+        <v>44</v>
+      </c>
+      <c r="G192">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>198</v>
+      </c>
+      <c r="B193" t="s">
+        <v>220</v>
+      </c>
+      <c r="C193" t="s">
+        <v>421</v>
+      </c>
+      <c r="D193">
+        <v>2</v>
+      </c>
+      <c r="E193">
+        <v>88</v>
+      </c>
+      <c r="F193">
+        <v>88</v>
+      </c>
+      <c r="G193">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>199</v>
+      </c>
+      <c r="B194" t="s">
+        <v>225</v>
+      </c>
+      <c r="C194" t="s">
+        <v>422</v>
+      </c>
+      <c r="D194">
+        <v>3</v>
+      </c>
+      <c r="E194">
+        <v>132</v>
+      </c>
+      <c r="F194">
+        <v>132</v>
+      </c>
+      <c r="G194">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>200</v>
+      </c>
+      <c r="B195" t="s">
+        <v>225</v>
+      </c>
+      <c r="C195" t="s">
+        <v>423</v>
+      </c>
+      <c r="D195">
+        <v>3</v>
+      </c>
+      <c r="E195">
+        <v>132</v>
+      </c>
+      <c r="F195">
+        <v>132</v>
+      </c>
+      <c r="G195">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>201</v>
+      </c>
+      <c r="B196" t="s">
+        <v>230</v>
+      </c>
+      <c r="C196" t="s">
+        <v>424</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196">
+        <v>44</v>
+      </c>
+      <c r="F196">
+        <v>44</v>
+      </c>
+      <c r="G196">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" t="s">
+        <v>225</v>
+      </c>
+      <c r="C197" t="s">
+        <v>425</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197">
+        <v>44</v>
+      </c>
+      <c r="F197">
+        <v>44</v>
+      </c>
+      <c r="G197">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>203</v>
+      </c>
+      <c r="B198" t="s">
+        <v>230</v>
+      </c>
+      <c r="C198" t="s">
+        <v>426</v>
+      </c>
+      <c r="D198">
+        <v>2</v>
+      </c>
+      <c r="E198">
+        <v>88</v>
+      </c>
+      <c r="F198">
+        <v>88</v>
+      </c>
+      <c r="G198">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>204</v>
+      </c>
+      <c r="B199" t="s">
+        <v>230</v>
+      </c>
+      <c r="C199" t="s">
+        <v>427</v>
+      </c>
+      <c r="D199">
+        <v>2</v>
+      </c>
+      <c r="E199">
+        <v>88</v>
+      </c>
+      <c r="F199">
+        <v>88</v>
+      </c>
+      <c r="G199">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>205</v>
+      </c>
+      <c r="B200" t="s">
+        <v>225</v>
+      </c>
+      <c r="C200" t="s">
+        <v>428</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="E200">
+        <v>44</v>
+      </c>
+      <c r="F200">
+        <v>44</v>
+      </c>
+      <c r="G200">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>206</v>
+      </c>
+      <c r="B201" t="s">
+        <v>225</v>
+      </c>
+      <c r="C201" t="s">
+        <v>429</v>
+      </c>
+      <c r="D201">
+        <v>3</v>
+      </c>
+      <c r="E201">
+        <v>132</v>
+      </c>
+      <c r="F201">
+        <v>132</v>
+      </c>
+      <c r="G201">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>207</v>
+      </c>
+      <c r="B202" t="s">
+        <v>225</v>
+      </c>
+      <c r="C202" t="s">
+        <v>430</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>44</v>
+      </c>
+      <c r="F202">
+        <v>44</v>
+      </c>
+      <c r="G202">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>208</v>
+      </c>
+      <c r="B203" t="s">
+        <v>225</v>
+      </c>
+      <c r="C203" t="s">
+        <v>431</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203">
+        <v>44</v>
+      </c>
+      <c r="F203">
+        <v>44</v>
+      </c>
+      <c r="G203">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>209</v>
+      </c>
+      <c r="B204" t="s">
+        <v>225</v>
+      </c>
+      <c r="C204" t="s">
+        <v>432</v>
+      </c>
+      <c r="D204">
+        <v>3</v>
+      </c>
+      <c r="E204">
+        <v>132</v>
+      </c>
+      <c r="F204">
+        <v>132</v>
+      </c>
+      <c r="G204">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
+        <v>210</v>
+      </c>
+      <c r="B205" t="s">
+        <v>225</v>
+      </c>
+      <c r="C205" t="s">
+        <v>433</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205">
+        <v>44</v>
+      </c>
+      <c r="F205">
+        <v>44</v>
+      </c>
+      <c r="G205">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>211</v>
+      </c>
+      <c r="B206" t="s">
+        <v>225</v>
+      </c>
+      <c r="C206" t="s">
+        <v>434</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>44</v>
+      </c>
+      <c r="F206">
+        <v>44</v>
+      </c>
+      <c r="G206">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>212</v>
+      </c>
+      <c r="B207" t="s">
+        <v>225</v>
+      </c>
+      <c r="C207" t="s">
+        <v>435</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+      <c r="E207">
+        <v>88</v>
+      </c>
+      <c r="F207">
+        <v>88</v>
+      </c>
+      <c r="G207">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>213</v>
+      </c>
+      <c r="B208" t="s">
+        <v>225</v>
+      </c>
+      <c r="C208" t="s">
+        <v>436</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>44</v>
+      </c>
+      <c r="F208">
+        <v>44</v>
+      </c>
+      <c r="G208">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>214</v>
+      </c>
+      <c r="B209" t="s">
+        <v>225</v>
+      </c>
+      <c r="C209" t="s">
+        <v>437</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>44</v>
+      </c>
+      <c r="F209">
+        <v>44</v>
+      </c>
+      <c r="G209">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>215</v>
+      </c>
+      <c r="B210" t="s">
+        <v>225</v>
+      </c>
+      <c r="C210" t="s">
+        <v>438</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>44</v>
+      </c>
+      <c r="F210">
+        <v>44</v>
+      </c>
+      <c r="G210">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" t="s">
+        <v>216</v>
+      </c>
+      <c r="B211" t="s">
+        <v>225</v>
+      </c>
+      <c r="C211" t="s">
+        <v>439</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>44</v>
+      </c>
+      <c r="F211">
+        <v>44</v>
+      </c>
+      <c r="G211">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" t="s">
+        <v>217</v>
+      </c>
+      <c r="B212" t="s">
+        <v>225</v>
+      </c>
+      <c r="C212" t="s">
+        <v>440</v>
+      </c>
+      <c r="D212">
         <v>4</v>
       </c>
-      <c r="E181">
+      <c r="E212">
         <v>176</v>
       </c>
-      <c r="F181">
+      <c r="F212">
         <v>176</v>
       </c>
-      <c r="G181">
+      <c r="G212">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="443">
   <si>
     <t>clues</t>
   </si>
@@ -106,6 +106,9 @@
     <t>VZIMB007160</t>
   </si>
   <si>
+    <t>MCIMB002512</t>
+  </si>
+  <si>
     <t>SPIMB002253</t>
   </si>
   <si>
@@ -145,528 +148,528 @@
     <t>SPIMB000445</t>
   </si>
   <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>MCIMB006905</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
     <t>NTIMB000126</t>
   </si>
   <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
+    <t>MCIMB000716</t>
   </si>
   <si>
     <t>QRIMB000474</t>
   </si>
   <si>
-    <t>MCIMB000716</t>
-  </si>
-  <si>
-    <t>MCIMB006905</t>
-  </si>
-  <si>
     <t>MCIMB008730</t>
   </si>
   <si>
     <t>SPIMB000450</t>
   </si>
   <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
     <t>QRIMB001652</t>
   </si>
   <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
     <t>SPIMB002661</t>
   </si>
   <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
     <t>SPIMB002562</t>
   </si>
   <si>
     <t>SPIMB003146</t>
   </si>
   <si>
-    <t>MCIMB003842</t>
+    <t>MCIMB007214</t>
   </si>
   <si>
     <t>MCIMB001503</t>
   </si>
   <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
     <t>VZIMB002395</t>
   </si>
   <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB006642</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
     <t>MCIMB004163</t>
   </si>
   <si>
-    <t>MCIMB006642</t>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB000733</t>
+  </si>
+  <si>
+    <t>MCIMB008585</t>
+  </si>
+  <si>
+    <t>MCIMB008573</t>
+  </si>
+  <si>
+    <t>MCIMB008544</t>
+  </si>
+  <si>
+    <t>MCIMB008532</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB008520</t>
+  </si>
+  <si>
+    <t>MCIMB006934</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006852</t>
+  </si>
+  <si>
+    <t>MCIMB006876</t>
+  </si>
+  <si>
+    <t>MCIMB006922</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB001642</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>NTIMB001700</t>
+  </si>
+  <si>
+    <t>NTIMB001671</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
   </si>
   <si>
     <t>MCIMB006654</t>
   </si>
   <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB000733</t>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB006823</t>
+  </si>
+  <si>
+    <t>MCIMB006811</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006910</t>
+  </si>
+  <si>
+    <t>MCIMB000692</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
   </si>
   <si>
     <t>BCIMB000990</t>
   </si>
   <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB008585</t>
-  </si>
-  <si>
-    <t>MCIMB008573</t>
-  </si>
-  <si>
-    <t>MCIMB008544</t>
-  </si>
-  <si>
-    <t>MCIMB008520</t>
-  </si>
-  <si>
-    <t>MCIMB008532</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006876</t>
-  </si>
-  <si>
-    <t>MCIMB006910</t>
-  </si>
-  <si>
-    <t>MCIMB006934</t>
-  </si>
-  <si>
-    <t>MCIMB009524</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001613</t>
-  </si>
-  <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>NTIMB001642</t>
-  </si>
-  <si>
-    <t>NTIMB001671</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>NTIMB001700</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>QRIMB001372</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB001051</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
   </si>
   <si>
     <t>QRIMB000054</t>
   </si>
   <si>
-    <t>NTIMB002050</t>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
   </si>
   <si>
     <t>QRIMB000141</t>
   </si>
   <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006852</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB006823</t>
-  </si>
-  <si>
-    <t>MCIMB006811</t>
-  </si>
-  <si>
-    <t>MCIMB006922</t>
-  </si>
-  <si>
-    <t>MCIMB000692</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000835</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB002585</t>
+  </si>
+  <si>
+    <t>TSIMB001482</t>
+  </si>
+  <si>
+    <t>TSIMB001144</t>
+  </si>
+  <si>
+    <t>TSIMB003343</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
   </si>
   <si>
     <t>QRIMB001430</t>
   </si>
   <si>
-    <t>QRIMB001372</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB001051</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000835</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB001144</t>
-  </si>
-  <si>
-    <t>TSIMB002585</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB001482</t>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB000831</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003384</t>
   </si>
   <si>
     <t>TSIMB003372</t>
   </si>
   <si>
-    <t>TSIMB003343</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
+    <t>VZIMB002890</t>
   </si>
   <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>VZIMB000831</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003384</t>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB003264</t>
   </si>
   <si>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
     <t>VZIMB002412</t>
   </si>
   <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
+    <t>VZIMB007831</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
   </si>
   <si>
     <t>VZIMB007604</t>
   </si>
   <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007831</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -778,6 +781,9 @@
     <t>CENTRO DE SALUD URSULO GALVÁN</t>
   </si>
   <si>
+    <t>COLONIA SANTA CRUZ TLAPACOYA</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD ROTARIOS</t>
   </si>
   <si>
@@ -817,523 +823,523 @@
     <t>AURELIO MANRIQUE</t>
   </si>
   <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO LIMON</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
     <t>VALLE DE LA URRACA</t>
   </si>
   <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+    <t>PALMAR CHICO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL LIMONES</t>
   </si>
   <si>
-    <t>PALMAR CHICO</t>
-  </si>
-  <si>
-    <t>SAN PEDRO LIMON</t>
-  </si>
-  <si>
     <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
   </si>
   <si>
     <t>PONCIANO ARRIAGA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL UCUM</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
   </si>
   <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD TERCERAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD VILLA CACTUS</t>
   </si>
   <si>
-    <t>EL MOLINITO</t>
+    <t>PRADOS</t>
   </si>
   <si>
     <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
   </si>
   <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
   </si>
   <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
     <t>SAN JOSÉ DEL VIDRIO</t>
   </si>
   <si>
-    <t>CUAUHTÉMOC</t>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN MARTÍN</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>EL REPARO</t>
+  </si>
+  <si>
+    <t>PALO GORDO</t>
+  </si>
+  <si>
+    <t>HERMILTEPEC</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>EL VALLECITO DE COAHUILOTES</t>
+  </si>
+  <si>
+    <t>TLACOCUSPAN</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DE ASIS</t>
+  </si>
+  <si>
+    <t>SAN JUAN CORRAL</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>LO DE MARCOS</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>SAN JUAN DE ABAJO</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
   </si>
   <si>
     <t>LA LAGUNA</t>
   </si>
   <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>SAN MARTÍN</t>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>NUEVO COPALTEPEC</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SANTA ANA ZICATECOYAN</t>
+  </si>
+  <si>
+    <t>CINCUENTA ARROBAS</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
   </si>
   <si>
     <t>PEDREGAL DE SANTA JULIA</t>
   </si>
   <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>SANTA CRUZ</t>
-  </si>
-  <si>
-    <t>EL REPARO</t>
-  </si>
-  <si>
-    <t>PALO GORDO</t>
-  </si>
-  <si>
-    <t>EL VALLECITO DE COAHUILOTES</t>
-  </si>
-  <si>
-    <t>HERMILTEPEC</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN JUAN CORRAL</t>
-  </si>
-  <si>
-    <t>SANTA ANA ZICATECOYAN</t>
-  </si>
-  <si>
-    <t>TLACOCUSPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NAUCALPAN</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
-  </si>
-  <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>LO DE MARCOS</t>
-  </si>
-  <si>
-    <t>SAN JUAN DE ABAJO</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
   </si>
   <si>
-    <t>EL PORVENIR</t>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
   </si>
   <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO DE ASIS</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>NUEVO COPALTEPEC</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA</t>
-  </si>
-  <si>
-    <t>CINCUENTA ARROBAS</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LA SOLEDAD</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
   </si>
   <si>
     <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LA SOLEDAD</t>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. LAS BRISAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
+    <t>CHICHIGAPA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>ORIZABA</t>
   </si>
   <si>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
+    <t>ZAPOAPAN</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
   </si>
   <si>
     <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>ZAPOAPAN</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1694,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1725,10 +1731,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1748,10 +1754,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1771,10 +1777,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1794,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1817,10 +1823,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1840,10 +1846,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1863,10 +1869,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1886,10 +1892,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1909,10 +1915,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1932,10 +1938,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1955,10 +1961,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1978,10 +1984,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2001,10 +2007,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2024,10 +2030,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2047,10 +2053,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2070,10 +2076,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2093,10 +2099,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2116,10 +2122,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2139,10 +2145,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2162,10 +2168,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2185,10 +2191,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2208,10 +2214,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2231,10 +2237,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2254,22 +2260,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G25">
-        <v>47.7</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2277,22 +2283,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F26">
         <v>44</v>
       </c>
       <c r="G26">
-        <v>52.3</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2300,22 +2306,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>53.8</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2323,22 +2329,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F28">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G28">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2346,22 +2352,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G29">
-        <v>68.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2369,22 +2375,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F30">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>70.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2392,22 +2398,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>79.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2415,22 +2421,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>81.8</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2438,22 +2444,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F33">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G33">
-        <v>87.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2461,22 +2467,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="F34">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G34">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2484,22 +2490,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F35">
         <v>44</v>
       </c>
       <c r="G35">
-        <v>95.5</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2507,22 +2513,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>343</v>
+        <v>42</v>
       </c>
       <c r="F36">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="G36">
-        <v>97.40000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2530,22 +2536,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>43</v>
+        <v>343</v>
       </c>
       <c r="F37">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G37">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2553,10 +2559,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2576,10 +2582,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2599,19 +2605,19 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F40">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G40">
         <v>97.7</v>
@@ -2622,10 +2628,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2645,19 +2651,19 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F42">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G42">
         <v>97.7</v>
@@ -2668,10 +2674,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2691,22 +2697,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C44" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F44">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G44">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2714,10 +2720,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2737,10 +2743,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2760,10 +2766,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D47">
         <v>6</v>
@@ -2783,22 +2789,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F48">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G48">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2806,22 +2812,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F49">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G49">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2829,10 +2835,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -2852,10 +2858,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2875,22 +2881,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F52">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G52">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2898,10 +2904,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D53">
         <v>5</v>
@@ -2921,22 +2927,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C54" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D54">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>615</v>
+        <v>219</v>
       </c>
       <c r="F54">
-        <v>616</v>
+        <v>220</v>
       </c>
       <c r="G54">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2944,22 +2950,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C55" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E55">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F55">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G55">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2967,10 +2973,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C56" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2990,19 +2996,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C57" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F57">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G57">
         <v>100</v>
@@ -3013,19 +3019,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F58">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -3036,10 +3042,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C59" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3059,10 +3065,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C60" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3082,10 +3088,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C61" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3105,10 +3111,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C62" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3128,10 +3134,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3151,10 +3157,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C64" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3174,10 +3180,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C65" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3197,10 +3203,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3220,10 +3226,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C67" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3243,10 +3249,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C68" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3266,10 +3272,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C69" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3289,10 +3295,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3312,10 +3318,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C71" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3335,19 +3341,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C72" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F72">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -3358,19 +3364,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C73" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F73">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -3381,10 +3387,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C74" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3404,10 +3410,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C75" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3427,10 +3433,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3450,10 +3456,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C77" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3473,10 +3479,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C78" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3496,10 +3502,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C79" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3519,19 +3525,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C80" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="F80">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -3542,10 +3548,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C81" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3565,10 +3571,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C82" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3588,10 +3594,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C83" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3611,19 +3617,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C84" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F84">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G84">
         <v>100</v>
@@ -3634,19 +3640,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C85" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F85">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -3657,10 +3663,10 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C86" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3680,10 +3686,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3703,10 +3709,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C88" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3726,10 +3732,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C89" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3749,10 +3755,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C90" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3772,10 +3778,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C91" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3795,10 +3801,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C92" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3818,10 +3824,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C93" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3841,10 +3847,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C94" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3864,10 +3870,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C95" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3887,10 +3893,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C96" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3910,19 +3916,19 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C97" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F97">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G97">
         <v>100</v>
@@ -3933,10 +3939,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C98" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3956,10 +3962,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C99" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3979,10 +3985,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C100" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4002,19 +4008,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -4025,10 +4031,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C102" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4048,10 +4054,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C103" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -4071,10 +4077,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C104" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4094,19 +4100,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C105" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F105">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -4117,10 +4123,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C106" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4140,10 +4146,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C107" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -4163,19 +4169,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C108" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F108">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -4186,19 +4192,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C109" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D109">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E109">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="F109">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -4209,19 +4215,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C110" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F110">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -4232,10 +4238,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C111" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4255,10 +4261,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C112" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -4278,19 +4284,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C113" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D113">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E113">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F113">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G113">
         <v>100</v>
@@ -4301,10 +4307,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4324,10 +4330,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C115" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4347,10 +4353,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C116" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4370,19 +4376,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C117" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E117">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F117">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G117">
         <v>100</v>
@@ -4393,10 +4399,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C118" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4416,10 +4422,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C119" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4439,10 +4445,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C120" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4462,10 +4468,10 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C121" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4485,19 +4491,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C122" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F122">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4508,19 +4514,19 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C123" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F123">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G123">
         <v>100</v>
@@ -4531,10 +4537,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C124" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4554,10 +4560,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C125" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4577,10 +4583,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C126" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4600,10 +4606,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C127" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4623,10 +4629,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C128" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4646,10 +4652,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C129" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4669,19 +4675,19 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C130" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F130">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G130">
         <v>100</v>
@@ -4692,10 +4698,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C131" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4715,19 +4721,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C132" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F132">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4738,10 +4744,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C133" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -4761,10 +4767,10 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C134" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -4784,19 +4790,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C135" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4807,19 +4813,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C136" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4830,19 +4836,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C137" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F137">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G137">
         <v>100</v>
@@ -4853,10 +4859,10 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C138" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4876,19 +4882,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C139" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F139">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4899,19 +4905,19 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C140" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F140">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G140">
         <v>100</v>
@@ -4922,10 +4928,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C141" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4945,10 +4951,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C142" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4968,10 +4974,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C143" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4991,10 +4997,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C144" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -5014,10 +5020,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C145" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5037,10 +5043,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C146" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -5060,10 +5066,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C147" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5083,10 +5089,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C148" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -5106,10 +5112,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C149" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -5129,10 +5135,10 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C150" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -5152,10 +5158,10 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C151" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -5175,10 +5181,10 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C152" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -5198,19 +5204,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C153" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F153">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -5221,19 +5227,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C154" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F154">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G154">
         <v>100</v>
@@ -5244,10 +5250,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C155" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -5267,19 +5273,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C156" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F156">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G156">
         <v>100</v>
@@ -5290,10 +5296,10 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C157" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -5313,10 +5319,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C158" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5336,10 +5342,10 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C159" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -5359,19 +5365,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C160" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F160">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G160">
         <v>100</v>
@@ -5382,19 +5388,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C161" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F161">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G161">
         <v>100</v>
@@ -5405,10 +5411,10 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C162" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -5428,10 +5434,10 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C163" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D163">
         <v>2</v>
@@ -5451,10 +5457,10 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C164" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -5474,10 +5480,10 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C165" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5497,10 +5503,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C166" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -5520,19 +5526,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C167" t="s">
-        <v>274</v>
+        <v>397</v>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F167">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G167">
         <v>100</v>
@@ -5543,10 +5549,10 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C168" t="s">
-        <v>396</v>
+        <v>276</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -5566,19 +5572,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C169" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F169">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G169">
         <v>100</v>
@@ -5589,10 +5595,10 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C170" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -5612,10 +5618,10 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C171" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -5635,10 +5641,10 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C172" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -5658,10 +5664,10 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C173" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5681,10 +5687,10 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C174" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -5704,19 +5710,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C175" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F175">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G175">
         <v>100</v>
@@ -5727,10 +5733,10 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C176" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -5750,10 +5756,10 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C177" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -5773,19 +5779,19 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C178" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E178">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F178">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G178">
         <v>100</v>
@@ -5796,19 +5802,19 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C179" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E179">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F179">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G179">
         <v>100</v>
@@ -5819,10 +5825,10 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C180" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -5842,19 +5848,19 @@
         <v>186</v>
       </c>
       <c r="B181" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C181" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F181">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G181">
         <v>100</v>
@@ -5865,19 +5871,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C182" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F182">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G182">
         <v>100</v>
@@ -5888,10 +5894,10 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C183" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -5911,10 +5917,10 @@
         <v>189</v>
       </c>
       <c r="B184" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C184" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -5934,19 +5940,19 @@
         <v>190</v>
       </c>
       <c r="B185" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C185" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F185">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G185">
         <v>100</v>
@@ -5957,10 +5963,10 @@
         <v>191</v>
       </c>
       <c r="B186" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C186" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -5980,10 +5986,10 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C187" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D187">
         <v>2</v>
@@ -6003,10 +6009,10 @@
         <v>193</v>
       </c>
       <c r="B188" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C188" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6026,10 +6032,10 @@
         <v>194</v>
       </c>
       <c r="B189" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C189" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -6049,10 +6055,10 @@
         <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C190" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -6072,19 +6078,19 @@
         <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C191" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E191">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F191">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G191">
         <v>100</v>
@@ -6095,10 +6101,10 @@
         <v>197</v>
       </c>
       <c r="B192" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C192" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -6118,19 +6124,19 @@
         <v>198</v>
       </c>
       <c r="B193" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C193" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F193">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G193">
         <v>100</v>
@@ -6141,10 +6147,10 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C194" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -6164,19 +6170,19 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C195" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E195">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F195">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G195">
         <v>100</v>
@@ -6187,19 +6193,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C196" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F196">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G196">
         <v>100</v>
@@ -6210,10 +6216,10 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C197" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -6233,10 +6239,10 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C198" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D198">
         <v>2</v>
@@ -6256,10 +6262,10 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C199" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D199">
         <v>2</v>
@@ -6279,10 +6285,10 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C200" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -6302,10 +6308,10 @@
         <v>206</v>
       </c>
       <c r="B201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C201" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D201">
         <v>3</v>
@@ -6325,10 +6331,10 @@
         <v>207</v>
       </c>
       <c r="B202" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C202" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -6348,19 +6354,19 @@
         <v>208</v>
       </c>
       <c r="B203" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E203">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F203">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G203">
         <v>100</v>
@@ -6371,19 +6377,19 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C204" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D204">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E204">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F204">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G204">
         <v>100</v>
@@ -6394,10 +6400,10 @@
         <v>210</v>
       </c>
       <c r="B205" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C205" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -6417,19 +6423,19 @@
         <v>211</v>
       </c>
       <c r="B206" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C206" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F206">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G206">
         <v>100</v>
@@ -6440,19 +6446,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C207" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F207">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G207">
         <v>100</v>
@@ -6463,10 +6469,10 @@
         <v>213</v>
       </c>
       <c r="B208" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C208" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -6486,19 +6492,19 @@
         <v>214</v>
       </c>
       <c r="B209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C209" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E209">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F209">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G209">
         <v>100</v>
@@ -6509,10 +6515,10 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C210" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -6532,10 +6538,10 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C211" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -6555,21 +6561,44 @@
         <v>217</v>
       </c>
       <c r="B212" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C212" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="E212">
+        <v>44</v>
+      </c>
+      <c r="F212">
+        <v>44</v>
+      </c>
+      <c r="G212">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" t="s">
+        <v>218</v>
+      </c>
+      <c r="B213" t="s">
+        <v>226</v>
+      </c>
+      <c r="C213" t="s">
+        <v>442</v>
+      </c>
+      <c r="D213">
         <v>4</v>
       </c>
-      <c r="E212">
+      <c r="E213">
         <v>176</v>
       </c>
-      <c r="F212">
+      <c r="F213">
         <v>176</v>
       </c>
-      <c r="G212">
+      <c r="G213">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -2269,13 +2269,13 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F25">
         <v>220</v>
       </c>
       <c r="G25">
-        <v>43.2</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="26" spans="1:7">

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="445">
   <si>
     <t>clues</t>
   </si>
@@ -61,12 +61,12 @@
     <t>MCIMB004122</t>
   </si>
   <si>
+    <t>MCIMB008602</t>
+  </si>
+  <si>
     <t>OCIMB002392</t>
   </si>
   <si>
-    <t>MCIMB008602</t>
-  </si>
-  <si>
     <t>BSIMB000136</t>
   </si>
   <si>
@@ -82,18 +82,18 @@
     <t>CSIMB003651</t>
   </si>
   <si>
+    <t>MCIMB008293</t>
+  </si>
+  <si>
+    <t>NTIMB000131</t>
+  </si>
+  <si>
+    <t>MCIMB011962</t>
+  </si>
+  <si>
     <t>MCIMB000943</t>
   </si>
   <si>
-    <t>MCIMB008293</t>
-  </si>
-  <si>
-    <t>NTIMB000131</t>
-  </si>
-  <si>
-    <t>MCIMB011962</t>
-  </si>
-  <si>
     <t>MCIMB003760</t>
   </si>
   <si>
@@ -106,570 +106,573 @@
     <t>VZIMB007160</t>
   </si>
   <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>MCIMB006905</t>
+  </si>
+  <si>
+    <t>MCIMB000716</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
+    <t>MCIMB006642</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB000733</t>
+  </si>
+  <si>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>MCIMB008585</t>
+  </si>
+  <si>
+    <t>MCIMB008573</t>
+  </si>
+  <si>
+    <t>MCIMB008544</t>
+  </si>
+  <si>
+    <t>MCIMB008532</t>
+  </si>
+  <si>
+    <t>MCIMB008520</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006934</t>
+  </si>
+  <si>
+    <t>MCIMB006852</t>
+  </si>
+  <si>
+    <t>MCIMB006922</t>
+  </si>
+  <si>
+    <t>MCIMB006910</t>
+  </si>
+  <si>
+    <t>MCIMB006881</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
+    <t>NTIMB001700</t>
+  </si>
+  <si>
+    <t>NTIMB001671</t>
+  </si>
+  <si>
+    <t>NTIMB001642</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB006823</t>
+  </si>
+  <si>
+    <t>MCIMB006811</t>
+  </si>
+  <si>
+    <t>MCIMB006876</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>MCIMB000692</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
     <t>MCIMB002512</t>
   </si>
   <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>MCIMB006905</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>MCIMB000716</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB006642</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
   </si>
   <si>
     <t>MCIMB004093</t>
   </si>
   <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
-  </si>
-  <si>
-    <t>MCIMB000733</t>
-  </si>
-  <si>
-    <t>MCIMB008585</t>
-  </si>
-  <si>
-    <t>MCIMB008573</t>
-  </si>
-  <si>
-    <t>MCIMB008544</t>
-  </si>
-  <si>
-    <t>MCIMB008532</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB008520</t>
-  </si>
-  <si>
-    <t>MCIMB006934</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB006852</t>
-  </si>
-  <si>
-    <t>MCIMB006876</t>
-  </si>
-  <si>
-    <t>MCIMB006922</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>NTIMB001613</t>
-  </si>
-  <si>
-    <t>NTIMB001642</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>MCIMB009524</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>NTIMB001700</t>
-  </si>
-  <si>
-    <t>NTIMB001671</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>QRIMB001051</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
   </si>
   <si>
     <t>NTIMB002704</t>
   </si>
   <si>
-    <t>NTIMB001835</t>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
   </si>
   <si>
     <t>QRIMB000136</t>
   </si>
   <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB006823</t>
-  </si>
-  <si>
-    <t>MCIMB006811</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006910</t>
-  </si>
-  <si>
-    <t>MCIMB000692</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000835</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001144</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>TSIMB001482</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB002585</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
   </si>
   <si>
     <t>QRIMB001372</t>
   </si>
   <si>
-    <t>QRIMB001080</t>
-  </si>
-  <si>
-    <t>QRIMB001051</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB000835</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
-  </si>
-  <si>
-    <t>TSIMB002585</t>
-  </si>
-  <si>
-    <t>TSIMB001482</t>
-  </si>
-  <si>
-    <t>TSIMB001144</t>
+    <t>VZIMB002366</t>
+  </si>
+  <si>
+    <t>VZIMB000831</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB003372</t>
+  </si>
+  <si>
+    <t>TSIMB003384</t>
   </si>
   <si>
     <t>TSIMB003343</t>
   </si>
   <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>VZIMB002366</t>
-  </si>
-  <si>
-    <t>VZIMB000831</t>
-  </si>
-  <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
-  </si>
-  <si>
-    <t>TSIMB003384</t>
-  </si>
-  <si>
-    <t>TSIMB003372</t>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB002885</t>
   </si>
   <si>
     <t>VZIMB002890</t>
   </si>
   <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
     <t>VZIMB002400</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
+    <t>VZIMB007831</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
   </si>
   <si>
     <t>VZIMB007505</t>
   </si>
   <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
-  </si>
-  <si>
-    <t>VZIMB007831</t>
-  </si>
-  <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
     <t>VZIMB007942</t>
   </si>
   <si>
@@ -736,12 +739,12 @@
     <t>LA COLMENA</t>
   </si>
   <si>
+    <t>SAUZ PALO GORDO</t>
+  </si>
+  <si>
     <t>SAN JUAN YUTA</t>
   </si>
   <si>
-    <t>SAUZ PALO GORDO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
   </si>
   <si>
@@ -757,18 +760,18 @@
     <t>CENTRO DE SALUD TUXTLA GUTIERREZ, CHIAPAS</t>
   </si>
   <si>
+    <t>CALIMAYA NORTE</t>
+  </si>
+  <si>
+    <t>EL CARRIZAL</t>
+  </si>
+  <si>
+    <t>CEAPS SAN ANTONIO LA ISLA LEONARDO BRAVO BICENTENARIO</t>
+  </si>
+  <si>
     <t>SAN MARTÍN DE PORRES</t>
   </si>
   <si>
-    <t>CALIMAYA NORTE</t>
-  </si>
-  <si>
-    <t>EL CARRIZAL</t>
-  </si>
-  <si>
-    <t>CEAPS SAN ANTONIO LA ISLA LEONARDO BRAVO BICENTENARIO</t>
-  </si>
-  <si>
     <t>LAS HUERTAS</t>
   </si>
   <si>
@@ -781,565 +784,568 @@
     <t>CENTRO DE SALUD URSULO GALVÁN</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO LIMON</t>
+  </si>
+  <si>
+    <t>PALMAR CHICO</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>SAN MARTÍN</t>
+  </si>
+  <si>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>EL REPARO</t>
+  </si>
+  <si>
+    <t>PALO GORDO</t>
+  </si>
+  <si>
+    <t>HERMILTEPEC</t>
+  </si>
+  <si>
+    <t>EL VALLECITO DE COAHUILOTES</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>TLACOCUSPAN</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DE ASIS</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA</t>
+  </si>
+  <si>
+    <t>SANTA ANA ZICATECOYAN</t>
+  </si>
+  <si>
+    <t>SAN MATEO GUAYATENCO</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
+    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>SAN JUAN DE ABAJO</t>
+  </si>
+  <si>
+    <t>LO DE MARCOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>NUEVO COPALTEPEC</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>SAN JUAN CORRAL</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CINCUENTA ARROBAS</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
     <t>COLONIA SANTA CRUZ TLAPACOYA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO LIMON</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>PALMAR CHICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
   </si>
   <si>
     <t>EL GLOBO</t>
   </si>
   <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>SAN MARTÍN</t>
-  </si>
-  <si>
-    <t>SANTA CRUZ</t>
-  </si>
-  <si>
-    <t>EL REPARO</t>
-  </si>
-  <si>
-    <t>PALO GORDO</t>
-  </si>
-  <si>
-    <t>HERMILTEPEC</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>EL VALLECITO DE COAHUILOTES</t>
-  </si>
-  <si>
-    <t>TLACOCUSPAN</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO DE ASIS</t>
-  </si>
-  <si>
-    <t>SAN JUAN CORRAL</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
-  </si>
-  <si>
-    <t>LO DE MARCOS</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NAUCALPAN</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>SAN JUAN DE ABAJO</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
   </si>
   <si>
     <t>GUÁSIMA DEL METATE</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL POLYUC</t>
   </si>
   <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>NUEVO COPALTEPEC</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SANTA ANA ZICATECOYAN</t>
-  </si>
-  <si>
-    <t>CINCUENTA ARROBAS</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LA SOLEDAD</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LA SOLEDAD</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>LA CONCEPCIÓN</t>
   </si>
   <si>
     <t>CHICHIGAPA</t>
   </si>
   <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
     <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
+    <t>ZAPOAPAN</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
-  </si>
-  <si>
-    <t>ZAPOAPAN</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
@@ -1700,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G213"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1731,10 +1737,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1754,10 +1760,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1777,10 +1783,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1800,10 +1806,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1823,10 +1829,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1846,10 +1852,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1869,10 +1875,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1892,10 +1898,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1915,10 +1921,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1938,10 +1944,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1961,10 +1967,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1984,10 +1990,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2007,10 +2013,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2030,10 +2036,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2053,10 +2059,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2076,10 +2082,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2099,10 +2105,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2122,22 +2128,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G19">
-        <v>15.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2145,22 +2151,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2168,10 +2174,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2191,10 +2197,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2214,10 +2220,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2237,10 +2243,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2260,22 +2266,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>46.4</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2283,22 +2289,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F26">
         <v>44</v>
       </c>
       <c r="G26">
-        <v>47.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2306,22 +2312,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F27">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G27">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2329,22 +2335,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F28">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G28">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2352,22 +2358,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F29">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2378,19 +2384,19 @@
         <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G30">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2398,22 +2404,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2421,22 +2427,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32">
         <v>44</v>
       </c>
       <c r="G32">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2444,22 +2450,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="F33">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G33">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2470,19 +2476,19 @@
         <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="F34">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G34">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2490,22 +2496,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F35">
         <v>44</v>
       </c>
       <c r="G35">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2516,19 +2522,19 @@
         <v>221</v>
       </c>
       <c r="C36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>42</v>
+        <v>343</v>
       </c>
       <c r="F36">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G36">
-        <v>95.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2536,22 +2542,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>343</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="G37">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2562,7 +2568,7 @@
         <v>229</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2582,10 +2588,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2605,19 +2611,19 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F40">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G40">
         <v>97.7</v>
@@ -2628,10 +2634,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2651,19 +2657,19 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F42">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G42">
         <v>97.7</v>
@@ -2674,10 +2680,10 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2700,19 +2706,19 @@
         <v>221</v>
       </c>
       <c r="C44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F44">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G44">
-        <v>97.7</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2720,10 +2726,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2743,10 +2749,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2766,10 +2772,10 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D47">
         <v>6</v>
@@ -2789,22 +2795,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F48">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G48">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2812,22 +2818,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="F49">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="G49">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2835,10 +2841,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -2858,10 +2864,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2881,22 +2887,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F52">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G52">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2904,10 +2910,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D53">
         <v>5</v>
@@ -2927,22 +2933,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E54">
-        <v>219</v>
+        <v>615</v>
       </c>
       <c r="F54">
-        <v>220</v>
+        <v>616</v>
       </c>
       <c r="G54">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2950,22 +2956,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C55" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D55">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>615</v>
+        <v>44</v>
       </c>
       <c r="F55">
-        <v>616</v>
+        <v>44</v>
       </c>
       <c r="G55">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2973,10 +2979,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C56" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2996,10 +3002,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3019,10 +3025,10 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C58" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D58">
         <v>6</v>
@@ -3042,10 +3048,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C59" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3065,10 +3071,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C60" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3088,10 +3094,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3111,19 +3117,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C62" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F62">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -3134,10 +3140,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C63" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3157,10 +3163,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3180,10 +3186,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C65" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3203,10 +3209,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C66" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3226,10 +3232,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3249,10 +3255,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C68" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3272,10 +3278,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C69" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3295,10 +3301,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3318,10 +3324,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3341,19 +3347,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" t="s">
+        <v>303</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72">
         <v>220</v>
       </c>
-      <c r="C72" t="s">
-        <v>302</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>44</v>
-      </c>
       <c r="F72">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -3364,19 +3370,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C73" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F73">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -3387,10 +3393,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3410,10 +3416,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3433,10 +3439,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3456,10 +3462,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C77" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3479,10 +3485,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3502,10 +3508,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3525,19 +3531,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C80" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F80">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -3548,10 +3554,10 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C81" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3571,10 +3577,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C82" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3594,10 +3600,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3617,10 +3623,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C84" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3640,19 +3646,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C85" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F85">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G85">
         <v>100</v>
@@ -3663,19 +3669,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C86" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F86">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3686,10 +3692,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3709,10 +3715,10 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C88" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3732,10 +3738,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C89" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3755,10 +3761,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C90" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3778,10 +3784,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C91" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3801,10 +3807,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C92" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3824,10 +3830,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C93" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3847,10 +3853,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C94" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3870,10 +3876,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3893,10 +3899,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C96" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3916,19 +3922,19 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C97" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="F97">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G97">
         <v>100</v>
@@ -3939,10 +3945,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C98" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3962,10 +3968,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C99" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3985,10 +3991,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C100" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4008,19 +4014,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C101" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F101">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -4031,10 +4037,10 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C102" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4054,10 +4060,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C103" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -4077,10 +4083,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C104" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4100,19 +4106,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C105" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F105">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G105">
         <v>100</v>
@@ -4123,10 +4129,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4146,10 +4152,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C107" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -4169,10 +4175,10 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C108" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -4192,10 +4198,10 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C109" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -4215,19 +4221,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C110" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E110">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="F110">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -4238,10 +4244,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4261,10 +4267,10 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C112" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -4284,10 +4290,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4307,10 +4313,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C114" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4330,10 +4336,10 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4353,10 +4359,10 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C116" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4376,19 +4382,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C117" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D117">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E117">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F117">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G117">
         <v>100</v>
@@ -4399,10 +4405,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4422,10 +4428,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C119" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4445,10 +4451,10 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4468,19 +4474,19 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C121" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E121">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F121">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G121">
         <v>100</v>
@@ -4491,10 +4497,10 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C122" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D122">
         <v>3</v>
@@ -4514,10 +4520,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C123" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4537,10 +4543,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C124" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4560,10 +4566,10 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C125" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4583,10 +4589,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C126" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4606,10 +4612,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C127" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4629,10 +4635,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C128" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4652,10 +4658,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C129" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4675,10 +4681,10 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C130" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4698,19 +4704,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C131" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F131">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G131">
         <v>100</v>
@@ -4721,10 +4727,10 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C132" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D132">
         <v>2</v>
@@ -4744,10 +4750,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C133" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -4767,19 +4773,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C134" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F134">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G134">
         <v>100</v>
@@ -4790,19 +4796,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C135" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F135">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4813,19 +4819,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C136" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F136">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4836,10 +4842,10 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C137" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -4859,19 +4865,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C138" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F138">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G138">
         <v>100</v>
@@ -4882,19 +4888,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C139" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F139">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G139">
         <v>100</v>
@@ -4905,10 +4911,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C140" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4928,10 +4934,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C141" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4951,10 +4957,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C142" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4974,10 +4980,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C143" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4997,10 +5003,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C144" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -5020,10 +5026,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C145" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5043,10 +5049,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C146" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -5066,10 +5072,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C147" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5089,10 +5095,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C148" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -5112,10 +5118,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C149" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -5135,10 +5141,10 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -5158,10 +5164,10 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C151" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -5181,10 +5187,10 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C152" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -5204,19 +5210,19 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C153" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F153">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G153">
         <v>100</v>
@@ -5227,10 +5233,10 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C154" t="s">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -5250,7 +5256,7 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C155" t="s">
         <v>385</v>
@@ -5273,7 +5279,7 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C156" t="s">
         <v>386</v>
@@ -5296,7 +5302,7 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C157" t="s">
         <v>387</v>
@@ -5319,7 +5325,7 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C158" t="s">
         <v>388</v>
@@ -5342,7 +5348,7 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C159" t="s">
         <v>389</v>
@@ -5365,19 +5371,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C160" t="s">
         <v>390</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F160">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G160">
         <v>100</v>
@@ -5388,19 +5394,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C161" t="s">
         <v>391</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F161">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G161">
         <v>100</v>
@@ -5411,19 +5417,19 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C162" t="s">
         <v>392</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F162">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G162">
         <v>100</v>
@@ -5434,19 +5440,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C163" t="s">
         <v>393</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F163">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G163">
         <v>100</v>
@@ -5457,7 +5463,7 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C164" t="s">
         <v>394</v>
@@ -5480,19 +5486,19 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C165" t="s">
         <v>395</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F165">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G165">
         <v>100</v>
@@ -5503,19 +5509,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C166" t="s">
         <v>396</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F166">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G166">
         <v>100</v>
@@ -5526,7 +5532,7 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C167" t="s">
         <v>397</v>
@@ -5549,19 +5555,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C168" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F168">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G168">
         <v>100</v>
@@ -5572,10 +5578,10 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C169" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -5595,10 +5601,10 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C170" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -5618,10 +5624,10 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C171" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -5641,10 +5647,10 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C172" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -5664,10 +5670,10 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C173" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5687,10 +5693,10 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C174" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -5710,19 +5716,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C175" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F175">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G175">
         <v>100</v>
@@ -5733,10 +5739,10 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C176" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -5756,10 +5762,10 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C177" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -5779,19 +5785,19 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C178" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E178">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F178">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G178">
         <v>100</v>
@@ -5802,10 +5808,10 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C179" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -5825,19 +5831,19 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C180" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F180">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G180">
         <v>100</v>
@@ -5848,19 +5854,19 @@
         <v>186</v>
       </c>
       <c r="B181" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C181" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E181">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F181">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G181">
         <v>100</v>
@@ -5871,10 +5877,10 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C182" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -5894,19 +5900,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C183" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F183">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G183">
         <v>100</v>
@@ -5917,19 +5923,19 @@
         <v>189</v>
       </c>
       <c r="B184" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C184" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F184">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G184">
         <v>100</v>
@@ -5940,19 +5946,19 @@
         <v>190</v>
       </c>
       <c r="B185" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C185" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F185">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G185">
         <v>100</v>
@@ -5963,10 +5969,10 @@
         <v>191</v>
       </c>
       <c r="B186" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C186" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -5986,10 +5992,10 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C187" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D187">
         <v>2</v>
@@ -6009,10 +6015,10 @@
         <v>193</v>
       </c>
       <c r="B188" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C188" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6032,10 +6038,10 @@
         <v>194</v>
       </c>
       <c r="B189" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C189" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -6055,10 +6061,10 @@
         <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C190" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -6078,10 +6084,10 @@
         <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C191" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D191">
         <v>2</v>
@@ -6101,19 +6107,19 @@
         <v>197</v>
       </c>
       <c r="B192" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C192" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E192">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F192">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G192">
         <v>100</v>
@@ -6124,19 +6130,19 @@
         <v>198</v>
       </c>
       <c r="B193" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C193" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E193">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F193">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G193">
         <v>100</v>
@@ -6147,10 +6153,10 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C194" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -6170,10 +6176,10 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C195" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -6193,19 +6199,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C196" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F196">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G196">
         <v>100</v>
@@ -6216,19 +6222,19 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C197" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F197">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G197">
         <v>100</v>
@@ -6239,10 +6245,10 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C198" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D198">
         <v>2</v>
@@ -6262,10 +6268,10 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C199" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D199">
         <v>2</v>
@@ -6285,19 +6291,19 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C200" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E200">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F200">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G200">
         <v>100</v>
@@ -6308,10 +6314,10 @@
         <v>206</v>
       </c>
       <c r="B201" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C201" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D201">
         <v>3</v>
@@ -6331,19 +6337,19 @@
         <v>207</v>
       </c>
       <c r="B202" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C202" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E202">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F202">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G202">
         <v>100</v>
@@ -6354,19 +6360,19 @@
         <v>208</v>
       </c>
       <c r="B203" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C203" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E203">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F203">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G203">
         <v>100</v>
@@ -6377,10 +6383,10 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -6400,10 +6406,10 @@
         <v>210</v>
       </c>
       <c r="B205" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C205" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -6423,19 +6429,19 @@
         <v>211</v>
       </c>
       <c r="B206" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C206" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E206">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F206">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G206">
         <v>100</v>
@@ -6446,10 +6452,10 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C207" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -6469,10 +6475,10 @@
         <v>213</v>
       </c>
       <c r="B208" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C208" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -6492,10 +6498,10 @@
         <v>214</v>
       </c>
       <c r="B209" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C209" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D209">
         <v>3</v>
@@ -6515,10 +6521,10 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C210" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -6538,10 +6544,10 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C211" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -6561,10 +6567,10 @@
         <v>217</v>
       </c>
       <c r="B212" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C212" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -6584,21 +6590,44 @@
         <v>218</v>
       </c>
       <c r="B213" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C213" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D213">
+        <v>2</v>
+      </c>
+      <c r="E213">
+        <v>88</v>
+      </c>
+      <c r="F213">
+        <v>88</v>
+      </c>
+      <c r="G213">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" t="s">
+        <v>219</v>
+      </c>
+      <c r="B214" t="s">
+        <v>227</v>
+      </c>
+      <c r="C214" t="s">
+        <v>444</v>
+      </c>
+      <c r="D214">
         <v>4</v>
       </c>
-      <c r="E213">
+      <c r="E214">
         <v>176</v>
       </c>
-      <c r="F213">
+      <c r="F214">
         <v>176</v>
       </c>
-      <c r="G213">
+      <c r="G214">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="452">
   <si>
     <t>clues</t>
   </si>
@@ -91,490 +91,544 @@
     <t>MCIMB011962</t>
   </si>
   <si>
+    <t>MCIMB003760</t>
+  </si>
+  <si>
+    <t>MCIMB011180</t>
+  </si>
+  <si>
+    <t>VZIMB005475</t>
+  </si>
+  <si>
+    <t>VZIMB007160</t>
+  </si>
+  <si>
+    <t>SPIMB002253</t>
+  </si>
+  <si>
+    <t>VZIMB002260</t>
+  </si>
+  <si>
+    <t>SPIMB000701</t>
+  </si>
+  <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
+    <t>SPIMB000433</t>
+  </si>
+  <si>
+    <t>TSIMB003104</t>
+  </si>
+  <si>
+    <t>SPIMB002842</t>
+  </si>
+  <si>
+    <t>NTIMB001806</t>
+  </si>
+  <si>
+    <t>QRIMB001664</t>
+  </si>
+  <si>
+    <t>MCIMB004110</t>
+  </si>
+  <si>
+    <t>TSIMB000695</t>
+  </si>
+  <si>
+    <t>MCIMB010200</t>
+  </si>
+  <si>
+    <t>MCIMB000716</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
+    <t>MCIMB006905</t>
+  </si>
+  <si>
+    <t>SPIMB000445</t>
+  </si>
+  <si>
+    <t>ZSIMB001641</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>SPIMB000450</t>
+  </si>
+  <si>
+    <t>TSIMB003396</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
+    <t>SPIMB002661</t>
+  </si>
+  <si>
+    <t>SPIMB002562</t>
+  </si>
+  <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
+    <t>MCIMB003842</t>
+  </si>
+  <si>
+    <t>MCIMB001503</t>
+  </si>
+  <si>
+    <t>MCIMB007214</t>
+  </si>
+  <si>
+    <t>VZIMB002395</t>
+  </si>
+  <si>
+    <t>MCIMB004163</t>
+  </si>
+  <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB006630</t>
+  </si>
+  <si>
     <t>MCIMB000943</t>
   </si>
   <si>
-    <t>MCIMB003760</t>
-  </si>
-  <si>
-    <t>MCIMB011180</t>
-  </si>
-  <si>
-    <t>VZIMB005475</t>
-  </si>
-  <si>
-    <t>VZIMB007160</t>
-  </si>
-  <si>
-    <t>SPIMB002253</t>
-  </si>
-  <si>
-    <t>VZIMB002260</t>
-  </si>
-  <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
-    <t>SPIMB000433</t>
-  </si>
-  <si>
-    <t>SPIMB000701</t>
-  </si>
-  <si>
-    <t>TSIMB003104</t>
-  </si>
-  <si>
-    <t>SPIMB002842</t>
-  </si>
-  <si>
-    <t>NTIMB001806</t>
-  </si>
-  <si>
-    <t>QRIMB001664</t>
-  </si>
-  <si>
-    <t>MCIMB004110</t>
-  </si>
-  <si>
-    <t>SPIMB000445</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>MCIMB010200</t>
-  </si>
-  <si>
-    <t>MCIMB006905</t>
-  </si>
-  <si>
-    <t>MCIMB000716</t>
-  </si>
-  <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
-    <t>SPIMB000450</t>
-  </si>
-  <si>
-    <t>ZSIMB001641</t>
-  </si>
-  <si>
-    <t>SPIMB002661</t>
-  </si>
-  <si>
-    <t>SPIMB002562</t>
-  </si>
-  <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
-    <t>MCIMB003842</t>
-  </si>
-  <si>
-    <t>MCIMB001503</t>
-  </si>
-  <si>
-    <t>MCIMB007214</t>
-  </si>
-  <si>
-    <t>VZIMB002395</t>
-  </si>
-  <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB006630</t>
+    <t>MCIMB000733</t>
+  </si>
+  <si>
+    <t>MCIMB000692</t>
+  </si>
+  <si>
+    <t>MCIMB008544</t>
+  </si>
+  <si>
+    <t>MCIMB008532</t>
+  </si>
+  <si>
+    <t>MCIMB008520</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB006934</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006910</t>
+  </si>
+  <si>
+    <t>MCIMB006922</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB006852</t>
+  </si>
+  <si>
+    <t>MCIMB006881</t>
+  </si>
+  <si>
+    <t>MCIMB006876</t>
+  </si>
+  <si>
+    <t>MCIMB008573</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>MCIMB008585</t>
+  </si>
+  <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>NTIMB001642</t>
+  </si>
+  <si>
+    <t>NTIMB001613</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001700</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
   </si>
   <si>
     <t>MCIMB006642</t>
   </si>
   <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB004163</t>
-  </si>
-  <si>
     <t>MCIMB006654</t>
   </si>
   <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB000733</t>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006811</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006823</t>
+  </si>
+  <si>
+    <t>MCIMB000955</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>MCIMB002512</t>
+  </si>
+  <si>
+    <t>MCIMB000972</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
   </si>
   <si>
     <t>BCIMB000990</t>
   </si>
   <si>
-    <t>MCIMB008585</t>
-  </si>
-  <si>
-    <t>MCIMB008573</t>
-  </si>
-  <si>
-    <t>MCIMB008544</t>
-  </si>
-  <si>
-    <t>MCIMB008532</t>
-  </si>
-  <si>
-    <t>MCIMB008520</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB006934</t>
-  </si>
-  <si>
-    <t>MCIMB006852</t>
-  </si>
-  <si>
-    <t>MCIMB006922</t>
-  </si>
-  <si>
-    <t>MCIMB006910</t>
-  </si>
-  <si>
-    <t>MCIMB006881</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
-  </si>
-  <si>
-    <t>MCIMB009524</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>NTIMB001613</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
-    <t>NTIMB001700</t>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>QRIMB001046</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
+  </si>
+  <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
   </si>
   <si>
     <t>NTIMB001671</t>
   </si>
   <si>
-    <t>NTIMB001642</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB006823</t>
-  </si>
-  <si>
-    <t>MCIMB006811</t>
-  </si>
-  <si>
-    <t>MCIMB006876</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
-  </si>
-  <si>
-    <t>MCIMB000692</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>MCIMB002512</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000835</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB001132</t>
+  </si>
+  <si>
+    <t>TSIMB001144</t>
+  </si>
+  <si>
+    <t>TSIMB000951</t>
+  </si>
+  <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001051</t>
+  </si>
+  <si>
+    <t>QRIMB001372</t>
   </si>
   <si>
     <t>QRIMB001080</t>
   </si>
   <si>
-    <t>QRIMB001051</t>
-  </si>
-  <si>
-    <t>QRIMB001046</t>
-  </si>
-  <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000835</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>TSIMB000951</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
-  </si>
-  <si>
-    <t>TSIMB001144</t>
-  </si>
-  <si>
-    <t>TSIMB001115</t>
+    <t>TSIMB003401</t>
+  </si>
+  <si>
+    <t>TSIMB003384</t>
+  </si>
+  <si>
+    <t>TSIMB003372</t>
+  </si>
+  <si>
+    <t>TSIMB003343</t>
+  </si>
+  <si>
+    <t>TSIMB002585</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
   </si>
   <si>
     <t>TSIMB001482</t>
@@ -583,84 +637,42 @@
     <t>TSIMB001646</t>
   </si>
   <si>
-    <t>TSIMB002585</t>
-  </si>
-  <si>
-    <t>TSIMB001132</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001372</t>
+    <t>VZIMB002885</t>
+  </si>
+  <si>
+    <t>VZIMB002412</t>
+  </si>
+  <si>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
   </si>
   <si>
     <t>VZIMB002366</t>
   </si>
   <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
     <t>VZIMB000831</t>
   </si>
   <si>
     <t>TSIMB003640</t>
   </si>
   <si>
-    <t>TSIMB003401</t>
-  </si>
-  <si>
-    <t>TSIMB003372</t>
-  </si>
-  <si>
-    <t>TSIMB003384</t>
-  </si>
-  <si>
-    <t>TSIMB003343</t>
-  </si>
-  <si>
-    <t>VZIMB002412</t>
+    <t>VZIMB005661</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
   </si>
   <si>
     <t>VZIMB005620</t>
   </si>
   <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005661</t>
-  </si>
-  <si>
-    <t>VZIMB002885</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
     <t>VZIMB007831</t>
   </si>
   <si>
@@ -769,487 +781,538 @@
     <t>CEAPS SAN ANTONIO LA ISLA LEONARDO BRAVO BICENTENARIO</t>
   </si>
   <si>
+    <t>LAS HUERTAS</t>
+  </si>
+  <si>
+    <t>CEAPS SANTA MARÍA RAYÓN BICENTENARIO</t>
+  </si>
+  <si>
+    <t>BARRA DE CHACHALACAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URSULO GALVÁN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ROTARIOS</t>
+  </si>
+  <si>
+    <t>CUAUTLAPAN</t>
+  </si>
+  <si>
+    <t>DR. JUAN H. SANCHEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
+    <t>PLAN DE IGUALA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
+  </si>
+  <si>
+    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>CAMPO DE LOS LIMONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
+  </si>
+  <si>
+    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
+  </si>
+  <si>
+    <t>PALMAR CHICO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO LIMON</t>
+  </si>
+  <si>
+    <t>AURELIO MANRIQUE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD ZACATECAS</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>PONCIANO ARRIAGA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD TERCERAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
+    <t>EL MOLINITO</t>
+  </si>
+  <si>
+    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
+  </si>
+  <si>
+    <t>PRADOS</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ DEL VIDRIO</t>
+  </si>
+  <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>BENITO JUÁREZ</t>
+  </si>
+  <si>
     <t>SAN MARTÍN DE PORRES</t>
   </si>
   <si>
-    <t>LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>CEAPS SANTA MARÍA RAYÓN BICENTENARIO</t>
-  </si>
-  <si>
-    <t>BARRA DE CHACHALACAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URSULO GALVÁN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ROTARIOS</t>
-  </si>
-  <si>
-    <t>CUAUTLAPAN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
-    <t>PLAN DE IGUALA</t>
-  </si>
-  <si>
-    <t>DR. JUAN H. SANCHEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. JOSÉ MARÍA MORELOS</t>
-  </si>
-  <si>
-    <t>UMF SOLEDAD DE GRACIANO SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>CAMPO DE LOS LIMONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 07 CHETUMAL</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>AURELIO MANRIQUE</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO LIMON</t>
-  </si>
-  <si>
-    <t>PALMAR CHICO</t>
-  </si>
-  <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
-    <t>PONCIANO ARRIAGA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD ZACATECAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD TERCERAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>NUEVA SANTA MARÍA CUAUTITLÁN</t>
-  </si>
-  <si>
-    <t>PRADOS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
-  </si>
-  <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>BENITO JUÁREZ</t>
+    <t>SAN MARTÍN</t>
+  </si>
+  <si>
+    <t>CINCUENTA ARROBAS</t>
+  </si>
+  <si>
+    <t>PALO GORDO</t>
+  </si>
+  <si>
+    <t>HERMILTEPEC</t>
+  </si>
+  <si>
+    <t>EL VALLECITO DE COAHUILOTES</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>TLACOCUSPAN</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>SANTA ANA ZICATECOYAN</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DE ASIS</t>
+  </si>
+  <si>
+    <t>SAN MATEO GUAYATENCO</t>
+  </si>
+  <si>
+    <t>SAN JUAN CORRAL</t>
+  </si>
+  <si>
+    <t>EL REPARO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>LO DE MARCOS</t>
+  </si>
+  <si>
+    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
   </si>
   <si>
     <t>CUAUHTÉMOC</t>
   </si>
   <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ DEL VIDRIO</t>
-  </si>
-  <si>
     <t>LA LAGUNA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>SAN MARTÍN</t>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>NUEVO COPALTEPEC</t>
+  </si>
+  <si>
+    <t>COLONIA LAS PEÑITAS</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>COLONIA SANTA CRUZ TLAPACOYA</t>
+  </si>
+  <si>
+    <t>MARGARITA MAZA DE JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
   </si>
   <si>
     <t>PEDREGAL DE SANTA JULIA</t>
   </si>
   <si>
-    <t>SANTA CRUZ</t>
-  </si>
-  <si>
-    <t>EL REPARO</t>
-  </si>
-  <si>
-    <t>PALO GORDO</t>
-  </si>
-  <si>
-    <t>HERMILTEPEC</t>
-  </si>
-  <si>
-    <t>EL VALLECITO DE COAHUILOTES</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>TLACOCUSPAN</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO DE ASIS</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA</t>
-  </si>
-  <si>
-    <t>SANTA ANA ZICATECOYAN</t>
-  </si>
-  <si>
-    <t>SAN MATEO GUAYATENCO</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NAUCALPAN</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
-  </si>
-  <si>
-    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
   </si>
   <si>
     <t>SAN JUAN DE ABAJO</t>
   </si>
   <si>
-    <t>LO DE MARCOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>NUEVO COPALTEPEC</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>SAN JUAN CORRAL</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
-  </si>
-  <si>
-    <t>CINCUENTA ARROBAS</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>COLONIA SANTA CRUZ TLAPACOYA</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL MOQUETITO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL MOQUETITO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
   </si>
   <si>
     <t>CENTRO DE SALUD LA SOLEDAD</t>
@@ -1258,82 +1321,40 @@
     <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
+    <t>LA CONCEPCIÓN</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+  </si>
+  <si>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
   </si>
   <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
     <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD SOLISEÑO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. EL CAMBIO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. LAS BRISAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
+    <t>GRANJA RÍO MEDIO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
   </si>
   <si>
     <t>LAS BAJADAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>GRANJA RÍO MEDIO</t>
-  </si>
-  <si>
-    <t>LA CONCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
   </si>
   <si>
     <t>ZAPOAPAN</t>
@@ -1706,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1737,10 +1758,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1760,10 +1781,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1783,10 +1804,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1806,10 +1827,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1829,10 +1850,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1852,10 +1873,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1875,10 +1896,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1898,10 +1919,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1921,10 +1942,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1944,10 +1965,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1967,10 +1988,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1990,10 +2011,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2013,10 +2034,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2036,10 +2057,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2059,10 +2080,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2082,10 +2103,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2105,10 +2126,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2128,10 +2149,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2151,22 +2172,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C20" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F20">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G20">
-        <v>18.2</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2174,22 +2195,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="F21">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G21">
-        <v>21.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2197,22 +2218,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C22" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F22">
         <v>44</v>
       </c>
       <c r="G22">
-        <v>25</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2220,22 +2241,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23">
         <v>44</v>
       </c>
       <c r="G23">
-        <v>31.8</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2243,22 +2264,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F24">
         <v>44</v>
       </c>
       <c r="G24">
-        <v>43.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2266,22 +2287,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C25" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F25">
         <v>44</v>
       </c>
       <c r="G25">
-        <v>47.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2289,22 +2310,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F26">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>52.3</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2312,10 +2333,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -2335,10 +2356,10 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2358,10 +2379,10 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2381,10 +2402,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2404,22 +2425,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F31">
         <v>44</v>
       </c>
       <c r="G31">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2427,22 +2448,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G32">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2450,22 +2471,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C33" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="F33">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G33">
-        <v>87.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2473,22 +2494,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F34">
         <v>44</v>
       </c>
       <c r="G34">
-        <v>90.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2496,22 +2517,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>42</v>
+        <v>343</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="G35">
-        <v>95.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2519,22 +2540,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C36" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="F36">
-        <v>352</v>
+        <v>132</v>
       </c>
       <c r="G36">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2542,10 +2563,10 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C37" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2565,19 +2586,19 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F38">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G38">
         <v>97.7</v>
@@ -2588,10 +2609,10 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2611,10 +2632,10 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C40" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2634,10 +2655,10 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2657,10 +2678,10 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2680,19 +2701,19 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F43">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G43">
         <v>97.7</v>
@@ -2703,19 +2724,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F44">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="G44">
         <v>98.90000000000001</v>
@@ -2726,10 +2747,10 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2749,10 +2770,10 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C46" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2772,19 +2793,19 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C47" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>261</v>
+        <v>87</v>
       </c>
       <c r="F47">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="G47">
         <v>98.90000000000001</v>
@@ -2795,22 +2816,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C48" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F48">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G48">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2818,22 +2839,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F49">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G49">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2841,10 +2862,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -2864,10 +2885,10 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C51" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2887,22 +2908,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C52" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="F52">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="G52">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2910,10 +2931,10 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D53">
         <v>5</v>
@@ -2933,22 +2954,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D54">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>615</v>
+        <v>219</v>
       </c>
       <c r="F54">
-        <v>616</v>
+        <v>220</v>
       </c>
       <c r="G54">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2956,22 +2977,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C55" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E55">
-        <v>44</v>
+        <v>615</v>
       </c>
       <c r="F55">
-        <v>44</v>
+        <v>616</v>
       </c>
       <c r="G55">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2979,10 +3000,10 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C56" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3002,10 +3023,10 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C57" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3025,19 +3046,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C58" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F58">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G58">
         <v>100</v>
@@ -3048,10 +3069,10 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C59" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3071,10 +3092,10 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3094,10 +3115,10 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C61" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3117,19 +3138,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C62" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -3140,10 +3161,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C63" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3163,10 +3184,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C64" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3186,10 +3207,10 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C65" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3209,10 +3230,10 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C66" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3232,10 +3253,10 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C67" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3255,10 +3276,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C68" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3278,10 +3299,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C69" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3301,10 +3322,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C70" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3324,19 +3345,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C71" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F71">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G71">
         <v>100</v>
@@ -3347,19 +3368,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C72" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F72">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G72">
         <v>100</v>
@@ -3370,10 +3391,10 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C73" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3393,10 +3414,10 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C74" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3416,10 +3437,10 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C75" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3439,10 +3460,10 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C76" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3462,10 +3483,10 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C77" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3485,10 +3506,10 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C78" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3508,10 +3529,10 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C79" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3531,10 +3552,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C80" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3554,19 +3575,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C81" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="F81">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="G81">
         <v>100</v>
@@ -3577,10 +3598,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C82" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3600,10 +3621,10 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C83" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3623,10 +3644,10 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C84" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3646,10 +3667,10 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C85" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3669,19 +3690,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C86" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F86">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G86">
         <v>100</v>
@@ -3692,10 +3713,10 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C87" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3715,19 +3736,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C88" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F88">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G88">
         <v>100</v>
@@ -3738,10 +3759,10 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C89" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3761,10 +3782,10 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C90" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3784,10 +3805,10 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C91" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3807,10 +3828,10 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C92" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3830,10 +3851,10 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C93" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3853,10 +3874,10 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C94" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3876,10 +3897,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3899,10 +3920,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C96" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3922,19 +3943,19 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C97" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="F97">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="G97">
         <v>100</v>
@@ -3945,10 +3966,10 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C98" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3968,10 +3989,10 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C99" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3991,10 +4012,10 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C100" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4014,19 +4035,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C101" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F101">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G101">
         <v>100</v>
@@ -4037,19 +4058,19 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C102" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F102">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G102">
         <v>100</v>
@@ -4060,10 +4081,10 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C103" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -4083,10 +4104,10 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C104" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4106,10 +4127,10 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C105" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -4129,10 +4150,10 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C106" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4152,10 +4173,10 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C107" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -4175,19 +4196,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C108" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E108">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F108">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G108">
         <v>100</v>
@@ -4198,19 +4219,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C109" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F109">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G109">
         <v>100</v>
@@ -4221,19 +4242,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C110" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E110">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="F110">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="G110">
         <v>100</v>
@@ -4244,10 +4265,10 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C111" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4267,19 +4288,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C112" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F112">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -4290,10 +4311,10 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C113" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4313,10 +4334,10 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4336,19 +4357,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C115" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="F115">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="G115">
         <v>100</v>
@@ -4359,19 +4380,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C116" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F116">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G116">
         <v>100</v>
@@ -4382,10 +4403,10 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C117" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4405,10 +4426,10 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4428,10 +4449,10 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C119" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4451,19 +4472,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C120" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E120">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="F120">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="G120">
         <v>100</v>
@@ -4474,19 +4495,19 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C121" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E121">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="F121">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="G121">
         <v>100</v>
@@ -4497,19 +4518,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F122">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G122">
         <v>100</v>
@@ -4520,10 +4541,10 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C123" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4543,10 +4564,10 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C124" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4566,19 +4587,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C125" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F125">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G125">
         <v>100</v>
@@ -4589,10 +4610,10 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C126" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4612,10 +4633,10 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4635,10 +4656,10 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C128" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4658,10 +4679,10 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C129" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4681,19 +4702,19 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C130" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F130">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G130">
         <v>100</v>
@@ -4704,10 +4725,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C131" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -4727,19 +4748,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C132" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F132">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G132">
         <v>100</v>
@@ -4750,10 +4771,10 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C133" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -4773,10 +4794,10 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C134" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4796,19 +4817,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C135" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F135">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G135">
         <v>100</v>
@@ -4819,19 +4840,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C136" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F136">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -4842,10 +4863,10 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C137" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -4865,19 +4886,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C138" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F138">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G138">
         <v>100</v>
@@ -4888,10 +4909,10 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C139" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4911,10 +4932,10 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C140" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4934,10 +4955,10 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C141" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4957,10 +4978,10 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C142" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4980,10 +5001,10 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C143" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -5003,10 +5024,10 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C144" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -5026,10 +5047,10 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C145" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5049,10 +5070,10 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C146" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -5072,10 +5093,10 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C147" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5095,10 +5116,10 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C148" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -5118,10 +5139,10 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C149" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -5141,10 +5162,10 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C150" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -5164,10 +5185,10 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C151" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -5187,10 +5208,10 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C152" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -5210,10 +5231,10 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C153" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -5233,10 +5254,10 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C154" t="s">
-        <v>277</v>
+        <v>389</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -5256,10 +5277,10 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C155" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -5279,10 +5300,10 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C156" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -5302,10 +5323,10 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C157" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -5325,10 +5346,10 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C158" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -5348,19 +5369,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C159" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F159">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G159">
         <v>100</v>
@@ -5371,10 +5392,10 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C160" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D160">
         <v>2</v>
@@ -5394,10 +5415,10 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C161" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -5417,19 +5438,19 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C162" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F162">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G162">
         <v>100</v>
@@ -5440,19 +5461,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C163" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F163">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G163">
         <v>100</v>
@@ -5463,10 +5484,10 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C164" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -5486,10 +5507,10 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C165" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D165">
         <v>2</v>
@@ -5509,10 +5530,10 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C166" t="s">
-        <v>396</v>
+        <v>281</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -5532,10 +5553,10 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C167" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -5555,19 +5576,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C168" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F168">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G168">
         <v>100</v>
@@ -5578,10 +5599,10 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C169" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -5601,10 +5622,10 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C170" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -5624,10 +5645,10 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C171" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -5647,19 +5668,19 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C172" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F172">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G172">
         <v>100</v>
@@ -5670,10 +5691,10 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C173" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5693,10 +5714,10 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C174" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -5716,10 +5737,10 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C175" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -5739,19 +5760,19 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C176" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F176">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G176">
         <v>100</v>
@@ -5762,10 +5783,10 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C177" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -5785,10 +5806,10 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C178" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -5808,10 +5829,10 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C179" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -5831,19 +5852,19 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C180" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F180">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G180">
         <v>100</v>
@@ -5854,19 +5875,19 @@
         <v>186</v>
       </c>
       <c r="B181" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C181" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D181">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E181">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F181">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G181">
         <v>100</v>
@@ -5877,10 +5898,10 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C182" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D182">
         <v>1</v>
@@ -5900,19 +5921,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C183" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F183">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G183">
         <v>100</v>
@@ -5923,19 +5944,19 @@
         <v>189</v>
       </c>
       <c r="B184" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C184" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F184">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G184">
         <v>100</v>
@@ -5946,19 +5967,19 @@
         <v>190</v>
       </c>
       <c r="B185" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C185" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E185">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F185">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G185">
         <v>100</v>
@@ -5969,19 +5990,19 @@
         <v>191</v>
       </c>
       <c r="B186" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C186" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F186">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G186">
         <v>100</v>
@@ -5992,19 +6013,19 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C187" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F187">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G187">
         <v>100</v>
@@ -6015,10 +6036,10 @@
         <v>193</v>
       </c>
       <c r="B188" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C188" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6038,10 +6059,10 @@
         <v>194</v>
       </c>
       <c r="B189" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C189" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -6061,19 +6082,19 @@
         <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C190" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E190">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F190">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G190">
         <v>100</v>
@@ -6084,10 +6105,10 @@
         <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C191" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D191">
         <v>2</v>
@@ -6107,19 +6128,19 @@
         <v>197</v>
       </c>
       <c r="B192" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C192" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F192">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G192">
         <v>100</v>
@@ -6130,10 +6151,10 @@
         <v>198</v>
       </c>
       <c r="B193" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C193" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -6153,19 +6174,19 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C194" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D194">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="F194">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="G194">
         <v>100</v>
@@ -6176,19 +6197,19 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C195" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F195">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G195">
         <v>100</v>
@@ -6199,19 +6220,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C196" t="s">
-        <v>426</v>
+        <v>271</v>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="F196">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G196">
         <v>100</v>
@@ -6222,10 +6243,10 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C197" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D197">
         <v>2</v>
@@ -6245,10 +6266,10 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C198" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D198">
         <v>2</v>
@@ -6268,10 +6289,10 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C199" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D199">
         <v>2</v>
@@ -6291,19 +6312,19 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C200" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F200">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="G200">
         <v>100</v>
@@ -6314,19 +6335,19 @@
         <v>206</v>
       </c>
       <c r="B201" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C201" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E201">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F201">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G201">
         <v>100</v>
@@ -6337,19 +6358,19 @@
         <v>207</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C202" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D202">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E202">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F202">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G202">
         <v>100</v>
@@ -6360,19 +6381,19 @@
         <v>208</v>
       </c>
       <c r="B203" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C203" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E203">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F203">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G203">
         <v>100</v>
@@ -6383,10 +6404,10 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C204" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -6406,10 +6427,10 @@
         <v>210</v>
       </c>
       <c r="B205" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C205" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -6429,19 +6450,19 @@
         <v>211</v>
       </c>
       <c r="B206" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C206" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F206">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G206">
         <v>100</v>
@@ -6452,19 +6473,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C207" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E207">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="F207">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="G207">
         <v>100</v>
@@ -6475,10 +6496,10 @@
         <v>213</v>
       </c>
       <c r="B208" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -6498,19 +6519,19 @@
         <v>214</v>
       </c>
       <c r="B209" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C209" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D209">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E209">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="F209">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G209">
         <v>100</v>
@@ -6521,10 +6542,10 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C210" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -6544,10 +6565,10 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C211" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -6567,10 +6588,10 @@
         <v>217</v>
       </c>
       <c r="B212" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C212" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -6590,19 +6611,19 @@
         <v>218</v>
       </c>
       <c r="B213" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C213" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E213">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="F213">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G213">
         <v>100</v>
@@ -6613,21 +6634,113 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C214" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214">
+        <v>44</v>
+      </c>
+      <c r="F214">
+        <v>44</v>
+      </c>
+      <c r="G214">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" t="s">
+        <v>220</v>
+      </c>
+      <c r="B215" t="s">
+        <v>231</v>
+      </c>
+      <c r="C215" t="s">
+        <v>448</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+      <c r="E215">
+        <v>44</v>
+      </c>
+      <c r="F215">
+        <v>44</v>
+      </c>
+      <c r="G215">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" t="s">
+        <v>221</v>
+      </c>
+      <c r="B216" t="s">
+        <v>231</v>
+      </c>
+      <c r="C216" t="s">
+        <v>449</v>
+      </c>
+      <c r="D216">
+        <v>1</v>
+      </c>
+      <c r="E216">
+        <v>44</v>
+      </c>
+      <c r="F216">
+        <v>44</v>
+      </c>
+      <c r="G216">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" t="s">
+        <v>222</v>
+      </c>
+      <c r="B217" t="s">
+        <v>231</v>
+      </c>
+      <c r="C217" t="s">
+        <v>450</v>
+      </c>
+      <c r="D217">
+        <v>2</v>
+      </c>
+      <c r="E217">
+        <v>88</v>
+      </c>
+      <c r="F217">
+        <v>88</v>
+      </c>
+      <c r="G217">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" t="s">
+        <v>223</v>
+      </c>
+      <c r="B218" t="s">
+        <v>231</v>
+      </c>
+      <c r="C218" t="s">
+        <v>451</v>
+      </c>
+      <c r="D218">
         <v>4</v>
       </c>
-      <c r="E214">
+      <c r="E218">
         <v>176</v>
       </c>
-      <c r="F214">
+      <c r="F218">
         <v>176</v>
       </c>
-      <c r="G214">
+      <c r="G218">
         <v>100</v>
       </c>
     </row>

--- a/tabla_unidades.xlsx
+++ b/tabla_unidades.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="462">
   <si>
     <t>clues</t>
   </si>
@@ -46,12 +46,12 @@
     <t>MCIMB003941</t>
   </si>
   <si>
+    <t>QRIMB001775</t>
+  </si>
+  <si>
     <t>QRIMB001536</t>
   </si>
   <si>
-    <t>QRIMB001775</t>
-  </si>
-  <si>
     <t>BSIMB000030</t>
   </si>
   <si>
@@ -109,18 +109,18 @@
     <t>VZIMB002260</t>
   </si>
   <si>
+    <t>SPIMB002241</t>
+  </si>
+  <si>
+    <t>VZIMB007843</t>
+  </si>
+  <si>
+    <t>BCIMB000092</t>
+  </si>
+  <si>
     <t>SPIMB000701</t>
   </si>
   <si>
-    <t>SPIMB002241</t>
-  </si>
-  <si>
-    <t>VZIMB007843</t>
-  </si>
-  <si>
-    <t>BCIMB000092</t>
-  </si>
-  <si>
     <t>SPIMB000433</t>
   </si>
   <si>
@@ -145,48 +145,48 @@
     <t>MCIMB010200</t>
   </si>
   <si>
+    <t>MCIMB006905</t>
+  </si>
+  <si>
+    <t>NTIMB001280</t>
+  </si>
+  <si>
+    <t>QRIMB000474</t>
+  </si>
+  <si>
+    <t>NTIMB000126</t>
+  </si>
+  <si>
     <t>MCIMB000716</t>
   </si>
   <si>
-    <t>NTIMB001280</t>
-  </si>
-  <si>
-    <t>QRIMB000474</t>
-  </si>
-  <si>
-    <t>NTIMB000126</t>
-  </si>
-  <si>
-    <t>MCIMB006905</t>
-  </si>
-  <si>
     <t>SPIMB000445</t>
   </si>
   <si>
+    <t>TSIMB003396</t>
+  </si>
+  <si>
+    <t>MCIMB008730</t>
+  </si>
+  <si>
+    <t>QRIMB001652</t>
+  </si>
+  <si>
     <t>ZSIMB001641</t>
   </si>
   <si>
-    <t>MCIMB008730</t>
-  </si>
-  <si>
     <t>SPIMB000450</t>
   </si>
   <si>
-    <t>TSIMB003396</t>
-  </si>
-  <si>
-    <t>QRIMB001652</t>
-  </si>
-  <si>
     <t>SPIMB002661</t>
   </si>
   <si>
+    <t>SPIMB003146</t>
+  </si>
+  <si>
     <t>SPIMB002562</t>
   </si>
   <si>
-    <t>SPIMB003146</t>
-  </si>
-  <si>
     <t>MCIMB003842</t>
   </si>
   <si>
@@ -199,382 +199,430 @@
     <t>VZIMB002395</t>
   </si>
   <si>
+    <t>MCIMB004146</t>
+  </si>
+  <si>
+    <t>MCIMB006625</t>
+  </si>
+  <si>
+    <t>MCIMB004105</t>
+  </si>
+  <si>
+    <t>MCIMB004093</t>
+  </si>
+  <si>
+    <t>MCIMB004081</t>
+  </si>
+  <si>
+    <t>MCIMB003883</t>
+  </si>
+  <si>
+    <t>MCIMB003801</t>
+  </si>
+  <si>
+    <t>MCIMB000955</t>
+  </si>
+  <si>
+    <t>MCIMB000733</t>
+  </si>
+  <si>
+    <t>MCIMB000943</t>
+  </si>
+  <si>
+    <t>MCIMB008520</t>
+  </si>
+  <si>
+    <t>MCIMB007243</t>
+  </si>
+  <si>
+    <t>MCIMB007226</t>
+  </si>
+  <si>
+    <t>MCIMB006934</t>
+  </si>
+  <si>
+    <t>MCIMB006910</t>
+  </si>
+  <si>
+    <t>MCIMB006922</t>
+  </si>
+  <si>
+    <t>MCIMB006876</t>
+  </si>
+  <si>
+    <t>MCIMB006881</t>
+  </si>
+  <si>
+    <t>MCIMB006811</t>
+  </si>
+  <si>
+    <t>MCIMB006823</t>
+  </si>
+  <si>
+    <t>MCIMB006852</t>
+  </si>
+  <si>
+    <t>MCIMB006835</t>
+  </si>
+  <si>
+    <t>MCIMB008544</t>
+  </si>
+  <si>
+    <t>MCIMB008800</t>
+  </si>
+  <si>
+    <t>MCIMB008573</t>
+  </si>
+  <si>
+    <t>MCIMB008660</t>
+  </si>
+  <si>
+    <t>MCIMB009524</t>
+  </si>
+  <si>
+    <t>NTIMB000184</t>
+  </si>
+  <si>
+    <t>NTIMB000341</t>
+  </si>
+  <si>
+    <t>NTIMB000201</t>
+  </si>
+  <si>
+    <t>NTIMB000411</t>
+  </si>
+  <si>
+    <t>NTIMB000522</t>
+  </si>
+  <si>
+    <t>NTIMB000546</t>
+  </si>
+  <si>
+    <t>NTIMB001292</t>
+  </si>
+  <si>
+    <t>NTIMB001316</t>
+  </si>
+  <si>
+    <t>NTIMB001345</t>
+  </si>
+  <si>
+    <t>NTIMB001374</t>
+  </si>
+  <si>
+    <t>NTIMB001415</t>
+  </si>
+  <si>
+    <t>NTIMB001444</t>
+  </si>
+  <si>
+    <t>MCIMB008532</t>
+  </si>
+  <si>
+    <t>MCIMB010253</t>
+  </si>
+  <si>
+    <t>MCIMB008585</t>
+  </si>
+  <si>
+    <t>NTIMB001596</t>
+  </si>
+  <si>
+    <t>NTIMB001473</t>
+  </si>
+  <si>
+    <t>NTIMB001456</t>
+  </si>
+  <si>
+    <t>NTIMB001671</t>
+  </si>
+  <si>
+    <t>NTIMB001700</t>
+  </si>
+  <si>
+    <t>NTIMB001753</t>
+  </si>
+  <si>
+    <t>NTIMB001835</t>
+  </si>
+  <si>
     <t>MCIMB004163</t>
   </si>
   <si>
-    <t>MCIMB004146</t>
-  </si>
-  <si>
-    <t>MCIMB004105</t>
-  </si>
-  <si>
-    <t>MCIMB004093</t>
-  </si>
-  <si>
-    <t>MCIMB004081</t>
-  </si>
-  <si>
-    <t>MCIMB003883</t>
+    <t>MCIMB006671</t>
+  </si>
+  <si>
+    <t>MCIMB006683</t>
+  </si>
+  <si>
+    <t>MCIMB006695</t>
+  </si>
+  <si>
+    <t>MCIMB006724</t>
+  </si>
+  <si>
+    <t>MCIMB006736</t>
   </si>
   <si>
     <t>MCIMB006630</t>
   </si>
   <si>
-    <t>MCIMB000943</t>
-  </si>
-  <si>
-    <t>MCIMB000733</t>
+    <t>MCIMB006642</t>
+  </si>
+  <si>
+    <t>MCIMB006654</t>
+  </si>
+  <si>
+    <t>MCIMB006770</t>
+  </si>
+  <si>
+    <t>MCIMB006753</t>
+  </si>
+  <si>
+    <t>MCIMB006741</t>
+  </si>
+  <si>
+    <t>MCIMB006782</t>
+  </si>
+  <si>
+    <t>MCIMB000214</t>
+  </si>
+  <si>
+    <t>MCIMB001520</t>
+  </si>
+  <si>
+    <t>MCIMB002261</t>
+  </si>
+  <si>
+    <t>MCIMB000972</t>
+  </si>
+  <si>
+    <t>MCIMB003796</t>
+  </si>
+  <si>
+    <t>MCIMB002512</t>
+  </si>
+  <si>
+    <t>MCIMB003813</t>
   </si>
   <si>
     <t>MCIMB000692</t>
   </si>
   <si>
-    <t>MCIMB008544</t>
-  </si>
-  <si>
-    <t>MCIMB008532</t>
-  </si>
-  <si>
-    <t>MCIMB008520</t>
-  </si>
-  <si>
-    <t>MCIMB007243</t>
-  </si>
-  <si>
-    <t>MCIMB006934</t>
-  </si>
-  <si>
-    <t>MCIMB007226</t>
-  </si>
-  <si>
-    <t>MCIMB006910</t>
-  </si>
-  <si>
-    <t>MCIMB006922</t>
-  </si>
-  <si>
-    <t>MCIMB006835</t>
-  </si>
-  <si>
-    <t>MCIMB006852</t>
-  </si>
-  <si>
-    <t>MCIMB006881</t>
-  </si>
-  <si>
-    <t>MCIMB006876</t>
-  </si>
-  <si>
-    <t>MCIMB008573</t>
-  </si>
-  <si>
-    <t>MCIMB009524</t>
-  </si>
-  <si>
-    <t>MCIMB008585</t>
-  </si>
-  <si>
-    <t>MCIMB008800</t>
-  </si>
-  <si>
-    <t>NTIMB000201</t>
-  </si>
-  <si>
-    <t>NTIMB000341</t>
-  </si>
-  <si>
-    <t>NTIMB000522</t>
-  </si>
-  <si>
-    <t>NTIMB000411</t>
-  </si>
-  <si>
-    <t>NTIMB000546</t>
-  </si>
-  <si>
-    <t>NTIMB001292</t>
-  </si>
-  <si>
-    <t>NTIMB001316</t>
-  </si>
-  <si>
-    <t>NTIMB001345</t>
-  </si>
-  <si>
-    <t>NTIMB001374</t>
-  </si>
-  <si>
-    <t>NTIMB001415</t>
-  </si>
-  <si>
-    <t>NTIMB001444</t>
-  </si>
-  <si>
-    <t>NTIMB001456</t>
-  </si>
-  <si>
-    <t>NTIMB001473</t>
-  </si>
-  <si>
-    <t>MCIMB010253</t>
-  </si>
-  <si>
-    <t>NTIMB000184</t>
-  </si>
-  <si>
-    <t>MCIMB008660</t>
+    <t>BCIMB000990</t>
+  </si>
+  <si>
+    <t>BCIMB000302</t>
+  </si>
+  <si>
+    <t>BCIMB000314</t>
+  </si>
+  <si>
+    <t>BCIMB000536</t>
+  </si>
+  <si>
+    <t>QRIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB000964</t>
+  </si>
+  <si>
+    <t>QRIMB000906</t>
+  </si>
+  <si>
+    <t>QRIMB000783</t>
+  </si>
+  <si>
+    <t>QRIMB000730</t>
+  </si>
+  <si>
+    <t>QRIMB000713</t>
+  </si>
+  <si>
+    <t>QRIMB000655</t>
+  </si>
+  <si>
+    <t>QRIMB000503</t>
+  </si>
+  <si>
+    <t>QRIMB000433</t>
+  </si>
+  <si>
+    <t>QRIMB000375</t>
+  </si>
+  <si>
+    <t>QRIMB000363</t>
+  </si>
+  <si>
+    <t>QRIMB000322</t>
+  </si>
+  <si>
+    <t>QRIMB000276</t>
+  </si>
+  <si>
+    <t>QRIMB000293</t>
+  </si>
+  <si>
+    <t>QRIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB000240</t>
   </si>
   <si>
     <t>NTIMB001642</t>
   </si>
   <si>
+    <t>QRIMB000141</t>
+  </si>
+  <si>
+    <t>QRIMB000136</t>
+  </si>
+  <si>
+    <t>QRIMB000054</t>
+  </si>
+  <si>
+    <t>NTIMB002704</t>
+  </si>
+  <si>
+    <t>NTIMB002651</t>
+  </si>
+  <si>
+    <t>NTIMB002173</t>
+  </si>
+  <si>
+    <t>NTIMB002050</t>
+  </si>
+  <si>
     <t>NTIMB001613</t>
   </si>
   <si>
-    <t>NTIMB001596</t>
-  </si>
-  <si>
-    <t>NTIMB001700</t>
-  </si>
-  <si>
-    <t>NTIMB001835</t>
-  </si>
-  <si>
-    <t>NTIMB002050</t>
-  </si>
-  <si>
-    <t>NTIMB002173</t>
-  </si>
-  <si>
-    <t>MCIMB006625</t>
-  </si>
-  <si>
-    <t>MCIMB006683</t>
-  </si>
-  <si>
-    <t>MCIMB006695</t>
-  </si>
-  <si>
-    <t>MCIMB006724</t>
-  </si>
-  <si>
-    <t>MCIMB006736</t>
-  </si>
-  <si>
-    <t>MCIMB006741</t>
-  </si>
-  <si>
-    <t>MCIMB006642</t>
-  </si>
-  <si>
-    <t>MCIMB006654</t>
-  </si>
-  <si>
-    <t>MCIMB006671</t>
-  </si>
-  <si>
-    <t>MCIMB006811</t>
-  </si>
-  <si>
-    <t>MCIMB006770</t>
-  </si>
-  <si>
-    <t>MCIMB006753</t>
-  </si>
-  <si>
-    <t>MCIMB006823</t>
-  </si>
-  <si>
-    <t>MCIMB000955</t>
-  </si>
-  <si>
-    <t>BCIMB000314</t>
-  </si>
-  <si>
-    <t>MCIMB002512</t>
-  </si>
-  <si>
-    <t>MCIMB000972</t>
-  </si>
-  <si>
-    <t>MCIMB003801</t>
-  </si>
-  <si>
-    <t>MCIMB003796</t>
-  </si>
-  <si>
-    <t>MCIMB002261</t>
-  </si>
-  <si>
-    <t>MCIMB003813</t>
-  </si>
-  <si>
-    <t>MCIMB000214</t>
-  </si>
-  <si>
-    <t>BCIMB000302</t>
-  </si>
-  <si>
-    <t>BCIMB000990</t>
-  </si>
-  <si>
-    <t>BCIMB000536</t>
+    <t>QRIMB001944</t>
+  </si>
+  <si>
+    <t>QRIMB001676</t>
+  </si>
+  <si>
+    <t>QRIMB001710</t>
+  </si>
+  <si>
+    <t>QRIMB001372</t>
+  </si>
+  <si>
+    <t>QRIMB001990</t>
+  </si>
+  <si>
+    <t>SPIMB000252</t>
+  </si>
+  <si>
+    <t>QRIMB001635</t>
+  </si>
+  <si>
+    <t>SPIMB002195</t>
+  </si>
+  <si>
+    <t>SPIMB002101</t>
+  </si>
+  <si>
+    <t>SPIMB001331</t>
+  </si>
+  <si>
+    <t>SPIMB000993</t>
+  </si>
+  <si>
+    <t>SPIMB000520</t>
+  </si>
+  <si>
+    <t>SPIMB000981</t>
+  </si>
+  <si>
+    <t>QRIMB001985</t>
+  </si>
+  <si>
+    <t>SPIMB002533</t>
+  </si>
+  <si>
+    <t>SPIMB002731</t>
+  </si>
+  <si>
+    <t>SPIMB002545</t>
+  </si>
+  <si>
+    <t>SPIMB002521</t>
+  </si>
+  <si>
+    <t>SPIMB002830</t>
+  </si>
+  <si>
+    <t>SPIMB002760</t>
+  </si>
+  <si>
+    <t>TSIMB000292</t>
+  </si>
+  <si>
+    <t>TSIMB000683</t>
+  </si>
+  <si>
+    <t>SPIMB002340</t>
+  </si>
+  <si>
+    <t>TSIMB000835</t>
+  </si>
+  <si>
+    <t>TSIMB000840</t>
+  </si>
+  <si>
+    <t>TSIMB000876</t>
+  </si>
+  <si>
+    <t>TSIMB000864</t>
+  </si>
+  <si>
+    <t>TSIMB000905</t>
+  </si>
+  <si>
+    <t>TSIMB000910</t>
+  </si>
+  <si>
+    <t>TSIMB000922</t>
+  </si>
+  <si>
+    <t>QRIMB001961</t>
+  </si>
+  <si>
+    <t>SPIMB000264</t>
+  </si>
+  <si>
+    <t>QRIMB001524</t>
+  </si>
+  <si>
+    <t>QRIMB001430</t>
+  </si>
+  <si>
+    <t>QRIMB001483</t>
+  </si>
+  <si>
+    <t>QRIMB000993</t>
   </si>
   <si>
     <t>QRIMB001046</t>
   </si>
   <si>
-    <t>QRIMB000993</t>
-  </si>
-  <si>
-    <t>QRIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB000964</t>
-  </si>
-  <si>
-    <t>QRIMB000906</t>
-  </si>
-  <si>
-    <t>QRIMB000783</t>
-  </si>
-  <si>
-    <t>QRIMB000730</t>
-  </si>
-  <si>
-    <t>QRIMB000713</t>
-  </si>
-  <si>
-    <t>QRIMB000655</t>
-  </si>
-  <si>
-    <t>QRIMB000503</t>
-  </si>
-  <si>
-    <t>QRIMB000433</t>
-  </si>
-  <si>
-    <t>QRIMB000375</t>
-  </si>
-  <si>
-    <t>QRIMB000322</t>
-  </si>
-  <si>
-    <t>QRIMB000363</t>
-  </si>
-  <si>
-    <t>QRIMB000293</t>
-  </si>
-  <si>
-    <t>QRIMB000276</t>
-  </si>
-  <si>
-    <t>NTIMB001753</t>
-  </si>
-  <si>
-    <t>QRIMB000252</t>
-  </si>
-  <si>
-    <t>QRIMB000240</t>
-  </si>
-  <si>
-    <t>QRIMB000141</t>
-  </si>
-  <si>
-    <t>QRIMB000136</t>
-  </si>
-  <si>
-    <t>QRIMB000054</t>
-  </si>
-  <si>
-    <t>NTIMB002704</t>
-  </si>
-  <si>
-    <t>NTIMB002651</t>
-  </si>
-  <si>
-    <t>NTIMB001671</t>
-  </si>
-  <si>
-    <t>QRIMB001985</t>
-  </si>
-  <si>
-    <t>QRIMB001944</t>
-  </si>
-  <si>
-    <t>QRIMB001710</t>
-  </si>
-  <si>
-    <t>QRIMB001676</t>
-  </si>
-  <si>
-    <t>QRIMB001483</t>
-  </si>
-  <si>
-    <t>SPIMB000264</t>
-  </si>
-  <si>
-    <t>SPIMB000252</t>
-  </si>
-  <si>
-    <t>SPIMB002340</t>
-  </si>
-  <si>
-    <t>SPIMB002195</t>
-  </si>
-  <si>
-    <t>SPIMB001331</t>
-  </si>
-  <si>
-    <t>SPIMB002101</t>
-  </si>
-  <si>
-    <t>SPIMB000993</t>
-  </si>
-  <si>
-    <t>SPIMB000981</t>
-  </si>
-  <si>
-    <t>QRIMB001990</t>
-  </si>
-  <si>
-    <t>SPIMB002545</t>
-  </si>
-  <si>
-    <t>SPIMB002830</t>
-  </si>
-  <si>
-    <t>SPIMB002760</t>
-  </si>
-  <si>
-    <t>SPIMB002731</t>
-  </si>
-  <si>
-    <t>TSIMB000292</t>
-  </si>
-  <si>
-    <t>TSIMB000835</t>
-  </si>
-  <si>
-    <t>TSIMB000840</t>
-  </si>
-  <si>
-    <t>SPIMB002533</t>
-  </si>
-  <si>
-    <t>SPIMB002521</t>
-  </si>
-  <si>
-    <t>TSIMB000876</t>
-  </si>
-  <si>
-    <t>TSIMB000864</t>
-  </si>
-  <si>
-    <t>TSIMB000905</t>
-  </si>
-  <si>
-    <t>TSIMB000910</t>
+    <t>QRIMB001051</t>
+  </si>
+  <si>
+    <t>QRIMB001080</t>
+  </si>
+  <si>
+    <t>TSIMB003046</t>
+  </si>
+  <si>
+    <t>TSIMB002585</t>
+  </si>
+  <si>
+    <t>TSIMB001646</t>
+  </si>
+  <si>
+    <t>TSIMB001482</t>
   </si>
   <si>
     <t>TSIMB001132</t>
@@ -583,58 +631,40 @@
     <t>TSIMB001144</t>
   </si>
   <si>
+    <t>TSIMB001115</t>
+  </si>
+  <si>
     <t>TSIMB000951</t>
   </si>
   <si>
-    <t>TSIMB001115</t>
-  </si>
-  <si>
-    <t>SPIMB000520</t>
-  </si>
-  <si>
-    <t>QRIMB001961</t>
-  </si>
-  <si>
-    <t>QRIMB001635</t>
-  </si>
-  <si>
-    <t>QRIMB001524</t>
-  </si>
-  <si>
-    <t>QRIMB001430</t>
-  </si>
-  <si>
-    <t>QRIMB001051</t>
-  </si>
-  <si>
-    <t>QRIMB001372</t>
-  </si>
-  <si>
-    <t>QRIMB001080</t>
+    <t>TSIMB000893</t>
+  </si>
+  <si>
+    <t>VZIMB000831</t>
+  </si>
+  <si>
+    <t>VZIMB002400</t>
+  </si>
+  <si>
+    <t>TSIMB003640</t>
+  </si>
+  <si>
+    <t>TSIMB003384</t>
   </si>
   <si>
     <t>TSIMB003401</t>
   </si>
   <si>
-    <t>TSIMB003384</t>
-  </si>
-  <si>
     <t>TSIMB003372</t>
   </si>
   <si>
     <t>TSIMB003343</t>
   </si>
   <si>
-    <t>TSIMB002585</t>
-  </si>
-  <si>
-    <t>TSIMB003046</t>
-  </si>
-  <si>
-    <t>TSIMB001482</t>
-  </si>
-  <si>
-    <t>TSIMB001646</t>
+    <t>VZIMB003264</t>
+  </si>
+  <si>
+    <t>VZIMB002890</t>
   </si>
   <si>
     <t>VZIMB002885</t>
@@ -643,51 +673,36 @@
     <t>VZIMB002412</t>
   </si>
   <si>
-    <t>VZIMB003264</t>
-  </si>
-  <si>
-    <t>VZIMB002890</t>
-  </si>
-  <si>
     <t>VZIMB002366</t>
   </si>
   <si>
-    <t>VZIMB002400</t>
-  </si>
-  <si>
-    <t>VZIMB000831</t>
-  </si>
-  <si>
-    <t>TSIMB003640</t>
+    <t>VZIMB005620</t>
+  </si>
+  <si>
+    <t>VZIMB005656</t>
+  </si>
+  <si>
+    <t>VZIMB005632</t>
+  </si>
+  <si>
+    <t>VZIMB007616</t>
+  </si>
+  <si>
+    <t>VZIMB007604</t>
+  </si>
+  <si>
+    <t>VZIMB007505</t>
   </si>
   <si>
     <t>VZIMB005661</t>
   </si>
   <si>
-    <t>VZIMB005656</t>
-  </si>
-  <si>
-    <t>VZIMB005632</t>
-  </si>
-  <si>
-    <t>VZIMB005620</t>
+    <t>VZIMB007942</t>
   </si>
   <si>
     <t>VZIMB007831</t>
   </si>
   <si>
-    <t>VZIMB007616</t>
-  </si>
-  <si>
-    <t>VZIMB007604</t>
-  </si>
-  <si>
-    <t>VZIMB007505</t>
-  </si>
-  <si>
-    <t>VZIMB007942</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
@@ -736,12 +751,12 @@
     <t>CIUDAD LAGO</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD RURAL FELIPE ÁNGELES</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD RURAL ADOLFO LÓPEZ MATEOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD BENITO JUÁREZ</t>
   </si>
   <si>
@@ -799,18 +814,18 @@
     <t>CUAUTLAPAN</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD DORACELI</t>
+  </si>
+  <si>
+    <t>LA ANTIGUA</t>
+  </si>
+  <si>
+    <t>FRACCIONAMIENTO MAR</t>
+  </si>
+  <si>
     <t>DR. JUAN H. SANCHEZ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD DORACELI</t>
-  </si>
-  <si>
-    <t>LA ANTIGUA</t>
-  </si>
-  <si>
-    <t>FRACCIONAMIENTO MAR</t>
-  </si>
-  <si>
     <t>PLAN DE IGUALA</t>
   </si>
   <si>
@@ -835,48 +850,48 @@
     <t>CEAPS CON SERVICIOS GERIATRICOS REFORMA URBANA</t>
   </si>
   <si>
+    <t>SAN PEDRO LIMON</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LIMONES</t>
+  </si>
+  <si>
+    <t>VALLE DE LA URRACA</t>
+  </si>
+  <si>
     <t>PALMAR CHICO</t>
   </si>
   <si>
-    <t>TEPIC, COL. 26 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LIMONES</t>
-  </si>
-  <si>
-    <t>VALLE DE LA URRACA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO LIMON</t>
-  </si>
-  <si>
     <t>AURELIO MANRIQUE</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. BENITO JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL UCUM</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD ZACATECAS</t>
   </si>
   <si>
-    <t>SAN BUENAVENTURA (EJIDO DE JALPA)</t>
-  </si>
-  <si>
     <t>PONCIANO ARRIAGA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. BENITO JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL UCUM</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD JARDINES DE MARIA CECILIA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD VILLA CACTUS</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD TERCERAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD VILLA CACTUS</t>
-  </si>
-  <si>
     <t>EL MOLINITO</t>
   </si>
   <si>
@@ -889,379 +904,427 @@
     <t>XALAPA-ENRÍQUEZ DR. GASTON MELO</t>
   </si>
   <si>
+    <t>CAHUACAN 5O. BARRIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CARACOLES</t>
+  </si>
+  <si>
+    <t>COL. LIBERTAD</t>
+  </si>
+  <si>
+    <t>EL GLOBO</t>
+  </si>
+  <si>
+    <t>COL. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>RINCÓN VERDE</t>
+  </si>
+  <si>
+    <t>SAN MATEO (LA PRESA)</t>
+  </si>
+  <si>
+    <t>COLONIA LAS PEÑITAS</t>
+  </si>
+  <si>
+    <t>SAN MARTÍN</t>
+  </si>
+  <si>
+    <t>SAN MARTÍN DE PORRES</t>
+  </si>
+  <si>
+    <t>EL VALLECITO DE COAHUILOTES</t>
+  </si>
+  <si>
+    <t>VALLE DE BRAVO</t>
+  </si>
+  <si>
+    <t>SAN PABLO DE LAS SALINAS</t>
+  </si>
+  <si>
+    <t>TLACOCUSPAN</t>
+  </si>
+  <si>
+    <t>SANTA ANA ZICATECOYAN</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA</t>
+  </si>
+  <si>
+    <t>SAN JUAN CORRAL</t>
+  </si>
+  <si>
+    <t>SAN MATEO GUAYATENCO</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>NUEVO COPALTEPEC</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DE ASIS</t>
+  </si>
+  <si>
+    <t>PALMAR GRANDE</t>
+  </si>
+  <si>
+    <t>PALO GORDO</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA OZUMBILLA</t>
+  </si>
+  <si>
+    <t>EL REPARO</t>
+  </si>
+  <si>
+    <t>ALBORADA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NAUCALPAN</t>
+  </si>
+  <si>
+    <t>UZETA</t>
+  </si>
+  <si>
+    <t>SANTA MARÍA DE PICACHOS</t>
+  </si>
+  <si>
+    <t>LOS CERRITOS</t>
+  </si>
+  <si>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>MESA DEL NAYAR</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. PARAÍSO</t>
+  </si>
+  <si>
+    <t>TEPIC, COL. 2 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>ATONALISCO</t>
+  </si>
+  <si>
+    <t>COLORADO DE LA MORA</t>
+  </si>
+  <si>
+    <t>LO DE LAMEDO</t>
+  </si>
+  <si>
+    <t>HERMILTEPEC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>EL COATANTE</t>
+  </si>
+  <si>
+    <t>SALVADOR ALLENDE</t>
+  </si>
+  <si>
+    <t>SAN ANDRÉS</t>
+  </si>
+  <si>
+    <t>SAN JUAN DE ABAJO</t>
+  </si>
+  <si>
+    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>LA GLORIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
+  </si>
+  <si>
     <t>SAN JOSÉ DEL VIDRIO</t>
   </si>
   <si>
-    <t>CAHUACAN 5O. BARRIO</t>
-  </si>
-  <si>
-    <t>COL. LIBERTAD</t>
-  </si>
-  <si>
-    <t>EL GLOBO</t>
-  </si>
-  <si>
-    <t>COL. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>RINCÓN VERDE</t>
+    <t>SAN PEDRO BARRIENTOS</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS III</t>
+  </si>
+  <si>
+    <t>LÁZARO CÁRDENAS II</t>
+  </si>
+  <si>
+    <t>EL TENAYO</t>
+  </si>
+  <si>
+    <t>PRADO IXTACALA</t>
   </si>
   <si>
     <t>BENITO JUÁREZ</t>
   </si>
   <si>
-    <t>SAN MARTÍN DE PORRES</t>
-  </si>
-  <si>
-    <t>SAN MARTÍN</t>
+    <t>CUAUHTÉMOC</t>
+  </si>
+  <si>
+    <t>LA LAGUNA</t>
+  </si>
+  <si>
+    <t>DR. JORGE JIMÉNEZ CANTU</t>
+  </si>
+  <si>
+    <t>SAN JUANICO</t>
+  </si>
+  <si>
+    <t>SANTA CECILIA</t>
+  </si>
+  <si>
+    <t>SAN JAVIER</t>
+  </si>
+  <si>
+    <t>SAN PEDRO TEPETITLÁN</t>
+  </si>
+  <si>
+    <t>JARDINES DE CHALCO</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL DE LOS JAGUEYES</t>
+  </si>
+  <si>
+    <t>MARGARITA MAZA DE JUÁREZ</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO CUAUTLALPAN</t>
+  </si>
+  <si>
+    <t>COLONIA SANTA CRUZ TLAPACOYA</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL CHAMAPA</t>
   </si>
   <si>
     <t>CINCUENTA ARROBAS</t>
   </si>
   <si>
-    <t>PALO GORDO</t>
-  </si>
-  <si>
-    <t>HERMILTEPEC</t>
-  </si>
-  <si>
-    <t>EL VALLECITO DE COAHUILOTES</t>
-  </si>
-  <si>
-    <t>VALLE DE BRAVO</t>
-  </si>
-  <si>
-    <t>TLACOCUSPAN</t>
-  </si>
-  <si>
-    <t>SAN PABLO DE LAS SALINAS</t>
-  </si>
-  <si>
-    <t>SANTA ANA ZICATECOYAN</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA</t>
-  </si>
-  <si>
-    <t>PALMAR GRANDE</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO DE ASIS</t>
-  </si>
-  <si>
-    <t>SAN MATEO GUAYATENCO</t>
-  </si>
-  <si>
-    <t>SAN JUAN CORRAL</t>
-  </si>
-  <si>
-    <t>EL REPARO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NAUCALPAN</t>
-  </si>
-  <si>
-    <t>SANTA CRUZ</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA OZUMBILLA</t>
-  </si>
-  <si>
-    <t>LOS CERRITOS</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA DE PICACHOS</t>
-  </si>
-  <si>
-    <t>MESA DEL NAYAR</t>
-  </si>
-  <si>
-    <t>SANTA FE</t>
-  </si>
-  <si>
-    <t>SANTA TERESA</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. PARAÍSO</t>
-  </si>
-  <si>
-    <t>TEPIC, COL. 2 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>ATONALISCO</t>
-  </si>
-  <si>
-    <t>COLORADO DE LA MORA</t>
-  </si>
-  <si>
-    <t>LO DE LAMEDO</t>
-  </si>
-  <si>
-    <t>SAN ANDRÉS</t>
-  </si>
-  <si>
-    <t>SALVADOR ALLENDE</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CLARA CÓRDOVA</t>
-  </si>
-  <si>
-    <t>UZETA</t>
-  </si>
-  <si>
-    <t>ALBORADA</t>
+    <t>PEDREGAL DE SANTA JULIA</t>
+  </si>
+  <si>
+    <t>HÉROES DE LA INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>VALLE DE LA TRINIDAD</t>
+  </si>
+  <si>
+    <t>DURANGO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-YATIL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
   </si>
   <si>
     <t>LO DE MARCOS</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL POLYUC</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
+  </si>
+  <si>
+    <t>GUÁSIMA DEL METATE</t>
+  </si>
+  <si>
+    <t>CINCO DE MAYO (EL CIRUELO)</t>
+  </si>
+  <si>
+    <t>ARROYO DE CAMARONES</t>
+  </si>
+  <si>
+    <t>EL PORVENIR</t>
+  </si>
+  <si>
     <t>FORTUNA DE VALLEJO (LA GLORIA)</t>
   </si>
   <si>
-    <t>EL COATANTE</t>
-  </si>
-  <si>
-    <t>FRACCIÓNAMIENTO EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON SERVICIOS AMPLIADOS XALISCO</t>
-  </si>
-  <si>
-    <t>EL PORVENIR</t>
-  </si>
-  <si>
-    <t>ARROYO DE CAMARONES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CARACOLES</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS III</t>
-  </si>
-  <si>
-    <t>LÁZARO CÁRDENAS II</t>
-  </si>
-  <si>
-    <t>EL TENAYO</t>
-  </si>
-  <si>
-    <t>PRADO IXTACALA</t>
-  </si>
-  <si>
-    <t>SANTA CECILIA</t>
-  </si>
-  <si>
-    <t>CUAUHTÉMOC</t>
-  </si>
-  <si>
-    <t>LA LAGUNA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO BARRIENTOS</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>DR. JORGE JIMÉNEZ CANTU</t>
-  </si>
-  <si>
-    <t>SAN JUANICO</t>
-  </si>
-  <si>
-    <t>NUEVO COPALTEPEC</t>
-  </si>
-  <si>
-    <t>COLONIA LAS PEÑITAS</t>
-  </si>
-  <si>
-    <t>VALLE DE LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>COLONIA SANTA CRUZ TLAPACOYA</t>
-  </si>
-  <si>
-    <t>MARGARITA MAZA DE JUÁREZ</t>
-  </si>
-  <si>
-    <t>SAN MATEO (LA PRESA)</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO CUAUTLALPAN</t>
-  </si>
-  <si>
-    <t>SAN MIGUEL DE LOS JAGUEYES</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL CHAMAPA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO TEPETITLÁN</t>
-  </si>
-  <si>
-    <t>HÉROES DE LA INDEPENDENCIA</t>
-  </si>
-  <si>
-    <t>PEDREGAL DE SANTA JULIA</t>
-  </si>
-  <si>
-    <t>DURANGO</t>
+    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
+  </si>
+  <si>
+    <t>PIMIENTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 6 DE JUNIO</t>
+  </si>
+  <si>
+    <t>16 DE septiembre</t>
+  </si>
+  <si>
+    <t>NUEVO TAMPAON</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS POCITOS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LOS MAGUEYES</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
+  </si>
+  <si>
+    <t>C.S. URBANO ANÁHUAC</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PROGRESO SOCIAL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. OBRERA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. PARAISO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LAS BLANCAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL CONTROL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD EL GALANEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
+  </si>
+  <si>
+    <t>COL. JUÁREZ</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL EL TESORO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO TULUM</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
   </si>
   <si>
     <t>CENTRO DE SALUD URBANO 10 CANCÚN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD URBANO 12 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 11 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 05 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MELCHOR OCAMPO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LUIS ECHEVERRÍA ALVÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUCTÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BLANCA FLOR</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL MAHAHUAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL BUENAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 02 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL KAMPOKOLCHÉ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 04 CHETUMAL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL FRANCISCO I. MADERO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL ANDRÉS QUINTANA ROO</t>
-  </si>
-  <si>
-    <t>LA GLORIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-YATIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL X-PICHIL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PRESIDENTE JUÁREZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL POLYUC</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHUMPÓN</t>
-  </si>
-  <si>
-    <t>GUÁSIMA DEL METATE</t>
-  </si>
-  <si>
-    <t>CINCO DE MAYO (EL CIRUELO)</t>
-  </si>
-  <si>
-    <t>SAN JUAN DE ABAJO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL PUERTO ARTURO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL TIXCACAL GUARDIA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL DE RÍO ESCONDIDO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL CHACCHOBEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO TULUM</t>
-  </si>
-  <si>
-    <t>COL. JUÁREZ</t>
-  </si>
-  <si>
-    <t>PIMIENTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRANCISCO VILLA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 6 DE JUNIO</t>
-  </si>
-  <si>
-    <t>NUEVO TAMPAON</t>
-  </si>
-  <si>
-    <t>16 DE septiembre</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD 1RO. DE MAYO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN ÁNGEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>C.S. URBANO ANÁHUAC</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS MAGUEYES</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD NUEVO SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. PARAISO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BOSQUES DE JACARANDAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SIMÓN DÍAZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. CHULAVISTA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD COL. TECNOLÓGICO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LAS BLANCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD EL CONTROL</t>
+    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD LA SOLEDAD</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. MANUEL CAVAZOS</t>
@@ -1270,55 +1333,37 @@
     <t>CENTRO DE SALUD UNIDAD HABITACIONAL MACLOVIO HERRERA</t>
   </si>
   <si>
+    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
+  </si>
+  <si>
     <t>CENTRO DE SALUD EL MOQUETITO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS POCITOS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO CALDERITAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRO DE SALUD  RURAL XUL-HA </t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL EL TESORO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 PLAYA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD URBANO 01 CANCÚN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL SAN MARTINIANO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD RURAL LEÓNA VICARÍO</t>
+    <t>CENTRO DE SALUD COL. EUSKADI</t>
+  </si>
+  <si>
+    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD SOLISEÑO</t>
+  </si>
+  <si>
+    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. EL CAMBIO</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. AEROPUERTO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. LAS PALMITAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD FRANCISCO ZARCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FRACCIONAMIENTO VILLAS DE SAN MIGUEL</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LA SOLEDAD</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD BARRANCÓN DEL TÍO BLAS</t>
+    <t>ORIZABA</t>
+  </si>
+  <si>
+    <t>CHICHIGAPA</t>
   </si>
   <si>
     <t>LA CONCEPCIÓN</t>
@@ -1327,49 +1372,34 @@
     <t>XALAPA-ENRÍQUEZ - MIGUEL ALEMÁN</t>
   </si>
   <si>
-    <t>ORIZABA</t>
-  </si>
-  <si>
-    <t>CHICHIGAPA</t>
-  </si>
-  <si>
     <t>XALAPA-ENRÍQUEZ COL. EMILIANO ZAPATA</t>
   </si>
   <si>
-    <t>XALAPA-ENRÍQUEZ  COL. REVOLUCIÓN</t>
-  </si>
-  <si>
-    <t>COATZACOALCOS  COL. NUEVA OBRERA</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD SOLISEÑO</t>
+    <t>LAS BAJADAS</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>DELFINO VICTORIA (SANTA FE)</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
+    <t>CHORRO DE MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
   </si>
   <si>
     <t>GRANJA RÍO MEDIO</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>DELFINO VICTORIA (SANTA FE)</t>
-  </si>
-  <si>
-    <t>LAS BAJADAS</t>
+    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
   <si>
     <t>ZAPOAPAN</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
-  </si>
-  <si>
-    <t>CHORRO DE MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>XALAPA-ENRÍQUEZ ARROYO BLANCO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON HOSPITALIZACION DE LA LOCALIDAD DE ALLENDE, VER.</t>
   </si>
 </sst>
 </file>
@@ -1727,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1758,10 +1788,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1781,10 +1811,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1804,10 +1834,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1827,10 +1857,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1850,10 +1880,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1873,10 +1903,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1896,10 +1926,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1919,10 +1949,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1942,10 +1972,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1965,10 +1995,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1988,10 +2018,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2011,10 +2041,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2034,10 +2064,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2057,10 +2087,10 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2080,10 +2110,10 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2103,10 +2133,10 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2126,10 +2156,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2149,10 +2179,10 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2172,10 +2202,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2195,10 +2225,10 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2218,10 +2248,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2241,10 +2271,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2264,10 +2294,10 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2287,10 +2317,10 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2310,22 +2340,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F26">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G26">
-        <v>53.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2333,22 +2363,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F27">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2356,22 +2386,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F28">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G28">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2379,22 +2409,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29">
-        <v>60</v>
